--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0694</v>
+        <v>0.0612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G2" t="n">
         <v>0.881</v>
@@ -518,7 +518,7 @@
         <v>0.0984</v>
       </c>
       <c r="J2" t="n">
-        <v>0.208</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>0.059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G3" t="n">
         <v>0.881</v>
@@ -558,7 +558,7 @@
         <v>0.0984</v>
       </c>
       <c r="J3" t="n">
-        <v>0.182</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="4">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.383</v>
+        <v>0.389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G4" t="n">
         <v>0.8080000000000001</v>
@@ -598,7 +598,7 @@
         <v>0.164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.522</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +626,7 @@
         <v>0.501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G5" t="n">
         <v>0.8080000000000001</v>
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.324</v>
+        <v>0.304</v>
       </c>
       <c r="F6" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G6" t="n">
         <v>0.867</v>
@@ -678,7 +678,7 @@
         <v>0.0871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.486</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="7">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.204</v>
+        <v>0.186</v>
       </c>
       <c r="F7" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G7" t="n">
         <v>0.867</v>
@@ -718,7 +718,7 @@
         <v>0.0871</v>
       </c>
       <c r="J7" t="n">
-        <v>0.306</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="8">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.632</v>
+        <v>0.64</v>
       </c>
       <c r="F8" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G8" t="n">
         <v>0.828</v>
@@ -758,7 +758,7 @@
         <v>0.145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.634</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="9">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.501</v>
+        <v>0.485</v>
       </c>
       <c r="F9" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G9" t="n">
         <v>0.828</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.457</v>
+        <v>0.466</v>
       </c>
       <c r="F10" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G10" t="n">
         <v>0.826</v>
@@ -838,7 +838,7 @@
         <v>0.186</v>
       </c>
       <c r="J10" t="n">
-        <v>0.571</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="11">
@@ -866,7 +866,7 @@
         <v>0.887</v>
       </c>
       <c r="F11" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G11" t="n">
         <v>0.826</v>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.502</v>
+        <v>0.51</v>
       </c>
       <c r="F12" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G12" t="n">
         <v>0.82</v>
@@ -918,7 +918,7 @@
         <v>0.147</v>
       </c>
       <c r="J12" t="n">
-        <v>0.579</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="13">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.798</v>
+        <v>0.755</v>
       </c>
       <c r="F13" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G13" t="n">
         <v>0.82</v>
@@ -958,7 +958,7 @@
         <v>0.147</v>
       </c>
       <c r="J13" t="n">
-        <v>0.855</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="F14" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G14" t="n">
         <v>0.879</v>
@@ -998,7 +998,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.238</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="15">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G15" t="n">
         <v>0.879</v>
@@ -1038,7 +1038,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.285</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="16">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.634</v>
+        <v>0.641</v>
       </c>
       <c r="F16" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G16" t="n">
         <v>0.826</v>
@@ -1078,7 +1078,7 @@
         <v>0.165</v>
       </c>
       <c r="J16" t="n">
-        <v>0.634</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="17">
@@ -1106,7 +1106,7 @@
         <v>0.55</v>
       </c>
       <c r="F17" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G17" t="n">
         <v>0.826</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.00058</v>
+        <v>0.000515</v>
       </c>
       <c r="F18" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G18" t="n">
         <v>0.922</v>
@@ -1158,7 +1158,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.00773</v>
       </c>
     </row>
     <row r="19">
@@ -1186,7 +1186,7 @@
         <v>0.000976</v>
       </c>
       <c r="F19" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G19" t="n">
         <v>0.922</v>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0195</v>
+        <v>0.0176</v>
       </c>
       <c r="F20" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G20" t="n">
         <v>0.888</v>
@@ -1238,7 +1238,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0731</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0607</v>
+        <v>0.0445</v>
       </c>
       <c r="F21" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
       <c r="G21" t="n">
         <v>0.888</v>
@@ -1278,7 +1278,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="22">
@@ -1315,10 +1315,10 @@
         <v>0.164</v>
       </c>
       <c r="I22" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0731</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1355,7 +1355,7 @@
         <v>0.164</v>
       </c>
       <c r="I23" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="J23" t="n">
         <v>0.0905</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="F24" t="n">
         <v>0.796</v>
@@ -1398,7 +1398,7 @@
         <v>0.186</v>
       </c>
       <c r="J24" t="n">
-        <v>0.238</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="25">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="F26" t="n">
         <v>0.796</v>
@@ -1478,7 +1478,7 @@
         <v>0.187</v>
       </c>
       <c r="J26" t="n">
-        <v>0.238</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.187</v>
       </c>
       <c r="J27" t="n">
-        <v>0.288</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="28">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.211</v>
+        <v>0.207</v>
       </c>
       <c r="F28" t="n">
         <v>0.796</v>
@@ -1558,7 +1558,7 @@
         <v>0.203</v>
       </c>
       <c r="J28" t="n">
-        <v>0.352</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="29">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.157</v>
+        <v>0.14</v>
       </c>
       <c r="F29" t="n">
         <v>0.796</v>
@@ -1598,7 +1598,7 @@
         <v>0.203</v>
       </c>
       <c r="J29" t="n">
-        <v>0.288</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="30">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.00404</v>
+        <v>0.00389</v>
       </c>
       <c r="F30" t="n">
         <v>0.796</v>
@@ -1638,7 +1638,7 @@
         <v>0.0897</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0303</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="31">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0929</v>
       </c>
       <c r="F40" t="n">
         <v>0.87</v>
@@ -2038,7 +2038,7 @@
         <v>0.211</v>
       </c>
       <c r="J40" t="n">
-        <v>0.278</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="41">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.0866</v>
+        <v>0.0867</v>
       </c>
       <c r="F42" t="n">
         <v>0.87</v>
@@ -2118,7 +2118,7 @@
         <v>0.277</v>
       </c>
       <c r="J42" t="n">
-        <v>0.278</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="43">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="F44" t="n">
         <v>0.87</v>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0863</v>
+        <v>0.0864</v>
       </c>
       <c r="F46" t="n">
         <v>0.87</v>
@@ -2278,7 +2278,7 @@
         <v>0.24</v>
       </c>
       <c r="J46" t="n">
-        <v>0.278</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="47">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="F50" t="n">
         <v>0.87</v>
@@ -2438,7 +2438,7 @@
         <v>0.174</v>
       </c>
       <c r="J50" t="n">
-        <v>0.54</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="51">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="F52" t="n">
         <v>0.779</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.66</v>
+        <v>0.658</v>
       </c>
       <c r="F54" t="n">
         <v>0.779</v>
@@ -2598,7 +2598,7 @@
         <v>0.209</v>
       </c>
       <c r="J54" t="n">
-        <v>0.66</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="55">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.535</v>
+        <v>0.534</v>
       </c>
       <c r="F56" t="n">
         <v>0.779</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
       <c r="F58" t="n">
         <v>0.779</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00161</v>
+        <v>0.0016</v>
       </c>
       <c r="F60" t="n">
         <v>0.779</v>
@@ -2838,7 +2838,7 @@
         <v>0.101</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0242</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="61">
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.0167</v>
       </c>
       <c r="F62" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G62" t="n">
         <v>0.821</v>
       </c>
       <c r="H62" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I62" t="n">
         <v>0.187</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0429</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="63">
@@ -2946,13 +2946,13 @@
         <v>0.0186</v>
       </c>
       <c r="F63" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G63" t="n">
         <v>0.821</v>
       </c>
       <c r="H63" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I63" t="n">
         <v>0.187</v>
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="F64" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G64" t="n">
         <v>0.797</v>
       </c>
       <c r="H64" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I64" t="n">
         <v>0.242</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="65">
@@ -3023,22 +3023,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0413</v>
+        <v>0.0309</v>
       </c>
       <c r="F65" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G65" t="n">
         <v>0.797</v>
       </c>
       <c r="H65" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I65" t="n">
         <v>0.242</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0688</v>
+        <v>0.0579</v>
       </c>
     </row>
     <row r="66">
@@ -3063,22 +3063,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.206</v>
+        <v>0.191</v>
       </c>
       <c r="F66" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G66" t="n">
         <v>0.793</v>
       </c>
       <c r="H66" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I66" t="n">
         <v>0.126</v>
       </c>
       <c r="J66" t="n">
-        <v>0.309</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="67">
@@ -3106,13 +3106,13 @@
         <v>0.245</v>
       </c>
       <c r="F67" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G67" t="n">
         <v>0.793</v>
       </c>
       <c r="H67" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I67" t="n">
         <v>0.126</v>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.848</v>
+        <v>0.835</v>
       </c>
       <c r="F68" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G68" t="n">
         <v>0.757</v>
       </c>
       <c r="H68" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I68" t="n">
         <v>0.198</v>
       </c>
       <c r="J68" t="n">
-        <v>0.856</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="69">
@@ -3183,22 +3183,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.224</v>
+        <v>0.205</v>
       </c>
       <c r="F69" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G69" t="n">
         <v>0.757</v>
       </c>
       <c r="H69" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I69" t="n">
         <v>0.198</v>
       </c>
       <c r="J69" t="n">
-        <v>0.283</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="70">
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0112</v>
+        <v>0.009769999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G70" t="n">
         <v>0.833</v>
       </c>
       <c r="H70" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I70" t="n">
         <v>0.097</v>
       </c>
       <c r="J70" t="n">
-        <v>0.028</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="71">
@@ -3266,13 +3266,13 @@
         <v>0.00963</v>
       </c>
       <c r="F71" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G71" t="n">
         <v>0.833</v>
       </c>
       <c r="H71" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I71" t="n">
         <v>0.097</v>
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.835</v>
+        <v>0.846</v>
       </c>
       <c r="F72" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G72" t="n">
         <v>0.728</v>
       </c>
       <c r="H72" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I72" t="n">
         <v>0.253</v>
       </c>
       <c r="J72" t="n">
-        <v>0.856</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="73">
@@ -3346,13 +3346,13 @@
         <v>0.496</v>
       </c>
       <c r="F73" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G73" t="n">
         <v>0.728</v>
       </c>
       <c r="H73" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I73" t="n">
         <v>0.253</v>
@@ -3383,22 +3383,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.038</v>
+        <v>0.0338</v>
       </c>
       <c r="F74" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G74" t="n">
         <v>0.824</v>
       </c>
       <c r="H74" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I74" t="n">
         <v>0.111</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0648</v>
+        <v>0.0603</v>
       </c>
     </row>
     <row r="75">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0413</v>
+        <v>0.0354</v>
       </c>
       <c r="F75" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G75" t="n">
         <v>0.824</v>
       </c>
       <c r="H75" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I75" t="n">
         <v>0.111</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0688</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="76">
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.788</v>
+        <v>0.778</v>
       </c>
       <c r="F76" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G76" t="n">
         <v>0.766</v>
       </c>
       <c r="H76" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I76" t="n">
         <v>0.265</v>
       </c>
       <c r="J76" t="n">
-        <v>0.856</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="77">
@@ -3503,22 +3503,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.233</v>
+        <v>0.208</v>
       </c>
       <c r="F77" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G77" t="n">
         <v>0.766</v>
       </c>
       <c r="H77" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I77" t="n">
         <v>0.265</v>
       </c>
       <c r="J77" t="n">
-        <v>0.283</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="78">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.0022</v>
+        <v>0.00197</v>
       </c>
       <c r="F78" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G78" t="n">
         <v>0.859</v>
       </c>
       <c r="H78" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I78" t="n">
         <v>0.157</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0184</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="79">
@@ -3583,16 +3583,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.00713</v>
+        <v>0.00577</v>
       </c>
       <c r="F79" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G79" t="n">
         <v>0.859</v>
       </c>
       <c r="H79" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I79" t="n">
         <v>0.157</v>
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0389</v>
+        <v>0.0362</v>
       </c>
       <c r="F80" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G80" t="n">
         <v>0.824</v>
       </c>
       <c r="H80" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I80" t="n">
         <v>0.183</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0648</v>
+        <v>0.0603</v>
       </c>
     </row>
     <row r="81">
@@ -3666,13 +3666,13 @@
         <v>0.0546</v>
       </c>
       <c r="F81" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="G81" t="n">
         <v>0.824</v>
       </c>
       <c r="H81" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="I81" t="n">
         <v>0.183</v>
@@ -3706,19 +3706,19 @@
         <v>0.0106</v>
       </c>
       <c r="F82" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I82" t="n">
         <v>0.157</v>
       </c>
       <c r="J82" t="n">
-        <v>0.028</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="83">
@@ -3746,13 +3746,13 @@
         <v>0.00763</v>
       </c>
       <c r="F83" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I83" t="n">
         <v>0.157</v>
@@ -3783,22 +3783,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.00248</v>
+        <v>0.00258</v>
       </c>
       <c r="F84" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G84" t="n">
         <v>0.842</v>
       </c>
       <c r="H84" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I84" t="n">
         <v>0.102</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0184</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="85">
@@ -3826,13 +3826,13 @@
         <v>0.00261</v>
       </c>
       <c r="F85" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G85" t="n">
         <v>0.842</v>
       </c>
       <c r="H85" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I85" t="n">
         <v>0.102</v>
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.00367</v>
+        <v>0.00371</v>
       </c>
       <c r="F86" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G86" t="n">
         <v>0.837</v>
       </c>
       <c r="H86" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I86" t="n">
         <v>0.0997</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0184</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="87">
@@ -3906,13 +3906,13 @@
         <v>0.00336</v>
       </c>
       <c r="F87" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G87" t="n">
         <v>0.837</v>
       </c>
       <c r="H87" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I87" t="n">
         <v>0.0997</v>
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.00659</v>
+        <v>0.00671</v>
       </c>
       <c r="F88" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G88" t="n">
         <v>0.841</v>
       </c>
       <c r="H88" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I88" t="n">
         <v>0.104</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0247</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="89">
@@ -3986,13 +3986,13 @@
         <v>0.00629</v>
       </c>
       <c r="F89" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G89" t="n">
         <v>0.841</v>
       </c>
       <c r="H89" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I89" t="n">
         <v>0.104</v>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.856</v>
+        <v>0.874</v>
       </c>
       <c r="F90" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G90" t="n">
         <v>0.734</v>
       </c>
       <c r="H90" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I90" t="n">
         <v>0.184</v>
       </c>
       <c r="J90" t="n">
-        <v>0.856</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="91">
@@ -4066,13 +4066,13 @@
         <v>0.955</v>
       </c>
       <c r="F91" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="G91" t="n">
         <v>0.734</v>
       </c>
       <c r="H91" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="I91" t="n">
         <v>0.184</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.196</v>
+        <v>0.184</v>
       </c>
       <c r="F92" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G92" t="n">
         <v>0.821</v>
@@ -4118,7 +4118,7 @@
         <v>0.161</v>
       </c>
       <c r="J92" t="n">
-        <v>0.327</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="93">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.274</v>
+        <v>0.252</v>
       </c>
       <c r="F93" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G93" t="n">
         <v>0.821</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.507</v>
+        <v>0.513</v>
       </c>
       <c r="F94" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G94" t="n">
         <v>0.741</v>
@@ -4198,7 +4198,7 @@
         <v>0.245</v>
       </c>
       <c r="J94" t="n">
-        <v>0.603</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="95">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.82</v>
+        <v>0.776</v>
       </c>
       <c r="F95" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G95" t="n">
         <v>0.741</v>
@@ -4238,7 +4238,7 @@
         <v>0.245</v>
       </c>
       <c r="J95" t="n">
-        <v>0.879</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="96">
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.523</v>
+        <v>0.509</v>
       </c>
       <c r="F96" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G96" t="n">
         <v>0.8080000000000001</v>
@@ -4278,7 +4278,7 @@
         <v>0.113</v>
       </c>
       <c r="J96" t="n">
-        <v>0.603</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="97">
@@ -4306,7 +4306,7 @@
         <v>0.274</v>
       </c>
       <c r="F97" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G97" t="n">
         <v>0.8080000000000001</v>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.725</v>
+        <v>0.731</v>
       </c>
       <c r="F98" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G98" t="n">
         <v>0.762</v>
@@ -4358,7 +4358,7 @@
         <v>0.206</v>
       </c>
       <c r="J98" t="n">
-        <v>0.725</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="99">
@@ -4386,7 +4386,7 @@
         <v>0.464</v>
       </c>
       <c r="F99" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G99" t="n">
         <v>0.762</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.501</v>
+        <v>0.487</v>
       </c>
       <c r="F100" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G100" t="n">
         <v>0.806</v>
@@ -4438,7 +4438,7 @@
         <v>0.153</v>
       </c>
       <c r="J100" t="n">
-        <v>0.603</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="101">
@@ -4466,7 +4466,7 @@
         <v>0.57</v>
       </c>
       <c r="F101" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G101" t="n">
         <v>0.806</v>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.431</v>
+        <v>0.436</v>
       </c>
       <c r="F102" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G102" t="n">
         <v>0.733</v>
@@ -4518,7 +4518,7 @@
         <v>0.258</v>
       </c>
       <c r="J102" t="n">
-        <v>0.603</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="103">
@@ -4546,7 +4546,7 @@
         <v>0.98</v>
       </c>
       <c r="F103" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G103" t="n">
         <v>0.733</v>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.179</v>
+        <v>0.17</v>
       </c>
       <c r="F104" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G104" t="n">
         <v>0.826</v>
@@ -4598,7 +4598,7 @@
         <v>0.118</v>
       </c>
       <c r="J104" t="n">
-        <v>0.327</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="105">
@@ -4626,7 +4626,7 @@
         <v>0.125</v>
       </c>
       <c r="F105" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G105" t="n">
         <v>0.826</v>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.627</v>
+        <v>0.633</v>
       </c>
       <c r="F106" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G106" t="n">
         <v>0.753</v>
@@ -4678,7 +4678,7 @@
         <v>0.244</v>
       </c>
       <c r="J106" t="n">
-        <v>0.672</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="107">
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.394</v>
+        <v>0.363</v>
       </c>
       <c r="F107" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G107" t="n">
         <v>0.753</v>
@@ -4718,7 +4718,7 @@
         <v>0.244</v>
       </c>
       <c r="J107" t="n">
-        <v>0.537</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="108">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.000213</v>
+        <v>0.000187</v>
       </c>
       <c r="F108" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G108" t="n">
         <v>0.886</v>
@@ -4758,7 +4758,7 @@
         <v>0.118</v>
       </c>
       <c r="J108" t="n">
-        <v>0.00319</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="109">
@@ -4786,7 +4786,7 @@
         <v>0.000982</v>
       </c>
       <c r="F109" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G109" t="n">
         <v>0.886</v>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.0577</v>
+        <v>0.0536</v>
       </c>
       <c r="F110" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G110" t="n">
         <v>0.827</v>
@@ -4838,7 +4838,7 @@
         <v>0.173</v>
       </c>
       <c r="J110" t="n">
-        <v>0.124</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="111">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="G111" t="n">
         <v>0.827</v>
@@ -4878,7 +4878,7 @@
         <v>0.173</v>
       </c>
       <c r="J111" t="n">
-        <v>0.213</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="112">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.00275</v>
+        <v>0.00286</v>
       </c>
       <c r="F112" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G112" t="n">
         <v>0.789</v>
@@ -4915,10 +4915,10 @@
         <v>0.176</v>
       </c>
       <c r="I112" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0206</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="113">
@@ -4946,7 +4946,7 @@
         <v>0.00377</v>
       </c>
       <c r="F113" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G113" t="n">
         <v>0.789</v>
@@ -4955,7 +4955,7 @@
         <v>0.176</v>
       </c>
       <c r="I113" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="J113" t="n">
         <v>0.0209</v>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.0141</v>
+        <v>0.0142</v>
       </c>
       <c r="F114" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G114" t="n">
         <v>0.799</v>
@@ -4998,7 +4998,7 @@
         <v>0.153</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0512</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="115">
@@ -5026,7 +5026,7 @@
         <v>0.00629</v>
       </c>
       <c r="F115" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G115" t="n">
         <v>0.799</v>
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.0175</v>
+        <v>0.0173</v>
       </c>
       <c r="F116" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G116" t="n">
         <v>0.798</v>
@@ -5078,7 +5078,7 @@
         <v>0.16</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0512</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="117">
@@ -5106,7 +5106,7 @@
         <v>0.029</v>
       </c>
       <c r="F117" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G117" t="n">
         <v>0.798</v>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="F118" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G118" t="n">
         <v>0.801</v>
@@ -5158,7 +5158,7 @@
         <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0512</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="119">
@@ -5186,7 +5186,7 @@
         <v>0.029</v>
       </c>
       <c r="F119" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G119" t="n">
         <v>0.801</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0124</v>
+        <v>0.0121</v>
       </c>
       <c r="F120" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G120" t="n">
         <v>0.8100000000000001</v>
@@ -5238,7 +5238,7 @@
         <v>0.149</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0512</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="121">
@@ -5266,7 +5266,7 @@
         <v>0.00418</v>
       </c>
       <c r="F121" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G121" t="n">
         <v>0.8100000000000001</v>
@@ -5700,16 +5700,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.833</v>
       </c>
       <c r="H11" t="n">
-        <v>0.013</v>
+        <v>0.0256</v>
       </c>
       <c r="I11" t="n">
-        <v>0.104</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="12">
@@ -6298,7 +6298,7 @@
         <v>0.913</v>
       </c>
       <c r="H27" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="I27" t="n">
         <v>0.48</v>
@@ -6560,7 +6560,7 @@
         <v>0.0479</v>
       </c>
       <c r="I34" t="n">
-        <v>0.128</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="35">
@@ -6884,16 +6884,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G43" t="n">
         <v>0.724</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0314</v>
+        <v>0.0609</v>
       </c>
       <c r="I43" t="n">
-        <v>0.101</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="44">
@@ -7476,16 +7476,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G59" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00657</v>
+        <v>0.0139</v>
       </c>
       <c r="I59" t="n">
-        <v>0.035</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="60">
@@ -7892,7 +7892,7 @@
         <v>0.588</v>
       </c>
       <c r="I70" t="n">
-        <v>0.821</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="71">
@@ -8003,7 +8003,7 @@
         <v>0.499</v>
       </c>
       <c r="I73" t="n">
-        <v>0.821</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="74">
@@ -8068,16 +8068,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G75" t="n">
         <v>0.917</v>
       </c>
       <c r="H75" t="n">
-        <v>0.616</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>0.821</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="76">
@@ -8114,7 +8114,7 @@
         <v>0.549</v>
       </c>
       <c r="I76" t="n">
-        <v>0.821</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="77">
@@ -8151,7 +8151,7 @@
         <v>0.579</v>
       </c>
       <c r="I77" t="n">
-        <v>0.821</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="78">
@@ -8299,7 +8299,7 @@
         <v>0.681</v>
       </c>
       <c r="I81" t="n">
-        <v>0.839</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="82">
@@ -8666,10 +8666,10 @@
         <v>0.929</v>
       </c>
       <c r="H91" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="I91" t="n">
-        <v>0.486</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="92">
@@ -9252,7 +9252,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G107" t="n">
         <v>0.897</v>
@@ -9520,7 +9520,7 @@
         <v>0.706</v>
       </c>
       <c r="I114" t="n">
-        <v>0.963</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -9668,7 +9668,7 @@
         <v>0.722</v>
       </c>
       <c r="I118" t="n">
-        <v>0.963</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -9844,16 +9844,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G123" t="n">
         <v>0.912</v>
       </c>
       <c r="H123" t="n">
-        <v>0.616</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>0.963</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -10001,7 +10001,7 @@
         <v>0.605</v>
       </c>
       <c r="I127" t="n">
-        <v>0.963</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -10149,7 +10149,7 @@
         <v>0.01</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0571</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="132">
@@ -10223,7 +10223,7 @@
         <v>0.0143</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0571</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="134">
@@ -10436,16 +10436,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G139" t="n">
         <v>0.833</v>
       </c>
       <c r="H139" t="n">
-        <v>0.013</v>
+        <v>0.0256</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0571</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="140">
@@ -11034,7 +11034,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>0.326</v>
+        <v>0.33</v>
       </c>
       <c r="I155" t="n">
         <v>0.5629999999999999</v>
@@ -11620,16 +11620,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G171" t="n">
         <v>0.707</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0185</v>
+        <v>0.0377</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0989</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="172">
@@ -12073,7 +12073,7 @@
         <v>0.00663</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0354</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="184">
@@ -12212,16 +12212,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G187" t="n">
         <v>0.804</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0039</v>
+        <v>0.00872</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0312</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="188">
@@ -12665,7 +12665,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>0.21</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="200">
@@ -12804,16 +12804,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G203" t="n">
         <v>0.858</v>
       </c>
       <c r="H203" t="n">
-        <v>0.0509</v>
+        <v>0.0893</v>
       </c>
       <c r="I203" t="n">
-        <v>0.204</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="204">
@@ -13402,10 +13402,10 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="H219" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="I219" t="n">
-        <v>0.452</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="220">
@@ -13988,16 +13988,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G235" t="n">
         <v>0.759</v>
       </c>
       <c r="H235" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="I235" t="n">
-        <v>0.267</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="236">
@@ -14580,16 +14580,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G251" t="n">
         <v>0.838</v>
       </c>
       <c r="H251" t="n">
-        <v>0.0291</v>
+        <v>0.0547</v>
       </c>
       <c r="I251" t="n">
-        <v>0.116</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="252">
@@ -14626,7 +14626,7 @@
         <v>0.0419</v>
       </c>
       <c r="I252" t="n">
-        <v>0.134</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="253">
@@ -15172,16 +15172,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G267" t="n">
         <v>0.908</v>
       </c>
       <c r="H267" t="n">
-        <v>0.463</v>
+        <v>0.634</v>
       </c>
       <c r="I267" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -16069,7 +16069,7 @@
         <v>0.489</v>
       </c>
       <c r="I291" t="n">
-        <v>0.783</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="292">
@@ -16356,16 +16356,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G299" t="n">
         <v>0.828</v>
       </c>
       <c r="H299" t="n">
-        <v>0.42</v>
+        <v>0.601</v>
       </c>
       <c r="I299" t="n">
-        <v>0.747</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="300">
@@ -16772,7 +16772,7 @@
         <v>0.388</v>
       </c>
       <c r="I310" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="311">
@@ -16948,16 +16948,16 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G315" t="n">
         <v>0.897</v>
       </c>
       <c r="H315" t="n">
-        <v>0.331</v>
+        <v>0.479</v>
       </c>
       <c r="I315" t="n">
-        <v>0.663</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="316">
@@ -17253,7 +17253,7 @@
         <v>0.112</v>
       </c>
       <c r="I323" t="n">
-        <v>0.542</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="324">
@@ -17401,7 +17401,7 @@
         <v>0.0975</v>
       </c>
       <c r="I327" t="n">
-        <v>0.542</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="328">
@@ -17512,7 +17512,7 @@
         <v>0.208</v>
       </c>
       <c r="I330" t="n">
-        <v>0.555</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="331">
@@ -17540,16 +17540,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G331" t="n">
         <v>0.883</v>
       </c>
       <c r="H331" t="n">
-        <v>0.169</v>
+        <v>0.263</v>
       </c>
       <c r="I331" t="n">
-        <v>0.542</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="332">
@@ -17623,7 +17623,7 @@
         <v>0.161</v>
       </c>
       <c r="I333" t="n">
-        <v>0.542</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="334">
@@ -18724,16 +18724,16 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G363" t="n">
         <v>0.776</v>
       </c>
       <c r="H363" t="n">
-        <v>0.131</v>
+        <v>0.219</v>
       </c>
       <c r="I363" t="n">
-        <v>0.233</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="364">
@@ -18807,7 +18807,7 @@
         <v>0.129</v>
       </c>
       <c r="I365" t="n">
-        <v>0.233</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="366">
@@ -19288,7 +19288,7 @@
         <v>0.0853</v>
       </c>
       <c r="I378" t="n">
-        <v>0.342</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="379">
@@ -19316,16 +19316,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G379" t="n">
         <v>0.865</v>
       </c>
       <c r="H379" t="n">
-        <v>0.107</v>
+        <v>0.177</v>
       </c>
       <c r="I379" t="n">
-        <v>0.342</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="380">
@@ -19362,7 +19362,7 @@
         <v>0.0941</v>
       </c>
       <c r="I380" t="n">
-        <v>0.342</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="381">
@@ -19695,7 +19695,7 @@
         <v>0.0293</v>
       </c>
       <c r="I389" t="n">
-        <v>0.117</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="390">
@@ -19908,16 +19908,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G395" t="n">
         <v>0.842</v>
       </c>
       <c r="H395" t="n">
-        <v>0.0209</v>
+        <v>0.0395</v>
       </c>
       <c r="I395" t="n">
-        <v>0.111</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="396">
@@ -20506,10 +20506,10 @@
         <v>0.898</v>
       </c>
       <c r="H411" t="n">
-        <v>0.102</v>
+        <v>0.105</v>
       </c>
       <c r="I411" t="n">
-        <v>0.328</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="412">
@@ -21092,16 +21092,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G427" t="n">
         <v>0.759</v>
       </c>
       <c r="H427" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="I427" t="n">
-        <v>0.267</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="428">
@@ -21175,7 +21175,7 @@
         <v>0.129</v>
       </c>
       <c r="I429" t="n">
-        <v>0.345</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="430">
@@ -21582,7 +21582,7 @@
         <v>0.0182</v>
       </c>
       <c r="I440" t="n">
-        <v>0.0584</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="441">
@@ -21656,7 +21656,7 @@
         <v>0.0141</v>
       </c>
       <c r="I442" t="n">
-        <v>0.0563</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="443">
@@ -21684,16 +21684,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G443" t="n">
         <v>0.822</v>
       </c>
       <c r="H443" t="n">
-        <v>0.0115</v>
+        <v>0.0235</v>
       </c>
       <c r="I443" t="n">
-        <v>0.0563</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="444">
@@ -22276,16 +22276,16 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G459" t="n">
         <v>0.9</v>
       </c>
       <c r="H459" t="n">
-        <v>0.339</v>
+        <v>0.484</v>
       </c>
       <c r="I459" t="n">
-        <v>0.678</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="460">
@@ -22877,7 +22877,7 @@
         <v>0.207</v>
       </c>
       <c r="I475" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="476">
@@ -23460,7 +23460,7 @@
         <v>10</v>
       </c>
       <c r="F491" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G491" t="n">
         <v>0.879</v>
@@ -23876,7 +23876,7 @@
         <v>0.304</v>
       </c>
       <c r="I502" t="n">
-        <v>0.602</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="503">
@@ -24052,16 +24052,16 @@
         <v>10</v>
       </c>
       <c r="F507" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G507" t="n">
         <v>0.895</v>
       </c>
       <c r="H507" t="n">
-        <v>0.339</v>
+        <v>0.485</v>
       </c>
       <c r="I507" t="n">
-        <v>0.602</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="508">
@@ -24209,7 +24209,7 @@
         <v>0.333</v>
       </c>
       <c r="I511" t="n">
-        <v>0.602</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="512">
@@ -24644,16 +24644,16 @@
         <v>10</v>
       </c>
       <c r="F523" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G523" t="n">
         <v>0.958</v>
       </c>
       <c r="H523" t="n">
-        <v>0.769</v>
+        <v>0.57</v>
       </c>
       <c r="I523" t="n">
-        <v>1</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="524">
@@ -25541,7 +25541,7 @@
         <v>0.489</v>
       </c>
       <c r="I547" t="n">
-        <v>0.783</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="548">
@@ -25652,7 +25652,7 @@
         <v>0.681</v>
       </c>
       <c r="I550" t="n">
-        <v>0.99</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="551">
@@ -25828,16 +25828,16 @@
         <v>10</v>
       </c>
       <c r="F555" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G555" t="n">
         <v>0.931</v>
       </c>
       <c r="H555" t="n">
-        <v>0.743</v>
+        <v>0.528</v>
       </c>
       <c r="I555" t="n">
-        <v>0.99</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="556">
@@ -26420,16 +26420,16 @@
         <v>10</v>
       </c>
       <c r="F571" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G571" t="n">
         <v>0.956</v>
       </c>
       <c r="H571" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.405</v>
       </c>
       <c r="I571" t="n">
-        <v>0.826</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="572">
@@ -27012,7 +27012,7 @@
         <v>10</v>
       </c>
       <c r="F587" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G587" t="n">
         <v>0.9330000000000001</v>
@@ -28196,13 +28196,13 @@
         <v>10</v>
       </c>
       <c r="F619" t="n">
-        <v>0.897</v>
+        <v>0.879</v>
       </c>
       <c r="G619" t="n">
         <v>0.914</v>
       </c>
       <c r="H619" t="n">
-        <v>1</v>
+        <v>0.762</v>
       </c>
       <c r="I619" t="n">
         <v>1</v>
@@ -28788,7 +28788,7 @@
         <v>10</v>
       </c>
       <c r="F635" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G635" t="n">
         <v>0.93</v>
@@ -29380,16 +29380,16 @@
         <v>10</v>
       </c>
       <c r="F651" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G651" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.925</v>
       </c>
       <c r="H651" t="n">
-        <v>0.00383</v>
+        <v>0.00491</v>
       </c>
       <c r="I651" t="n">
-        <v>0.0614</v>
+        <v>0.0786</v>
       </c>
     </row>
     <row r="652">
@@ -29972,13 +29972,13 @@
         <v>10</v>
       </c>
       <c r="F667" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="G667" t="n">
         <v>1</v>
       </c>
       <c r="H667" t="n">
-        <v>0.419</v>
+        <v>0.417</v>
       </c>
       <c r="I667" t="n">
         <v>1</v>
@@ -30564,16 +30564,16 @@
         <v>10</v>
       </c>
       <c r="F683" t="n">
-        <v>0.603</v>
+        <v>0.586</v>
       </c>
       <c r="G683" t="n">
-        <v>0.862</v>
+        <v>0.845</v>
       </c>
       <c r="H683" t="n">
-        <v>0.00294</v>
+        <v>0.00359</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0235</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="684">
@@ -31156,16 +31156,16 @@
         <v>10</v>
       </c>
       <c r="F699" t="n">
-        <v>0.745</v>
+        <v>0.731</v>
       </c>
       <c r="G699" t="n">
-        <v>0.926</v>
+        <v>0.916</v>
       </c>
       <c r="H699" t="n">
-        <v>0.000471</v>
+        <v>0.000611</v>
       </c>
       <c r="I699" t="n">
-        <v>0.00753</v>
+        <v>0.009769999999999999</v>
       </c>
     </row>
     <row r="700">
@@ -31748,16 +31748,16 @@
         <v>10</v>
       </c>
       <c r="F715" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G715" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H715" t="n">
-        <v>0.00383</v>
+        <v>0.0023</v>
       </c>
       <c r="I715" t="n">
-        <v>0.0614</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="716">
@@ -32340,13 +32340,13 @@
         <v>10</v>
       </c>
       <c r="F731" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="G731" t="n">
         <v>1</v>
       </c>
       <c r="H731" t="n">
-        <v>0.419</v>
+        <v>0.412</v>
       </c>
       <c r="I731" t="n">
         <v>1</v>
@@ -32932,16 +32932,16 @@
         <v>10</v>
       </c>
       <c r="F747" t="n">
-        <v>0.603</v>
+        <v>0.586</v>
       </c>
       <c r="G747" t="n">
         <v>0.862</v>
       </c>
       <c r="H747" t="n">
-        <v>0.00294</v>
+        <v>0.00159</v>
       </c>
       <c r="I747" t="n">
-        <v>0.0235</v>
+        <v>0.0127</v>
       </c>
     </row>
     <row r="748">
@@ -33524,16 +33524,16 @@
         <v>10</v>
       </c>
       <c r="F763" t="n">
-        <v>0.745</v>
+        <v>0.731</v>
       </c>
       <c r="G763" t="n">
         <v>0.926</v>
       </c>
       <c r="H763" t="n">
-        <v>0.000471</v>
+        <v>0.000234</v>
       </c>
       <c r="I763" t="n">
-        <v>0.00753</v>
+        <v>0.00374</v>
       </c>
     </row>
     <row r="764">
@@ -34088,7 +34088,7 @@
         <v>0.0154</v>
       </c>
       <c r="I778" t="n">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="779">
@@ -34116,16 +34116,16 @@
         <v>10</v>
       </c>
       <c r="F779" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G779" t="n">
         <v>0.908</v>
       </c>
       <c r="H779" t="n">
-        <v>0.0271</v>
+        <v>0.0179</v>
       </c>
       <c r="I779" t="n">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="780">
@@ -34708,7 +34708,7 @@
         <v>10</v>
       </c>
       <c r="F795" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="G795" t="n">
         <v>0.98</v>
@@ -35300,16 +35300,16 @@
         <v>10</v>
       </c>
       <c r="F811" t="n">
-        <v>0.603</v>
+        <v>0.586</v>
       </c>
       <c r="G811" t="n">
         <v>0.828</v>
       </c>
       <c r="H811" t="n">
-        <v>0.0129</v>
+        <v>0.0075</v>
       </c>
       <c r="I811" t="n">
-        <v>0.103</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="812">
@@ -35864,7 +35864,7 @@
         <v>0.00181</v>
       </c>
       <c r="I826" t="n">
-        <v>0.029</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="827">
@@ -35892,16 +35892,16 @@
         <v>10</v>
       </c>
       <c r="F827" t="n">
-        <v>0.745</v>
+        <v>0.731</v>
       </c>
       <c r="G827" t="n">
         <v>0.897</v>
       </c>
       <c r="H827" t="n">
-        <v>0.00517</v>
+        <v>0.00294</v>
       </c>
       <c r="I827" t="n">
-        <v>0.0413</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="828">
@@ -36456,7 +36456,7 @@
         <v>0.00226</v>
       </c>
       <c r="I842" t="n">
-        <v>0.0307</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="843">
@@ -36484,16 +36484,16 @@
         <v>10</v>
       </c>
       <c r="F843" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G843" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H843" t="n">
-        <v>0.00383</v>
+        <v>0.0023</v>
       </c>
       <c r="I843" t="n">
-        <v>0.0307</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="844">
@@ -37076,7 +37076,7 @@
         <v>10</v>
       </c>
       <c r="F859" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="G859" t="n">
         <v>0.981</v>
@@ -37668,16 +37668,16 @@
         <v>10</v>
       </c>
       <c r="F875" t="n">
-        <v>0.603</v>
+        <v>0.586</v>
       </c>
       <c r="G875" t="n">
         <v>0.879</v>
       </c>
       <c r="H875" t="n">
-        <v>0.00123</v>
+        <v>0.000639</v>
       </c>
       <c r="I875" t="n">
-        <v>0.009860000000000001</v>
+        <v>0.00511</v>
       </c>
     </row>
     <row r="876">
@@ -38232,7 +38232,7 @@
         <v>0.000169</v>
       </c>
       <c r="I890" t="n">
-        <v>0.0027</v>
+        <v>0.00171</v>
       </c>
     </row>
     <row r="891">
@@ -38260,16 +38260,16 @@
         <v>10</v>
       </c>
       <c r="F891" t="n">
-        <v>0.745</v>
+        <v>0.731</v>
       </c>
       <c r="G891" t="n">
         <v>0.927</v>
       </c>
       <c r="H891" t="n">
-        <v>0.000423</v>
+        <v>0.000213</v>
       </c>
       <c r="I891" t="n">
-        <v>0.00338</v>
+        <v>0.00171</v>
       </c>
     </row>
     <row r="892">
@@ -38602,7 +38602,7 @@
         <v>0.0503</v>
       </c>
       <c r="I900" t="n">
-        <v>0.233</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="901">
@@ -38852,16 +38852,16 @@
         <v>10</v>
       </c>
       <c r="F907" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G907" t="n">
         <v>0.892</v>
       </c>
       <c r="H907" t="n">
-        <v>0.0728</v>
+        <v>0.0507</v>
       </c>
       <c r="I907" t="n">
-        <v>0.233</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="908">
@@ -39009,7 +39009,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I911" t="n">
-        <v>0.233</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="912">
@@ -39444,7 +39444,7 @@
         <v>10</v>
       </c>
       <c r="F923" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="G923" t="n">
         <v>0.959</v>
@@ -40036,16 +40036,16 @@
         <v>10</v>
       </c>
       <c r="F939" t="n">
-        <v>0.603</v>
+        <v>0.586</v>
       </c>
       <c r="G939" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H939" t="n">
-        <v>0.0241</v>
+        <v>0.0146</v>
       </c>
       <c r="I939" t="n">
-        <v>0.128</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="940">
@@ -40628,16 +40628,16 @@
         <v>10</v>
       </c>
       <c r="F955" t="n">
-        <v>0.745</v>
+        <v>0.731</v>
       </c>
       <c r="G955" t="n">
         <v>0.879</v>
       </c>
       <c r="H955" t="n">
-        <v>0.0177</v>
+        <v>0.011</v>
       </c>
       <c r="I955" t="n">
-        <v>0.283</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="956">

--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -518,7 +518,7 @@
         <v>0.0984</v>
       </c>
       <c r="J2" t="n">
-        <v>0.184</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>0.0984</v>
       </c>
       <c r="J3" t="n">
-        <v>0.177</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.53</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.164</v>
       </c>
       <c r="J5" t="n">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
         <v>0.0871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.456</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.0871</v>
       </c>
       <c r="J7" t="n">
-        <v>0.279</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.641</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.186</v>
       </c>
       <c r="J10" t="n">
-        <v>0.583</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.186</v>
       </c>
       <c r="J11" t="n">
-        <v>0.887</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>0.147</v>
       </c>
       <c r="J12" t="n">
-        <v>0.588</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="13">
@@ -958,7 +958,7 @@
         <v>0.147</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.219</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1038,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.263</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="16">
@@ -1078,7 +1078,7 @@
         <v>0.165</v>
       </c>
       <c r="J16" t="n">
-        <v>0.641</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="17">
@@ -1118,7 +1118,7 @@
         <v>0.165</v>
       </c>
       <c r="J17" t="n">
-        <v>0.635</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="18">
@@ -1158,7 +1158,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00773</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.011</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.167</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.174</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.174</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0905</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.186</v>
       </c>
       <c r="J24" t="n">
-        <v>0.219</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.186</v>
       </c>
       <c r="J25" t="n">
-        <v>0.219</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.187</v>
       </c>
       <c r="J26" t="n">
-        <v>0.219</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.187</v>
       </c>
       <c r="J27" t="n">
-        <v>0.279</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.203</v>
       </c>
       <c r="J28" t="n">
-        <v>0.345</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.203</v>
       </c>
       <c r="J29" t="n">
-        <v>0.263</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="30">
@@ -1678,7 +1678,7 @@
         <v>0.0897</v>
       </c>
       <c r="J31" t="n">
-        <v>0.011</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.174</v>
       </c>
       <c r="J33" t="n">
-        <v>0.263</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.261</v>
       </c>
       <c r="J34" t="n">
-        <v>0.212</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1838,7 +1838,7 @@
         <v>0.261</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0313</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="36">
@@ -1878,7 +1878,7 @@
         <v>0.156</v>
       </c>
       <c r="J36" t="n">
-        <v>0.587</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.156</v>
       </c>
       <c r="J37" t="n">
-        <v>0.695</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.222</v>
       </c>
       <c r="J38" t="n">
-        <v>0.42</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.222</v>
       </c>
       <c r="J39" t="n">
-        <v>0.378</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.211</v>
       </c>
       <c r="J40" t="n">
-        <v>0.279</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.211</v>
       </c>
       <c r="J41" t="n">
-        <v>0.161</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.277</v>
       </c>
       <c r="J42" t="n">
-        <v>0.279</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.277</v>
       </c>
       <c r="J43" t="n">
-        <v>0.126</v>
+        <v>0.09569999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>0.587</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.16</v>
       </c>
       <c r="J45" t="n">
-        <v>0.378</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.24</v>
       </c>
       <c r="J46" t="n">
-        <v>0.279</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.24</v>
       </c>
       <c r="J47" t="n">
-        <v>0.126</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.064</v>
       </c>
       <c r="J48" t="n">
-        <v>0.319</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.064</v>
       </c>
       <c r="J49" t="n">
-        <v>0.732</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.174</v>
       </c>
       <c r="J50" t="n">
-        <v>0.542</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.174</v>
       </c>
       <c r="J51" t="n">
-        <v>0.263</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.235</v>
       </c>
       <c r="J52" t="n">
-        <v>0.319</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.235</v>
       </c>
       <c r="J53" t="n">
-        <v>0.263</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.209</v>
       </c>
       <c r="J54" t="n">
-        <v>0.658</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.209</v>
       </c>
       <c r="J55" t="n">
-        <v>0.732</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.22</v>
       </c>
       <c r="J56" t="n">
-        <v>0.587</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="57">
@@ -2758,7 +2758,7 @@
         <v>0.223</v>
       </c>
       <c r="J58" t="n">
-        <v>0.587</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.223</v>
       </c>
       <c r="J59" t="n">
-        <v>0.732</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.101</v>
       </c>
       <c r="J60" t="n">
-        <v>0.024</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="61">
@@ -2918,7 +2918,7 @@
         <v>0.187</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0358</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.187</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0399</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="64">
@@ -2998,7 +2998,7 @@
         <v>0.242</v>
       </c>
       <c r="J64" t="n">
-        <v>0.671</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="65">
@@ -3038,7 +3038,7 @@
         <v>0.242</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0579</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.126</v>
       </c>
       <c r="J66" t="n">
-        <v>0.287</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.126</v>
       </c>
       <c r="J67" t="n">
-        <v>0.283</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.198</v>
       </c>
       <c r="J68" t="n">
-        <v>0.874</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="69">
@@ -3198,7 +3198,7 @@
         <v>0.198</v>
       </c>
       <c r="J69" t="n">
-        <v>0.26</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="70">
@@ -3238,7 +3238,7 @@
         <v>0.097</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0265</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.097</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0241</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.253</v>
       </c>
       <c r="J72" t="n">
-        <v>0.874</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.253</v>
       </c>
       <c r="J73" t="n">
-        <v>0.531</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.111</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0603</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.111</v>
       </c>
       <c r="J75" t="n">
-        <v>0.059</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.265</v>
       </c>
       <c r="J76" t="n">
-        <v>0.874</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.265</v>
       </c>
       <c r="J77" t="n">
-        <v>0.26</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.157</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0186</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.157</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0229</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.183</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0603</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.183</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0819</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.157</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0265</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.157</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0229</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="84">
@@ -3798,7 +3798,7 @@
         <v>0.102</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0186</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="85">
@@ -3838,7 +3838,7 @@
         <v>0.102</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0229</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.0997</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0186</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.0997</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0229</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.104</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0252</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.104</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0229</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="90">
@@ -4078,7 +4078,7 @@
         <v>0.184</v>
       </c>
       <c r="J91" t="n">
-        <v>0.955</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.161</v>
       </c>
       <c r="J92" t="n">
-        <v>0.307</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.161</v>
       </c>
       <c r="J93" t="n">
-        <v>0.411</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.245</v>
       </c>
       <c r="J94" t="n">
-        <v>0.592</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="95">
@@ -4278,7 +4278,7 @@
         <v>0.113</v>
       </c>
       <c r="J96" t="n">
-        <v>0.592</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.113</v>
       </c>
       <c r="J97" t="n">
-        <v>0.411</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.206</v>
       </c>
       <c r="J98" t="n">
-        <v>0.731</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.206</v>
       </c>
       <c r="J99" t="n">
-        <v>0.58</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.153</v>
       </c>
       <c r="J100" t="n">
-        <v>0.592</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.153</v>
       </c>
       <c r="J101" t="n">
-        <v>0.658</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.258</v>
       </c>
       <c r="J102" t="n">
-        <v>0.592</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.258</v>
       </c>
       <c r="J103" t="n">
-        <v>0.98</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.118</v>
       </c>
       <c r="J104" t="n">
-        <v>0.307</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="105">
@@ -4678,7 +4678,7 @@
         <v>0.244</v>
       </c>
       <c r="J106" t="n">
-        <v>0.678</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="107">
@@ -4758,7 +4758,7 @@
         <v>0.118</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0028</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.118</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0147</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="110">
@@ -4838,7 +4838,7 @@
         <v>0.173</v>
       </c>
       <c r="J110" t="n">
-        <v>0.115</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.173</v>
       </c>
       <c r="J111" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.188</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0215</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.188</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0209</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.153</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0507</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.153</v>
       </c>
       <c r="J115" t="n">
-        <v>0.0236</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.16</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0507</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.16</v>
       </c>
       <c r="J117" t="n">
-        <v>0.0725</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0507</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.168</v>
       </c>
       <c r="J119" t="n">
-        <v>0.0725</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.149</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0507</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.149</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0209</v>
+        <v>0.0279</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -5376,7 +5376,7 @@
         <v>0.0775</v>
       </c>
       <c r="I2" t="n">
-        <v>0.31</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="3">
@@ -5413,7 +5413,7 @@
         <v>0.000118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00189</v>
+        <v>0.00177</v>
       </c>
     </row>
     <row r="4">
@@ -5450,7 +5450,7 @@
         <v>0.136</v>
       </c>
       <c r="I4" t="n">
-        <v>0.334</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="5">
@@ -5487,7 +5487,7 @@
         <v>0.498</v>
       </c>
       <c r="I5" t="n">
-        <v>0.664</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="6">
@@ -5524,7 +5524,7 @@
         <v>0.547</v>
       </c>
       <c r="I6" t="n">
-        <v>0.673</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5561,7 +5561,7 @@
         <v>0.0264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.141</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="8">
@@ -5598,7 +5598,7 @@
         <v>0.145</v>
       </c>
       <c r="I8" t="n">
-        <v>0.334</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -5709,7 +5709,7 @@
         <v>0.0256</v>
       </c>
       <c r="I11" t="n">
-        <v>0.141</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="12">
@@ -5746,7 +5746,7 @@
         <v>0.451</v>
       </c>
       <c r="I12" t="n">
-        <v>0.656</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="13">
@@ -5783,7 +5783,7 @@
         <v>0.187</v>
       </c>
       <c r="I13" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5820,7 +5820,7 @@
         <v>0.247</v>
       </c>
       <c r="I14" t="n">
-        <v>0.439</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="15">
@@ -5857,7 +5857,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.792</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="16">
@@ -5894,7 +5894,7 @@
         <v>0.146</v>
       </c>
       <c r="I16" t="n">
-        <v>0.334</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="17">
@@ -5931,7 +5931,7 @@
         <v>0.316</v>
       </c>
       <c r="I17" t="n">
-        <v>0.506</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="18">
@@ -6005,7 +6005,7 @@
         <v>0.000578</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00924</v>
+        <v>0.008670000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -6042,7 +6042,7 @@
         <v>0.092</v>
       </c>
       <c r="I20" t="n">
-        <v>0.48</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="21">
@@ -6079,7 +6079,7 @@
         <v>0.486</v>
       </c>
       <c r="I21" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6153,7 +6153,7 @@
         <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24">
@@ -6190,7 +6190,7 @@
         <v>0.133</v>
       </c>
       <c r="I24" t="n">
-        <v>0.48</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="25">
@@ -6301,7 +6301,7 @@
         <v>0.183</v>
       </c>
       <c r="I27" t="n">
-        <v>0.48</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="28">
@@ -6338,7 +6338,7 @@
         <v>0.694</v>
       </c>
       <c r="I28" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -6375,7 +6375,7 @@
         <v>0.238</v>
       </c>
       <c r="I29" t="n">
-        <v>0.48</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="30">
@@ -6412,7 +6412,7 @@
         <v>0.234</v>
       </c>
       <c r="I30" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -6449,7 +6449,7 @@
         <v>0.0111</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0886</v>
+        <v>0.0185</v>
       </c>
     </row>
     <row r="32">
@@ -6486,7 +6486,7 @@
         <v>0.249</v>
       </c>
       <c r="I32" t="n">
-        <v>0.48</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="33">
@@ -6523,7 +6523,7 @@
         <v>0.509</v>
       </c>
       <c r="I33" t="n">
-        <v>0.74</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -6560,7 +6560,7 @@
         <v>0.0479</v>
       </c>
       <c r="I34" t="n">
-        <v>0.153</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="35">
@@ -6708,7 +6708,7 @@
         <v>0.531</v>
       </c>
       <c r="I38" t="n">
-        <v>0.945</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -6745,7 +6745,7 @@
         <v>0.00238</v>
       </c>
       <c r="I39" t="n">
-        <v>0.019</v>
+        <v>0.00357</v>
       </c>
     </row>
     <row r="40">
@@ -6782,7 +6782,7 @@
         <v>0.009039999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0362</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="41">
@@ -6893,7 +6893,7 @@
         <v>0.0609</v>
       </c>
       <c r="I43" t="n">
-        <v>0.162</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="44">
@@ -6930,7 +6930,7 @@
         <v>0.154</v>
       </c>
       <c r="I44" t="n">
-        <v>0.353</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="45">
@@ -6967,7 +6967,7 @@
         <v>0.00156</v>
       </c>
       <c r="I45" t="n">
-        <v>0.019</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="46">
@@ -7041,7 +7041,7 @@
         <v>0.00535</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0285</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="48">
@@ -7078,7 +7078,7 @@
         <v>0.632</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="49">
@@ -7115,7 +7115,7 @@
         <v>0.494</v>
       </c>
       <c r="I49" t="n">
-        <v>0.945</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7152,7 +7152,7 @@
         <v>0.0491</v>
       </c>
       <c r="I50" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="51">
@@ -7189,7 +7189,7 @@
         <v>0.00106</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0169</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="52">
@@ -7226,7 +7226,7 @@
         <v>0.214</v>
       </c>
       <c r="I52" t="n">
-        <v>0.349</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="53">
@@ -7263,7 +7263,7 @@
         <v>0.492</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="54">
@@ -7300,7 +7300,7 @@
         <v>0.429</v>
       </c>
       <c r="I54" t="n">
-        <v>0.528</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="55">
@@ -7337,7 +7337,7 @@
         <v>0.00377</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0302</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="56">
@@ -7374,7 +7374,7 @@
         <v>0.0603</v>
       </c>
       <c r="I56" t="n">
-        <v>0.161</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="57">
@@ -7485,7 +7485,7 @@
         <v>0.0139</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0743</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="60">
@@ -7522,7 +7522,7 @@
         <v>0.173</v>
       </c>
       <c r="I60" t="n">
-        <v>0.349</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="61">
@@ -7559,7 +7559,7 @@
         <v>0.0412</v>
       </c>
       <c r="I61" t="n">
-        <v>0.157</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="62">
@@ -7596,7 +7596,7 @@
         <v>0.24</v>
       </c>
       <c r="I62" t="n">
-        <v>0.349</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="63">
@@ -7633,7 +7633,7 @@
         <v>0.234</v>
       </c>
       <c r="I63" t="n">
-        <v>0.349</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="64">
@@ -7670,7 +7670,7 @@
         <v>0.179</v>
       </c>
       <c r="I64" t="n">
-        <v>0.349</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="65">
@@ -7707,7 +7707,7 @@
         <v>0.267</v>
       </c>
       <c r="I65" t="n">
-        <v>0.356</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -7781,7 +7781,7 @@
         <v>0.00427</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0342</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="68">
@@ -7818,7 +7818,7 @@
         <v>0.216</v>
       </c>
       <c r="I68" t="n">
-        <v>0.493</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="69">
@@ -7855,7 +7855,7 @@
         <v>2.8e-35</v>
       </c>
       <c r="I69" t="n">
-        <v>4.48e-34</v>
+        <v>2.1e-34</v>
       </c>
     </row>
     <row r="70">
@@ -7892,7 +7892,7 @@
         <v>0.588</v>
       </c>
       <c r="I70" t="n">
-        <v>0.855</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -7929,7 +7929,7 @@
         <v>0.193</v>
       </c>
       <c r="I71" t="n">
-        <v>0.493</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="72">
@@ -8003,7 +8003,7 @@
         <v>0.499</v>
       </c>
       <c r="I73" t="n">
-        <v>0.855</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -8040,7 +8040,7 @@
         <v>0.0645</v>
       </c>
       <c r="I74" t="n">
-        <v>0.344</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="75">
@@ -8077,7 +8077,7 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>0.993</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="76">
@@ -8114,7 +8114,7 @@
         <v>0.549</v>
       </c>
       <c r="I76" t="n">
-        <v>0.855</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="77">
@@ -8151,7 +8151,7 @@
         <v>0.579</v>
       </c>
       <c r="I77" t="n">
-        <v>0.855</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8188,7 +8188,7 @@
         <v>0.122</v>
       </c>
       <c r="I78" t="n">
-        <v>0.39</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="79">
@@ -8225,7 +8225,7 @@
         <v>0.0916</v>
       </c>
       <c r="I79" t="n">
-        <v>0.366</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="80">
@@ -8262,7 +8262,7 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="81">
@@ -8299,7 +8299,7 @@
         <v>0.681</v>
       </c>
       <c r="I81" t="n">
-        <v>0.908</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="82">
@@ -8336,7 +8336,7 @@
         <v>0.112</v>
       </c>
       <c r="I82" t="n">
-        <v>0.189</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="83">
@@ -8373,7 +8373,7 @@
         <v>0.00473</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0151</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="84">
@@ -8410,7 +8410,7 @@
         <v>0.157</v>
       </c>
       <c r="I84" t="n">
-        <v>0.228</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="85">
@@ -8447,7 +8447,7 @@
         <v>8.22e-17</v>
       </c>
       <c r="I85" t="n">
-        <v>1.32e-15</v>
+        <v>6.16e-16</v>
       </c>
     </row>
     <row r="86">
@@ -8484,7 +8484,7 @@
         <v>0.015</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0343</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="87">
@@ -8521,7 +8521,7 @@
         <v>0.00389</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0151</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="88">
@@ -8558,7 +8558,7 @@
         <v>0.000503</v>
       </c>
       <c r="I88" t="n">
-        <v>0.00268</v>
+        <v>0.00641</v>
       </c>
     </row>
     <row r="89">
@@ -8632,7 +8632,7 @@
         <v>0.4</v>
       </c>
       <c r="I90" t="n">
-        <v>0.493</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="91">
@@ -8669,7 +8669,7 @@
         <v>0.365</v>
       </c>
       <c r="I91" t="n">
-        <v>0.487</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="92">
@@ -8706,7 +8706,7 @@
         <v>0.118</v>
       </c>
       <c r="I92" t="n">
-        <v>0.189</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="93">
@@ -8743,7 +8743,7 @@
         <v>0.0129</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0343</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="94">
@@ -8780,7 +8780,7 @@
         <v>0.113</v>
       </c>
       <c r="I94" t="n">
-        <v>0.189</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="95">
@@ -8817,7 +8817,7 @@
         <v>1.57e-05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.000125</v>
+        <v>0.000235</v>
       </c>
     </row>
     <row r="96">
@@ -8854,7 +8854,7 @@
         <v>0.856</v>
       </c>
       <c r="I96" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="97">
@@ -8891,7 +8891,7 @@
         <v>0.836</v>
       </c>
       <c r="I97" t="n">
-        <v>0.914</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -8928,7 +8928,7 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.184</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="99">
@@ -8965,7 +8965,7 @@
         <v>0.234</v>
       </c>
       <c r="I99" t="n">
-        <v>0.416</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="100">
@@ -9039,7 +9039,7 @@
         <v>1.29e-08</v>
       </c>
       <c r="I101" t="n">
-        <v>2.06e-07</v>
+        <v>6.45e-08</v>
       </c>
     </row>
     <row r="102">
@@ -9076,7 +9076,7 @@
         <v>0.681</v>
       </c>
       <c r="I102" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -9113,7 +9113,7 @@
         <v>6.830000000000001e-05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.000364</v>
+        <v>0.000342</v>
       </c>
     </row>
     <row r="104">
@@ -9150,7 +9150,7 @@
         <v>5.04e-05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.000364</v>
+        <v>0.0007560000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -9224,7 +9224,7 @@
         <v>0.00899</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0288</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="107">
@@ -9298,7 +9298,7 @@
         <v>0.0293</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0781</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="109">
@@ -9335,7 +9335,7 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>0.163</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="110">
@@ -9409,7 +9409,7 @@
         <v>0.00177</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00708</v>
+        <v>0.00885</v>
       </c>
     </row>
     <row r="112">
@@ -9483,7 +9483,7 @@
         <v>0.65</v>
       </c>
       <c r="I113" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -9520,7 +9520,7 @@
         <v>0.706</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -9557,7 +9557,7 @@
         <v>0.0343</v>
       </c>
       <c r="I115" t="n">
-        <v>0.137</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="116">
@@ -9594,7 +9594,7 @@
         <v>0.213</v>
       </c>
       <c r="I116" t="n">
-        <v>0.487</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="117">
@@ -9631,7 +9631,7 @@
         <v>4.69e-28</v>
       </c>
       <c r="I117" t="n">
-        <v>7.5e-27</v>
+        <v>3.52e-27</v>
       </c>
     </row>
     <row r="118">
@@ -9668,7 +9668,7 @@
         <v>0.722</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="119">
@@ -9705,7 +9705,7 @@
         <v>0.0223</v>
       </c>
       <c r="I119" t="n">
-        <v>0.119</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="120">
@@ -9742,7 +9742,7 @@
         <v>0.453</v>
       </c>
       <c r="I120" t="n">
-        <v>0.907</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="121">
@@ -9816,7 +9816,7 @@
         <v>0.0147</v>
       </c>
       <c r="I122" t="n">
-        <v>0.117</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="123">
@@ -9853,7 +9853,7 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="124">
@@ -9890,7 +9890,7 @@
         <v>0.132</v>
       </c>
       <c r="I124" t="n">
-        <v>0.352</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="125">
@@ -9964,7 +9964,7 @@
         <v>0.116</v>
       </c>
       <c r="I126" t="n">
-        <v>0.352</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="127">
@@ -10001,7 +10001,7 @@
         <v>0.605</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="128">
@@ -10112,7 +10112,7 @@
         <v>0.414</v>
       </c>
       <c r="I130" t="n">
-        <v>0.737</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -10149,7 +10149,7 @@
         <v>0.01</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0762</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="132">
@@ -10186,7 +10186,7 @@
         <v>0.000489</v>
       </c>
       <c r="I132" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.00733</v>
       </c>
     </row>
     <row r="133">
@@ -10223,7 +10223,7 @@
         <v>0.0143</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0762</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="134">
@@ -10297,7 +10297,7 @@
         <v>0.0425</v>
       </c>
       <c r="I135" t="n">
-        <v>0.136</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="136">
@@ -10334,7 +10334,7 @@
         <v>0.22</v>
       </c>
       <c r="I136" t="n">
-        <v>0.502</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="137">
@@ -10408,7 +10408,7 @@
         <v>0.681</v>
       </c>
       <c r="I138" t="n">
-        <v>0.991</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="139">
@@ -10445,7 +10445,7 @@
         <v>0.0256</v>
       </c>
       <c r="I139" t="n">
-        <v>0.102</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="140">
@@ -10482,7 +10482,7 @@
         <v>0.0576</v>
       </c>
       <c r="I140" t="n">
-        <v>0.154</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="141">
@@ -10630,7 +10630,7 @@
         <v>0.478</v>
       </c>
       <c r="I144" t="n">
-        <v>0.764</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="145">
@@ -10667,7 +10667,7 @@
         <v>0.316</v>
       </c>
       <c r="I145" t="n">
-        <v>0.632</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="146">
@@ -10704,7 +10704,7 @@
         <v>0.244</v>
       </c>
       <c r="I146" t="n">
-        <v>0.507</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="147">
@@ -10741,7 +10741,7 @@
         <v>0.0135</v>
       </c>
       <c r="I147" t="n">
-        <v>0.108</v>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="148">
@@ -10778,7 +10778,7 @@
         <v>0.00338</v>
       </c>
       <c r="I148" t="n">
-        <v>0.054</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="149">
@@ -10815,7 +10815,7 @@
         <v>0.0279</v>
       </c>
       <c r="I149" t="n">
-        <v>0.149</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="150">
@@ -10889,7 +10889,7 @@
         <v>0.154</v>
       </c>
       <c r="I151" t="n">
-        <v>0.412</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="152">
@@ -10926,7 +10926,7 @@
         <v>0.254</v>
       </c>
       <c r="I152" t="n">
-        <v>0.507</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="153">
@@ -11000,7 +11000,7 @@
         <v>0.491</v>
       </c>
       <c r="I154" t="n">
-        <v>0.655</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="155">
@@ -11037,7 +11037,7 @@
         <v>0.33</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="156">
@@ -11111,7 +11111,7 @@
         <v>0.0444</v>
       </c>
       <c r="I157" t="n">
-        <v>0.177</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="158">
@@ -11185,7 +11185,7 @@
         <v>0.0655</v>
       </c>
       <c r="I159" t="n">
-        <v>0.21</v>
+        <v>0.0819</v>
       </c>
     </row>
     <row r="160">
@@ -11222,7 +11222,7 @@
         <v>0.418</v>
       </c>
       <c r="I160" t="n">
-        <v>0.607</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="161">
@@ -11259,7 +11259,7 @@
         <v>0.352</v>
       </c>
       <c r="I161" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -11296,7 +11296,7 @@
         <v>0.663</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="163">
@@ -11333,7 +11333,7 @@
         <v>0.234</v>
       </c>
       <c r="I163" t="n">
-        <v>0.592</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="164">
@@ -11481,7 +11481,7 @@
         <v>0.0011</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0177</v>
+        <v>0.00183</v>
       </c>
     </row>
     <row r="168">
@@ -11518,7 +11518,7 @@
         <v>0.0407</v>
       </c>
       <c r="I168" t="n">
-        <v>0.163</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="169">
@@ -11592,7 +11592,7 @@
         <v>0.769</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="171">
@@ -11629,7 +11629,7 @@
         <v>0.0377</v>
       </c>
       <c r="I171" t="n">
-        <v>0.163</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -11666,7 +11666,7 @@
         <v>0.01</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0804</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="173">
@@ -11703,7 +11703,7 @@
         <v>0.129</v>
       </c>
       <c r="I173" t="n">
-        <v>0.414</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="174">
@@ -11777,7 +11777,7 @@
         <v>0.259</v>
       </c>
       <c r="I175" t="n">
-        <v>0.592</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="176">
@@ -11814,7 +11814,7 @@
         <v>0.507</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="177">
@@ -11888,7 +11888,7 @@
         <v>0.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.64</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="179">
@@ -11925,7 +11925,7 @@
         <v>0.0653</v>
       </c>
       <c r="I179" t="n">
-        <v>0.174</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="180">
@@ -11962,7 +11962,7 @@
         <v>0.00127</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0203</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="181">
@@ -11999,7 +11999,7 @@
         <v>0.0142</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0454</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="182">
@@ -12036,7 +12036,7 @@
         <v>0.703</v>
       </c>
       <c r="I182" t="n">
-        <v>0.75</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="183">
@@ -12073,7 +12073,7 @@
         <v>0.00663</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0418</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="184">
@@ -12110,7 +12110,7 @@
         <v>0.103</v>
       </c>
       <c r="I184" t="n">
-        <v>0.235</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="185">
@@ -12147,7 +12147,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -12184,7 +12184,7 @@
         <v>0.604</v>
       </c>
       <c r="I186" t="n">
-        <v>0.75</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="187">
@@ -12221,7 +12221,7 @@
         <v>0.00872</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0418</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="188">
@@ -12258,7 +12258,7 @@
         <v>0.0104</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0418</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="189">
@@ -12295,7 +12295,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I189" t="n">
-        <v>0.75</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="190">
@@ -12332,7 +12332,7 @@
         <v>0.492</v>
       </c>
       <c r="I190" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -12369,7 +12369,7 @@
         <v>0.695</v>
       </c>
       <c r="I191" t="n">
-        <v>0.75</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="192">
@@ -12406,7 +12406,7 @@
         <v>0.883</v>
       </c>
       <c r="I192" t="n">
-        <v>0.883</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -12443,7 +12443,7 @@
         <v>0.519</v>
       </c>
       <c r="I193" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -12480,7 +12480,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>0.91</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="195">
@@ -12517,7 +12517,7 @@
         <v>0.01</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0762</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="196">
@@ -12554,7 +12554,7 @@
         <v>0.499</v>
       </c>
       <c r="I196" t="n">
-        <v>0.799</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -12591,7 +12591,7 @@
         <v>4.07e-31</v>
       </c>
       <c r="I197" t="n">
-        <v>6.509999999999999e-30</v>
+        <v>2.03e-30</v>
       </c>
     </row>
     <row r="198">
@@ -12628,7 +12628,7 @@
         <v>0.853</v>
       </c>
       <c r="I198" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -12665,7 +12665,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>0.263</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="200">
@@ -12702,7 +12702,7 @@
         <v>0.85</v>
       </c>
       <c r="I200" t="n">
-        <v>0.91</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="201">
@@ -12776,7 +12776,7 @@
         <v>0.681</v>
       </c>
       <c r="I202" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="203">
@@ -12813,7 +12813,7 @@
         <v>0.0893</v>
       </c>
       <c r="I203" t="n">
-        <v>0.286</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="204">
@@ -12850,7 +12850,7 @@
         <v>0.164</v>
       </c>
       <c r="I204" t="n">
-        <v>0.328</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="205">
@@ -12887,7 +12887,7 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -12924,7 +12924,7 @@
         <v>0.0143</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0762</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="207">
@@ -12961,7 +12961,7 @@
         <v>0.225</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="208">
@@ -12998,7 +12998,7 @@
         <v>0.146</v>
       </c>
       <c r="I208" t="n">
-        <v>0.328</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="209">
@@ -13035,7 +13035,7 @@
         <v>0.146</v>
       </c>
       <c r="I209" t="n">
-        <v>0.328</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="210">
@@ -13072,7 +13072,7 @@
         <v>0.287</v>
       </c>
       <c r="I210" t="n">
-        <v>0.418</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="211">
@@ -13109,7 +13109,7 @@
         <v>0.0135</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0538</v>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="212">
@@ -13146,7 +13146,7 @@
         <v>0.665</v>
       </c>
       <c r="I212" t="n">
-        <v>0.742</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="213">
@@ -13183,7 +13183,7 @@
         <v>2.05e-14</v>
       </c>
       <c r="I213" t="n">
-        <v>3.28e-13</v>
+        <v>7.690000000000001e-14</v>
       </c>
     </row>
     <row r="214">
@@ -13220,7 +13220,7 @@
         <v>0.121</v>
       </c>
       <c r="I214" t="n">
-        <v>0.242</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="215">
@@ -13257,7 +13257,7 @@
         <v>0.0131</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0538</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="216">
@@ -13294,7 +13294,7 @@
         <v>0.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0641</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -13368,7 +13368,7 @@
         <v>0.622</v>
       </c>
       <c r="I218" t="n">
-        <v>0.742</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="219">
@@ -13405,7 +13405,7 @@
         <v>0.343</v>
       </c>
       <c r="I219" t="n">
-        <v>0.458</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="220">
@@ -13442,7 +13442,7 @@
         <v>0.695</v>
       </c>
       <c r="I220" t="n">
-        <v>0.742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -13479,7 +13479,7 @@
         <v>0.0421</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0963</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="222">
@@ -13516,7 +13516,7 @@
         <v>0.0268</v>
       </c>
       <c r="I222" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="223">
@@ -13553,7 +13553,7 @@
         <v>0.000354</v>
       </c>
       <c r="I223" t="n">
-        <v>0.00284</v>
+        <v>0.00106</v>
       </c>
     </row>
     <row r="224">
@@ -13590,7 +13590,7 @@
         <v>0.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.248</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="225">
@@ -13627,7 +13627,7 @@
         <v>0.251</v>
       </c>
       <c r="I225" t="n">
-        <v>0.401</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -13664,7 +13664,7 @@
         <v>0.158</v>
       </c>
       <c r="I226" t="n">
-        <v>0.387</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="227">
@@ -13701,7 +13701,7 @@
         <v>0.234</v>
       </c>
       <c r="I227" t="n">
-        <v>0.416</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="228">
@@ -13775,7 +13775,7 @@
         <v>1.75e-06</v>
       </c>
       <c r="I229" t="n">
-        <v>2.81e-05</v>
+        <v>6.56e-06</v>
       </c>
     </row>
     <row r="230">
@@ -13849,7 +13849,7 @@
         <v>2.21e-05</v>
       </c>
       <c r="I231" t="n">
-        <v>0.000177</v>
+        <v>0.000166</v>
       </c>
     </row>
     <row r="232">
@@ -13886,7 +13886,7 @@
         <v>0.0407</v>
       </c>
       <c r="I232" t="n">
-        <v>0.163</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="233">
@@ -13960,7 +13960,7 @@
         <v>0.461</v>
       </c>
       <c r="I234" t="n">
-        <v>0.737</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="235">
@@ -13997,7 +13997,7 @@
         <v>0.147</v>
       </c>
       <c r="I235" t="n">
-        <v>0.387</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="236">
@@ -14034,7 +14034,7 @@
         <v>0.0293</v>
       </c>
       <c r="I236" t="n">
-        <v>0.156</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="237">
@@ -14071,7 +14071,7 @@
         <v>0.214</v>
       </c>
       <c r="I237" t="n">
-        <v>0.416</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="238">
@@ -14145,7 +14145,7 @@
         <v>0.169</v>
       </c>
       <c r="I239" t="n">
-        <v>0.387</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="240">
@@ -14182,7 +14182,7 @@
         <v>0.656</v>
       </c>
       <c r="I240" t="n">
-        <v>0.874</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="241">
@@ -14219,7 +14219,7 @@
         <v>0.65</v>
       </c>
       <c r="I241" t="n">
-        <v>0.874</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -14256,7 +14256,7 @@
         <v>0.442</v>
       </c>
       <c r="I242" t="n">
-        <v>0.645</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="243">
@@ -14293,7 +14293,7 @@
         <v>0.0653</v>
       </c>
       <c r="I243" t="n">
-        <v>0.174</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="244">
@@ -14330,7 +14330,7 @@
         <v>0.484</v>
       </c>
       <c r="I244" t="n">
-        <v>0.645</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="245">
@@ -14367,7 +14367,7 @@
         <v>5.54e-23</v>
       </c>
       <c r="I245" t="n">
-        <v>8.870000000000001e-22</v>
+        <v>2.08e-22</v>
       </c>
     </row>
     <row r="246">
@@ -14404,7 +14404,7 @@
         <v>0.856</v>
       </c>
       <c r="I246" t="n">
-        <v>0.914</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="247">
@@ -14441,7 +14441,7 @@
         <v>0.00451</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0361</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="248">
@@ -14478,7 +14478,7 @@
         <v>0.451</v>
       </c>
       <c r="I248" t="n">
-        <v>0.645</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="249">
@@ -14515,7 +14515,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>0.681</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -14552,7 +14552,7 @@
         <v>0.44</v>
       </c>
       <c r="I250" t="n">
-        <v>0.645</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="251">
@@ -14589,7 +14589,7 @@
         <v>0.0547</v>
       </c>
       <c r="I251" t="n">
-        <v>0.174</v>
+        <v>0.0912</v>
       </c>
     </row>
     <row r="252">
@@ -14626,7 +14626,7 @@
         <v>0.0419</v>
       </c>
       <c r="I252" t="n">
-        <v>0.167</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="253">
@@ -14700,7 +14700,7 @@
         <v>0.0127</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0675</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="255">
@@ -14737,7 +14737,7 @@
         <v>0.596</v>
       </c>
       <c r="I255" t="n">
-        <v>0.681</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="256">
@@ -14774,7 +14774,7 @@
         <v>0.448</v>
       </c>
       <c r="I256" t="n">
-        <v>0.645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -14811,7 +14811,7 @@
         <v>0.196</v>
       </c>
       <c r="I257" t="n">
-        <v>0.449</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="258">
@@ -14848,7 +14848,7 @@
         <v>0.846</v>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="259">
@@ -14885,7 +14885,7 @@
         <v>0.0209</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0834</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="260">
@@ -14922,7 +14922,7 @@
         <v>0.009860000000000001</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0526</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="261">
@@ -14996,7 +14996,7 @@
         <v>0.377</v>
       </c>
       <c r="I262" t="n">
-        <v>0.754</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -15033,7 +15033,7 @@
         <v>0.0975</v>
       </c>
       <c r="I263" t="n">
-        <v>0.26</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="264">
@@ -15070,7 +15070,7 @@
         <v>0.85</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="265">
@@ -15144,7 +15144,7 @@
         <v>0.0454</v>
       </c>
       <c r="I266" t="n">
-        <v>0.145</v>
+        <v>0.0973</v>
       </c>
     </row>
     <row r="267">
@@ -15181,7 +15181,7 @@
         <v>0.634</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="268">
@@ -15218,7 +15218,7 @@
         <v>0.363</v>
       </c>
       <c r="I268" t="n">
-        <v>0.754</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="269">
@@ -15329,7 +15329,7 @@
         <v>0.715</v>
       </c>
       <c r="I271" t="n">
-        <v>1</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="272">
@@ -15366,7 +15366,7 @@
         <v>8.98e-05</v>
       </c>
       <c r="I272" t="n">
-        <v>0.000719</v>
+        <v>0.000674</v>
       </c>
     </row>
     <row r="273">
@@ -15403,7 +15403,7 @@
         <v>1.85e-07</v>
       </c>
       <c r="I273" t="n">
-        <v>2.96e-06</v>
+        <v>2.78e-06</v>
       </c>
     </row>
     <row r="274">
@@ -15440,7 +15440,7 @@
         <v>0.496</v>
       </c>
       <c r="I274" t="n">
-        <v>0.662</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="275">
@@ -15477,7 +15477,7 @@
         <v>0.0386</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0953</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15514,7 +15514,7 @@
         <v>0.0255</v>
       </c>
       <c r="I276" t="n">
-        <v>0.0953</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="277">
@@ -15588,7 +15588,7 @@
         <v>0.0286</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0953</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="279">
@@ -15625,7 +15625,7 @@
         <v>0.0417</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0953</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="280">
@@ -15662,7 +15662,7 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>0.128</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="281">
@@ -15736,7 +15736,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I282" t="n">
-        <v>0.154</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="283">
@@ -15810,7 +15810,7 @@
         <v>0.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.48</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="285">
@@ -15847,7 +15847,7 @@
         <v>0.375</v>
       </c>
       <c r="I285" t="n">
-        <v>0.545</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="286">
@@ -15921,7 +15921,7 @@
         <v>0.009140000000000001</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0953</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="288">
@@ -15958,7 +15958,7 @@
         <v>0.034</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0953</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="289">
@@ -15995,7 +15995,7 @@
         <v>0.012</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0953</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="290">
@@ -16069,7 +16069,7 @@
         <v>0.489</v>
       </c>
       <c r="I291" t="n">
-        <v>0.87</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="292">
@@ -16217,7 +16217,7 @@
         <v>0.0011</v>
       </c>
       <c r="I295" t="n">
-        <v>0.008840000000000001</v>
+        <v>0.00183</v>
       </c>
     </row>
     <row r="296">
@@ -16254,7 +16254,7 @@
         <v>0.195</v>
       </c>
       <c r="I296" t="n">
-        <v>0.624</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="297">
@@ -16328,7 +16328,7 @@
         <v>0.00099</v>
       </c>
       <c r="I298" t="n">
-        <v>0.008840000000000001</v>
+        <v>0.00297</v>
       </c>
     </row>
     <row r="299">
@@ -16365,7 +16365,7 @@
         <v>0.601</v>
       </c>
       <c r="I299" t="n">
-        <v>0.961</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="300">
@@ -16402,7 +16402,7 @@
         <v>0.047</v>
       </c>
       <c r="I300" t="n">
-        <v>0.25</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -16439,7 +16439,7 @@
         <v>0.328</v>
       </c>
       <c r="I301" t="n">
-        <v>0.718</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="302">
@@ -16513,7 +16513,7 @@
         <v>0.259</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="304">
@@ -16550,7 +16550,7 @@
         <v>0.0645</v>
       </c>
       <c r="I304" t="n">
-        <v>0.258</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="305">
@@ -16587,7 +16587,7 @@
         <v>0.359</v>
       </c>
       <c r="I305" t="n">
-        <v>0.718</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -16624,7 +16624,7 @@
         <v>0.847</v>
       </c>
       <c r="I306" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="307">
@@ -16661,7 +16661,7 @@
         <v>0.0736</v>
       </c>
       <c r="I307" t="n">
-        <v>0.235</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="308">
@@ -16698,7 +16698,7 @@
         <v>0.0149</v>
       </c>
       <c r="I308" t="n">
-        <v>0.0794</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="309">
@@ -16772,7 +16772,7 @@
         <v>0.388</v>
       </c>
       <c r="I310" t="n">
-        <v>0.76</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="311">
@@ -16809,7 +16809,7 @@
         <v>0.0131</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0794</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="312">
@@ -16846,7 +16846,7 @@
         <v>0.57</v>
       </c>
       <c r="I312" t="n">
-        <v>0.76</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="313">
@@ -16883,7 +16883,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I313" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -16920,7 +16920,7 @@
         <v>0.00637</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0794</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="315">
@@ -16957,7 +16957,7 @@
         <v>0.479</v>
       </c>
       <c r="I315" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -16994,7 +16994,7 @@
         <v>0.0936</v>
       </c>
       <c r="I316" t="n">
-        <v>0.25</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="317">
@@ -17031,7 +17031,7 @@
         <v>0.532</v>
       </c>
       <c r="I317" t="n">
-        <v>0.76</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="318">
@@ -17142,7 +17142,7 @@
         <v>0.159</v>
       </c>
       <c r="I320" t="n">
-        <v>0.362</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="321">
@@ -17179,7 +17179,7 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>0.235</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="322">
@@ -17253,7 +17253,7 @@
         <v>0.112</v>
       </c>
       <c r="I323" t="n">
-        <v>0.597</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="324">
@@ -17327,7 +17327,7 @@
         <v>1.49e-30</v>
       </c>
       <c r="I325" t="n">
-        <v>2.39e-29</v>
+        <v>5.59e-30</v>
       </c>
     </row>
     <row r="326">
@@ -17364,7 +17364,7 @@
         <v>0.715</v>
       </c>
       <c r="I326" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -17401,7 +17401,7 @@
         <v>0.0975</v>
       </c>
       <c r="I327" t="n">
-        <v>0.597</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="328">
@@ -17438,7 +17438,7 @@
         <v>0.701</v>
       </c>
       <c r="I328" t="n">
-        <v>0.888</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="329">
@@ -17475,7 +17475,7 @@
         <v>0.722</v>
       </c>
       <c r="I329" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -17512,7 +17512,7 @@
         <v>0.208</v>
       </c>
       <c r="I330" t="n">
-        <v>0.666</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="331">
@@ -17549,7 +17549,7 @@
         <v>0.263</v>
       </c>
       <c r="I331" t="n">
-        <v>0.702</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="332">
@@ -17586,7 +17586,7 @@
         <v>0.451</v>
       </c>
       <c r="I332" t="n">
-        <v>0.797</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="333">
@@ -17623,7 +17623,7 @@
         <v>0.161</v>
       </c>
       <c r="I333" t="n">
-        <v>0.644</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -17660,7 +17660,7 @@
         <v>0.498</v>
       </c>
       <c r="I334" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -17697,7 +17697,7 @@
         <v>0.475</v>
       </c>
       <c r="I335" t="n">
-        <v>0.797</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="336">
@@ -17734,7 +17734,7 @@
         <v>0.392</v>
       </c>
       <c r="I336" t="n">
-        <v>0.797</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="337">
@@ -17808,7 +17808,7 @@
         <v>0.445</v>
       </c>
       <c r="I338" t="n">
-        <v>0.713</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="339">
@@ -17845,7 +17845,7 @@
         <v>0.0675</v>
       </c>
       <c r="I339" t="n">
-        <v>0.18</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="340">
@@ -17919,7 +17919,7 @@
         <v>4.39e-16</v>
       </c>
       <c r="I341" t="n">
-        <v>7.02e-15</v>
+        <v>2.19e-15</v>
       </c>
     </row>
     <row r="342">
@@ -17956,7 +17956,7 @@
         <v>0.12</v>
       </c>
       <c r="I342" t="n">
-        <v>0.248</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="343">
@@ -17993,7 +17993,7 @@
         <v>0.0231</v>
       </c>
       <c r="I343" t="n">
-        <v>0.074</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="344">
@@ -18030,7 +18030,7 @@
         <v>0.0201</v>
       </c>
       <c r="I344" t="n">
-        <v>0.074</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="345">
@@ -18104,7 +18104,7 @@
         <v>0.628</v>
       </c>
       <c r="I346" t="n">
-        <v>0.914</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="347">
@@ -18178,7 +18178,7 @@
         <v>0.124</v>
       </c>
       <c r="I348" t="n">
-        <v>0.248</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="349">
@@ -18215,7 +18215,7 @@
         <v>0.00192</v>
       </c>
       <c r="I349" t="n">
-        <v>0.0103</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="350">
@@ -18289,7 +18289,7 @@
         <v>0.000227</v>
       </c>
       <c r="I351" t="n">
-        <v>0.00182</v>
+        <v>0.00106</v>
       </c>
     </row>
     <row r="352">
@@ -18326,7 +18326,7 @@
         <v>0.432</v>
       </c>
       <c r="I352" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="353">
@@ -18400,7 +18400,7 @@
         <v>0.506</v>
       </c>
       <c r="I354" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="355">
@@ -18437,7 +18437,7 @@
         <v>0.0496</v>
       </c>
       <c r="I355" t="n">
-        <v>0.132</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="356">
@@ -18511,7 +18511,7 @@
         <v>1.29e-08</v>
       </c>
       <c r="I357" t="n">
-        <v>2.06e-07</v>
+        <v>6.45e-08</v>
       </c>
     </row>
     <row r="358">
@@ -18585,7 +18585,7 @@
         <v>0.000477</v>
       </c>
       <c r="I359" t="n">
-        <v>0.00381</v>
+        <v>0.00102</v>
       </c>
     </row>
     <row r="360">
@@ -18622,7 +18622,7 @@
         <v>0.0203</v>
       </c>
       <c r="I360" t="n">
-        <v>0.065</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="361">
@@ -18696,7 +18696,7 @@
         <v>0.0987</v>
       </c>
       <c r="I362" t="n">
-        <v>0.226</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="363">
@@ -18733,7 +18733,7 @@
         <v>0.219</v>
       </c>
       <c r="I363" t="n">
-        <v>0.388</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="364">
@@ -18770,7 +18770,7 @@
         <v>0.01</v>
       </c>
       <c r="I364" t="n">
-        <v>0.0402</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="365">
@@ -18807,7 +18807,7 @@
         <v>0.129</v>
       </c>
       <c r="I365" t="n">
-        <v>0.259</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="366">
@@ -18881,7 +18881,7 @@
         <v>0.00177</v>
       </c>
       <c r="I367" t="n">
-        <v>0.00944</v>
+        <v>0.00885</v>
       </c>
     </row>
     <row r="368">
@@ -18992,7 +18992,7 @@
         <v>0.85</v>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="371">
@@ -19029,7 +19029,7 @@
         <v>0.392</v>
       </c>
       <c r="I371" t="n">
-        <v>0.896</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="372">
@@ -19103,7 +19103,7 @@
         <v>6.09e-27</v>
       </c>
       <c r="I373" t="n">
-        <v>9.74e-26</v>
+        <v>3.04e-26</v>
       </c>
     </row>
     <row r="374">
@@ -19140,7 +19140,7 @@
         <v>0.72</v>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="375">
@@ -19177,7 +19177,7 @@
         <v>0.0127</v>
       </c>
       <c r="I375" t="n">
-        <v>0.102</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="376">
@@ -19214,7 +19214,7 @@
         <v>0.339</v>
       </c>
       <c r="I376" t="n">
-        <v>0.896</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="377">
@@ -19288,7 +19288,7 @@
         <v>0.0853</v>
       </c>
       <c r="I378" t="n">
-        <v>0.376</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="379">
@@ -19325,7 +19325,7 @@
         <v>0.177</v>
       </c>
       <c r="I379" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="380">
@@ -19362,7 +19362,7 @@
         <v>0.0941</v>
       </c>
       <c r="I380" t="n">
-        <v>0.376</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="381">
@@ -19399,7 +19399,7 @@
         <v>0.581</v>
       </c>
       <c r="I381" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="382">
@@ -19436,7 +19436,7 @@
         <v>0.492</v>
       </c>
       <c r="I382" t="n">
-        <v>0.984</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -19584,7 +19584,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I386" t="n">
-        <v>1</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="387">
@@ -19621,7 +19621,7 @@
         <v>0.000489</v>
       </c>
       <c r="I387" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.00367</v>
       </c>
     </row>
     <row r="388">
@@ -19658,7 +19658,7 @@
         <v>0.0835</v>
       </c>
       <c r="I388" t="n">
-        <v>0.191</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="389">
@@ -19695,7 +19695,7 @@
         <v>0.0293</v>
       </c>
       <c r="I389" t="n">
-        <v>0.136</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="390">
@@ -19769,7 +19769,7 @@
         <v>0.00231</v>
       </c>
       <c r="I391" t="n">
-        <v>0.0185</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="392">
@@ -19806,7 +19806,7 @@
         <v>0.0509</v>
       </c>
       <c r="I392" t="n">
-        <v>0.136</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="393">
@@ -19880,7 +19880,7 @@
         <v>0.0454</v>
       </c>
       <c r="I394" t="n">
-        <v>0.136</v>
+        <v>0.0973</v>
       </c>
     </row>
     <row r="395">
@@ -19917,7 +19917,7 @@
         <v>0.0395</v>
       </c>
       <c r="I395" t="n">
-        <v>0.136</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="396">
@@ -19954,7 +19954,7 @@
         <v>0.219</v>
       </c>
       <c r="I396" t="n">
-        <v>0.389</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="397">
@@ -20065,7 +20065,7 @@
         <v>0.853</v>
       </c>
       <c r="I399" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="400">
@@ -20102,7 +20102,7 @@
         <v>0.146</v>
       </c>
       <c r="I400" t="n">
-        <v>0.292</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="401">
@@ -20139,7 +20139,7 @@
         <v>0.673</v>
       </c>
       <c r="I401" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="402">
@@ -20176,7 +20176,7 @@
         <v>0.496</v>
       </c>
       <c r="I402" t="n">
-        <v>0.826</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="403">
@@ -20213,7 +20213,7 @@
         <v>0.0023</v>
       </c>
       <c r="I403" t="n">
-        <v>0.0367</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="404">
@@ -20250,7 +20250,7 @@
         <v>0.243</v>
       </c>
       <c r="I404" t="n">
-        <v>0.647</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="405">
@@ -20287,7 +20287,7 @@
         <v>0.0304</v>
       </c>
       <c r="I405" t="n">
-        <v>0.162</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="406">
@@ -20361,7 +20361,7 @@
         <v>0.516</v>
       </c>
       <c r="I407" t="n">
-        <v>0.826</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="408">
@@ -20509,7 +20509,7 @@
         <v>0.105</v>
       </c>
       <c r="I411" t="n">
-        <v>0.337</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="412">
@@ -20546,7 +20546,7 @@
         <v>0.307</v>
       </c>
       <c r="I412" t="n">
-        <v>0.671</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="413">
@@ -20583,7 +20583,7 @@
         <v>0.07489999999999999</v>
       </c>
       <c r="I413" t="n">
-        <v>0.3</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="414">
@@ -20657,7 +20657,7 @@
         <v>0.009350000000000001</v>
       </c>
       <c r="I415" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="416">
@@ -20694,7 +20694,7 @@
         <v>0.335</v>
       </c>
       <c r="I416" t="n">
-        <v>0.671</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="417">
@@ -20731,7 +20731,7 @@
         <v>0.827</v>
       </c>
       <c r="I417" t="n">
-        <v>1</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="418">
@@ -20842,7 +20842,7 @@
         <v>0.343</v>
       </c>
       <c r="I420" t="n">
-        <v>0.6870000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -20953,7 +20953,7 @@
         <v>0.000189</v>
       </c>
       <c r="I423" t="n">
-        <v>0.00303</v>
+        <v>0.000473</v>
       </c>
     </row>
     <row r="424">
@@ -20990,7 +20990,7 @@
         <v>0.0203</v>
       </c>
       <c r="I424" t="n">
-        <v>0.0892</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="425">
@@ -21064,7 +21064,7 @@
         <v>0.0223</v>
       </c>
       <c r="I426" t="n">
-        <v>0.0892</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="427">
@@ -21101,7 +21101,7 @@
         <v>0.147</v>
       </c>
       <c r="I427" t="n">
-        <v>0.387</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="428">
@@ -21138,7 +21138,7 @@
         <v>0.01</v>
       </c>
       <c r="I428" t="n">
-        <v>0.0804</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="429">
@@ -21175,7 +21175,7 @@
         <v>0.129</v>
       </c>
       <c r="I429" t="n">
-        <v>0.387</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="430">
@@ -21249,7 +21249,7 @@
         <v>0.169</v>
       </c>
       <c r="I431" t="n">
-        <v>0.387</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="432">
@@ -21286,7 +21286,7 @@
         <v>0.465</v>
       </c>
       <c r="I432" t="n">
-        <v>0.827</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="433">
@@ -21360,7 +21360,7 @@
         <v>0.696</v>
       </c>
       <c r="I434" t="n">
-        <v>0.882</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="435">
@@ -21397,7 +21397,7 @@
         <v>0.00334</v>
       </c>
       <c r="I435" t="n">
-        <v>0.0267</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="436">
@@ -21434,7 +21434,7 @@
         <v>0.06850000000000001</v>
       </c>
       <c r="I436" t="n">
-        <v>0.137</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="437">
@@ -21471,7 +21471,7 @@
         <v>0.028</v>
       </c>
       <c r="I437" t="n">
-        <v>0.0746</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="438">
@@ -21508,7 +21508,7 @@
         <v>0.717</v>
       </c>
       <c r="I438" t="n">
-        <v>0.882</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="439">
@@ -21545,7 +21545,7 @@
         <v>0.000178</v>
       </c>
       <c r="I439" t="n">
-        <v>0.00284</v>
+        <v>0.00133</v>
       </c>
     </row>
     <row r="440">
@@ -21582,7 +21582,7 @@
         <v>0.0182</v>
       </c>
       <c r="I440" t="n">
-        <v>0.073</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="441">
@@ -21656,7 +21656,7 @@
         <v>0.0141</v>
       </c>
       <c r="I442" t="n">
-        <v>0.073</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="443">
@@ -21693,7 +21693,7 @@
         <v>0.0235</v>
       </c>
       <c r="I443" t="n">
-        <v>0.0746</v>
+        <v>0.0441</v>
       </c>
     </row>
     <row r="444">
@@ -21730,7 +21730,7 @@
         <v>0.0434</v>
       </c>
       <c r="I444" t="n">
-        <v>0.0993</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="445">
@@ -21767,7 +21767,7 @@
         <v>0.6840000000000001</v>
       </c>
       <c r="I445" t="n">
-        <v>0.882</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="446">
@@ -21878,7 +21878,7 @@
         <v>0.139</v>
       </c>
       <c r="I448" t="n">
-        <v>0.246</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="449">
@@ -21915,7 +21915,7 @@
         <v>0.637</v>
       </c>
       <c r="I449" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -21952,7 +21952,7 @@
         <v>0.846</v>
       </c>
       <c r="I450" t="n">
-        <v>1</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="451">
@@ -21989,7 +21989,7 @@
         <v>0.0688</v>
       </c>
       <c r="I451" t="n">
-        <v>0.275</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="452">
@@ -22026,7 +22026,7 @@
         <v>0.499</v>
       </c>
       <c r="I452" t="n">
-        <v>0.799</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -22063,7 +22063,7 @@
         <v>3.44e-37</v>
       </c>
       <c r="I453" t="n">
-        <v>5.51e-36</v>
+        <v>5.16e-36</v>
       </c>
     </row>
     <row r="454">
@@ -22100,7 +22100,7 @@
         <v>0.294</v>
       </c>
       <c r="I454" t="n">
-        <v>0.671</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -22137,7 +22137,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I455" t="n">
-        <v>0.275</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="456">
@@ -22248,7 +22248,7 @@
         <v>0.0893</v>
       </c>
       <c r="I458" t="n">
-        <v>0.286</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="459">
@@ -22285,7 +22285,7 @@
         <v>0.484</v>
       </c>
       <c r="I459" t="n">
-        <v>0.799</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="460">
@@ -22322,7 +22322,7 @@
         <v>0.0381</v>
       </c>
       <c r="I460" t="n">
-        <v>0.275</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="461">
@@ -22396,7 +22396,7 @@
         <v>0.247</v>
       </c>
       <c r="I462" t="n">
-        <v>0.658</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="463">
@@ -22470,7 +22470,7 @@
         <v>0.779</v>
       </c>
       <c r="I464" t="n">
-        <v>1</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="465">
@@ -22507,7 +22507,7 @@
         <v>0.478</v>
       </c>
       <c r="I465" t="n">
-        <v>0.799</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="466">
@@ -22544,7 +22544,7 @@
         <v>0.0674</v>
       </c>
       <c r="I466" t="n">
-        <v>0.153</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="467">
@@ -22581,7 +22581,7 @@
         <v>0.0765</v>
       </c>
       <c r="I467" t="n">
-        <v>0.153</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="468">
@@ -22618,7 +22618,7 @@
         <v>0.423</v>
       </c>
       <c r="I468" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="469">
@@ -22655,7 +22655,7 @@
         <v>4.59e-17</v>
       </c>
       <c r="I469" t="n">
-        <v>7.34e-16</v>
+        <v>6.16e-16</v>
       </c>
     </row>
     <row r="470">
@@ -22692,7 +22692,7 @@
         <v>0.0283</v>
       </c>
       <c r="I470" t="n">
-        <v>0.0755</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="471">
@@ -22729,7 +22729,7 @@
         <v>0.0131</v>
       </c>
       <c r="I471" t="n">
-        <v>0.0419</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="472">
@@ -22766,7 +22766,7 @@
         <v>0.000854</v>
       </c>
       <c r="I472" t="n">
-        <v>0.00683</v>
+        <v>0.00641</v>
       </c>
     </row>
     <row r="473">
@@ -22840,7 +22840,7 @@
         <v>0.239</v>
       </c>
       <c r="I474" t="n">
-        <v>0.382</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="475">
@@ -22877,7 +22877,7 @@
         <v>0.207</v>
       </c>
       <c r="I475" t="n">
-        <v>0.369</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="476">
@@ -22914,7 +22914,7 @@
         <v>0.314</v>
       </c>
       <c r="I476" t="n">
-        <v>0.456</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="477">
@@ -22951,7 +22951,7 @@
         <v>0.00831</v>
       </c>
       <c r="I477" t="n">
-        <v>0.0332</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="478">
@@ -23025,7 +23025,7 @@
         <v>0.00184</v>
       </c>
       <c r="I479" t="n">
-        <v>0.00979</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="480">
@@ -23062,7 +23062,7 @@
         <v>0.698</v>
       </c>
       <c r="I480" t="n">
-        <v>0.797</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="481">
@@ -23099,7 +23099,7 @@
         <v>0.513</v>
       </c>
       <c r="I481" t="n">
-        <v>0.631</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="482">
@@ -23136,7 +23136,7 @@
         <v>0.0219</v>
       </c>
       <c r="I482" t="n">
-        <v>0.0439</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="483">
@@ -23173,7 +23173,7 @@
         <v>0.234</v>
       </c>
       <c r="I483" t="n">
-        <v>0.374</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="484">
@@ -23247,7 +23247,7 @@
         <v>1.29e-08</v>
       </c>
       <c r="I485" t="n">
-        <v>2.06e-07</v>
+        <v>6.45e-08</v>
       </c>
     </row>
     <row r="486">
@@ -23321,7 +23321,7 @@
         <v>2.21e-05</v>
       </c>
       <c r="I487" t="n">
-        <v>0.000177</v>
+        <v>0.000166</v>
       </c>
     </row>
     <row r="488">
@@ -23358,7 +23358,7 @@
         <v>0.000285</v>
       </c>
       <c r="I488" t="n">
-        <v>0.00114</v>
+        <v>0.00214</v>
       </c>
     </row>
     <row r="489">
@@ -23432,7 +23432,7 @@
         <v>0.00899</v>
       </c>
       <c r="I490" t="n">
-        <v>0.0205</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="491">
@@ -23506,7 +23506,7 @@
         <v>0.000275</v>
       </c>
       <c r="I492" t="n">
-        <v>0.00114</v>
+        <v>0.00138</v>
       </c>
     </row>
     <row r="493">
@@ -23543,7 +23543,7 @@
         <v>0.00156</v>
       </c>
       <c r="I493" t="n">
-        <v>0.00416</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="494">
@@ -23580,7 +23580,7 @@
         <v>0.226</v>
       </c>
       <c r="I494" t="n">
-        <v>0.374</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -23617,7 +23617,7 @@
         <v>0.000461</v>
       </c>
       <c r="I495" t="n">
-        <v>0.00147</v>
+        <v>0.00692</v>
       </c>
     </row>
     <row r="496">
@@ -23654,7 +23654,7 @@
         <v>0.656</v>
       </c>
       <c r="I496" t="n">
-        <v>0.954</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="497">
@@ -23728,7 +23728,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="I498" t="n">
-        <v>0.695</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="499">
@@ -23765,7 +23765,7 @@
         <v>0.197</v>
       </c>
       <c r="I499" t="n">
-        <v>0.525</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="500">
@@ -23802,7 +23802,7 @@
         <v>0.487</v>
       </c>
       <c r="I500" t="n">
-        <v>0.649</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="501">
@@ -23839,7 +23839,7 @@
         <v>1.89e-28</v>
       </c>
       <c r="I501" t="n">
-        <v>3.03e-27</v>
+        <v>2.84e-27</v>
       </c>
     </row>
     <row r="502">
@@ -23876,7 +23876,7 @@
         <v>0.304</v>
       </c>
       <c r="I502" t="n">
-        <v>0.649</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="503">
@@ -23913,7 +23913,7 @@
         <v>0.00451</v>
       </c>
       <c r="I503" t="n">
-        <v>0.024</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="504">
@@ -23950,7 +23950,7 @@
         <v>0.454</v>
       </c>
       <c r="I504" t="n">
-        <v>0.649</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="505">
@@ -24024,7 +24024,7 @@
         <v>0.0218</v>
       </c>
       <c r="I506" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="507">
@@ -24061,7 +24061,7 @@
         <v>0.485</v>
       </c>
       <c r="I507" t="n">
-        <v>0.649</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="508">
@@ -24098,7 +24098,7 @@
         <v>0.00228</v>
       </c>
       <c r="I508" t="n">
-        <v>0.0182</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="509">
@@ -24135,7 +24135,7 @@
         <v>0.697</v>
       </c>
       <c r="I509" t="n">
-        <v>0.796</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="510">
@@ -24172,7 +24172,7 @@
         <v>0.102</v>
       </c>
       <c r="I510" t="n">
-        <v>0.325</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="511">
@@ -24209,7 +24209,7 @@
         <v>0.333</v>
       </c>
       <c r="I511" t="n">
-        <v>0.649</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="512">
@@ -24283,7 +24283,7 @@
         <v>0.432</v>
       </c>
       <c r="I513" t="n">
-        <v>0.649</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -24320,7 +24320,7 @@
         <v>0.131</v>
       </c>
       <c r="I514" t="n">
-        <v>0.299</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="515">
@@ -24357,7 +24357,7 @@
         <v>0.00158</v>
       </c>
       <c r="I515" t="n">
-        <v>0.00844</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="516">
@@ -24505,7 +24505,7 @@
         <v>0.00231</v>
       </c>
       <c r="I519" t="n">
-        <v>0.009259999999999999</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="520">
@@ -24542,7 +24542,7 @@
         <v>0.0509</v>
       </c>
       <c r="I520" t="n">
-        <v>0.136</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="521">
@@ -24616,7 +24616,7 @@
         <v>0.16</v>
       </c>
       <c r="I522" t="n">
-        <v>0.321</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="523">
@@ -24653,7 +24653,7 @@
         <v>0.57</v>
       </c>
       <c r="I523" t="n">
-        <v>0.829</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="524">
@@ -24690,7 +24690,7 @@
         <v>0.00493</v>
       </c>
       <c r="I524" t="n">
-        <v>0.0158</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="525">
@@ -24727,7 +24727,7 @@
         <v>0.398</v>
       </c>
       <c r="I525" t="n">
-        <v>0.663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -24801,7 +24801,7 @@
         <v>0.414</v>
       </c>
       <c r="I527" t="n">
-        <v>0.663</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="528">
@@ -24838,7 +24838,7 @@
         <v>0.000537</v>
       </c>
       <c r="I528" t="n">
-        <v>0.00839</v>
+        <v>0.00269</v>
       </c>
     </row>
     <row r="529">
@@ -24875,7 +24875,7 @@
         <v>0.00105</v>
       </c>
       <c r="I529" t="n">
-        <v>0.00839</v>
+        <v>0.00525</v>
       </c>
     </row>
     <row r="530">
@@ -24949,7 +24949,7 @@
         <v>0.00244</v>
       </c>
       <c r="I531" t="n">
-        <v>0.0391</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="532">
@@ -24986,7 +24986,7 @@
         <v>0.49</v>
       </c>
       <c r="I532" t="n">
-        <v>0.918</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="533">
@@ -25097,7 +25097,7 @@
         <v>0.516</v>
       </c>
       <c r="I535" t="n">
-        <v>0.918</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="536">
@@ -25134,7 +25134,7 @@
         <v>0.503</v>
       </c>
       <c r="I536" t="n">
-        <v>0.918</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="537">
@@ -25208,7 +25208,7 @@
         <v>0.238</v>
       </c>
       <c r="I538" t="n">
-        <v>0.634</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="539">
@@ -25319,7 +25319,7 @@
         <v>0.232</v>
       </c>
       <c r="I541" t="n">
-        <v>0.634</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="542">
@@ -25393,7 +25393,7 @@
         <v>0.0393</v>
       </c>
       <c r="I543" t="n">
-        <v>0.157</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="544">
@@ -25430,7 +25430,7 @@
         <v>0.00589</v>
       </c>
       <c r="I544" t="n">
-        <v>0.0471</v>
+        <v>0.0442</v>
       </c>
     </row>
     <row r="545">
@@ -25467,7 +25467,7 @@
         <v>0.0107</v>
       </c>
       <c r="I545" t="n">
-        <v>0.0571</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="546">
@@ -25504,7 +25504,7 @@
         <v>0.0219</v>
       </c>
       <c r="I546" t="n">
-        <v>0.0585</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="547">
@@ -25541,7 +25541,7 @@
         <v>0.489</v>
       </c>
       <c r="I547" t="n">
-        <v>0.768</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="548">
@@ -25652,7 +25652,7 @@
         <v>0.681</v>
       </c>
       <c r="I550" t="n">
-        <v>0.908</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -25689,7 +25689,7 @@
         <v>0.000189</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0022</v>
+        <v>0.000473</v>
       </c>
     </row>
     <row r="552">
@@ -25726,7 +25726,7 @@
         <v>0.009039999999999999</v>
       </c>
       <c r="I552" t="n">
-        <v>0.0362</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="553">
@@ -25800,7 +25800,7 @@
         <v>0.0336</v>
       </c>
       <c r="I554" t="n">
-        <v>0.0673</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="555">
@@ -25837,7 +25837,7 @@
         <v>0.528</v>
       </c>
       <c r="I555" t="n">
-        <v>0.768</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="556">
@@ -25874,7 +25874,7 @@
         <v>0.000275</v>
       </c>
       <c r="I556" t="n">
-        <v>0.0022</v>
+        <v>0.00138</v>
       </c>
     </row>
     <row r="557">
@@ -25911,7 +25911,7 @@
         <v>0.0152</v>
       </c>
       <c r="I557" t="n">
-        <v>0.0485</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="558">
@@ -25985,7 +25985,7 @@
         <v>0.00535</v>
       </c>
       <c r="I559" t="n">
-        <v>0.0285</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="560">
@@ -26022,7 +26022,7 @@
         <v>0.207</v>
       </c>
       <c r="I560" t="n">
-        <v>0.368</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="561">
@@ -26059,7 +26059,7 @@
         <v>0.0307</v>
       </c>
       <c r="I561" t="n">
-        <v>0.0673</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="562">
@@ -26096,7 +26096,7 @@
         <v>0.0866</v>
       </c>
       <c r="I562" t="n">
-        <v>0.173</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="563">
@@ -26133,7 +26133,7 @@
         <v>0.00915</v>
       </c>
       <c r="I563" t="n">
-        <v>0.0293</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="564">
@@ -26244,7 +26244,7 @@
         <v>0.701</v>
       </c>
       <c r="I566" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="567">
@@ -26281,7 +26281,7 @@
         <v>0.000178</v>
       </c>
       <c r="I567" t="n">
-        <v>0.00208</v>
+        <v>0.00133</v>
       </c>
     </row>
     <row r="568">
@@ -26318,7 +26318,7 @@
         <v>0.0175</v>
       </c>
       <c r="I568" t="n">
-        <v>0.0467</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="569">
@@ -26392,7 +26392,7 @@
         <v>0.0461</v>
       </c>
       <c r="I570" t="n">
-        <v>0.105</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="571">
@@ -26429,7 +26429,7 @@
         <v>0.405</v>
       </c>
       <c r="I571" t="n">
-        <v>0.589</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="572">
@@ -26466,7 +26466,7 @@
         <v>0.00026</v>
       </c>
       <c r="I572" t="n">
-        <v>0.00208</v>
+        <v>0.00195</v>
       </c>
     </row>
     <row r="573">
@@ -26503,7 +26503,7 @@
         <v>0.127</v>
       </c>
       <c r="I573" t="n">
-        <v>0.226</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="574">
@@ -26577,7 +26577,7 @@
         <v>0.146</v>
       </c>
       <c r="I575" t="n">
-        <v>0.233</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="576">
@@ -26614,7 +26614,7 @@
         <v>0.00135</v>
       </c>
       <c r="I576" t="n">
-        <v>0.0054</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="577">
@@ -26651,7 +26651,7 @@
         <v>0.000447</v>
       </c>
       <c r="I577" t="n">
-        <v>0.00238</v>
+        <v>0.00671</v>
       </c>
     </row>
     <row r="578">
@@ -26688,7 +26688,7 @@
         <v>0.0775</v>
       </c>
       <c r="I578" t="n">
-        <v>0.248</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="579">
@@ -26725,7 +26725,7 @@
         <v>0.00427</v>
       </c>
       <c r="I579" t="n">
-        <v>0.0394</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="580">
@@ -26873,7 +26873,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I583" t="n">
-        <v>0.248</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="584">
@@ -26910,7 +26910,7 @@
         <v>0.315</v>
       </c>
       <c r="I584" t="n">
-        <v>0.722</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="585">
@@ -26984,7 +26984,7 @@
         <v>0.0454</v>
       </c>
       <c r="I586" t="n">
-        <v>0.242</v>
+        <v>0.0973</v>
       </c>
     </row>
     <row r="587">
@@ -27058,7 +27058,7 @@
         <v>0.00493</v>
       </c>
       <c r="I588" t="n">
-        <v>0.0394</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="589">
@@ -27132,7 +27132,7 @@
         <v>0.498</v>
       </c>
       <c r="I590" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591">
@@ -27169,7 +27169,7 @@
         <v>0.475</v>
       </c>
       <c r="I591" t="n">
-        <v>0.885</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="592">
@@ -27206,7 +27206,7 @@
         <v>0.316</v>
       </c>
       <c r="I592" t="n">
-        <v>0.722</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="593">
@@ -27243,7 +27243,7 @@
         <v>0.673</v>
       </c>
       <c r="I593" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="594">
@@ -27317,7 +27317,7 @@
         <v>0.00473</v>
       </c>
       <c r="I595" t="n">
-        <v>0.0378</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="596">
@@ -27354,7 +27354,7 @@
         <v>0.667</v>
       </c>
       <c r="I596" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="597">
@@ -27428,7 +27428,7 @@
         <v>0.245</v>
       </c>
       <c r="I598" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="599">
@@ -27465,7 +27465,7 @@
         <v>0.0238</v>
       </c>
       <c r="I599" t="n">
-        <v>0.127</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="600">
@@ -27502,7 +27502,7 @@
         <v>0.0404</v>
       </c>
       <c r="I600" t="n">
-        <v>0.162</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="601">
@@ -27576,7 +27576,7 @@
         <v>0.397</v>
       </c>
       <c r="I602" t="n">
-        <v>0.794</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="603">
@@ -27613,7 +27613,7 @@
         <v>0.619</v>
       </c>
       <c r="I603" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -27650,7 +27650,7 @@
         <v>0.707</v>
       </c>
       <c r="I604" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -27687,7 +27687,7 @@
         <v>0.078</v>
       </c>
       <c r="I605" t="n">
-        <v>0.25</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="606">
@@ -27761,7 +27761,7 @@
         <v>0.000245</v>
       </c>
       <c r="I607" t="n">
-        <v>0.00392</v>
+        <v>0.00106</v>
       </c>
     </row>
     <row r="608">
@@ -27798,7 +27798,7 @@
         <v>0.223</v>
       </c>
       <c r="I608" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="609">
@@ -27835,7 +27835,7 @@
         <v>0.646</v>
       </c>
       <c r="I609" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="610">
@@ -27872,7 +27872,7 @@
         <v>0.0219</v>
       </c>
       <c r="I610" t="n">
-        <v>0.0585</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="611">
@@ -27909,7 +27909,7 @@
         <v>0.234</v>
       </c>
       <c r="I611" t="n">
-        <v>0.468</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="612">
@@ -28057,7 +28057,7 @@
         <v>0.000189</v>
       </c>
       <c r="I615" t="n">
-        <v>0.00151</v>
+        <v>0.000473</v>
       </c>
     </row>
     <row r="616">
@@ -28094,7 +28094,7 @@
         <v>0.00349</v>
       </c>
       <c r="I616" t="n">
-        <v>0.0186</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="617">
@@ -28168,7 +28168,7 @@
         <v>0.00899</v>
       </c>
       <c r="I618" t="n">
-        <v>0.0288</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="619">
@@ -28205,7 +28205,7 @@
         <v>0.762</v>
       </c>
       <c r="I619" t="n">
-        <v>1</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="620">
@@ -28242,7 +28242,7 @@
         <v>4.01e-05</v>
       </c>
       <c r="I620" t="n">
-        <v>0.000641</v>
+        <v>0.000602</v>
       </c>
     </row>
     <row r="621">
@@ -28279,7 +28279,7 @@
         <v>0.0352</v>
       </c>
       <c r="I621" t="n">
-        <v>0.0805</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="622">
@@ -28353,7 +28353,7 @@
         <v>0.00535</v>
       </c>
       <c r="I623" t="n">
-        <v>0.0214</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="624">
@@ -28390,7 +28390,7 @@
         <v>0.507</v>
       </c>
       <c r="I624" t="n">
-        <v>0.902</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="625">
@@ -28464,7 +28464,7 @@
         <v>0.0487</v>
       </c>
       <c r="I626" t="n">
-        <v>0.156</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="627">
@@ -28501,7 +28501,7 @@
         <v>0.0343</v>
       </c>
       <c r="I627" t="n">
-        <v>0.137</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="628">
@@ -28649,7 +28649,7 @@
         <v>0.00723</v>
       </c>
       <c r="I631" t="n">
-        <v>0.0518</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="632">
@@ -28686,7 +28686,7 @@
         <v>0.11</v>
       </c>
       <c r="I632" t="n">
-        <v>0.294</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="633">
@@ -28760,7 +28760,7 @@
         <v>0.009719999999999999</v>
       </c>
       <c r="I634" t="n">
-        <v>0.0518</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="635">
@@ -28834,7 +28834,7 @@
         <v>0.000224</v>
       </c>
       <c r="I636" t="n">
-        <v>0.00359</v>
+        <v>0.00195</v>
       </c>
     </row>
     <row r="637">
@@ -28871,7 +28871,7 @@
         <v>0.416</v>
       </c>
       <c r="I637" t="n">
-        <v>0.951</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="638">
@@ -28908,7 +28908,7 @@
         <v>0.492</v>
       </c>
       <c r="I638" t="n">
-        <v>0.984</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
@@ -29056,7 +29056,7 @@
         <v>0.133</v>
       </c>
       <c r="I642" t="n">
-        <v>0.707</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="643">
@@ -29167,7 +29167,7 @@
         <v>0.498</v>
       </c>
       <c r="I645" t="n">
-        <v>0.956</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="646">
@@ -29204,7 +29204,7 @@
         <v>0.579</v>
       </c>
       <c r="I646" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647">
@@ -29241,7 +29241,7 @@
         <v>0.329</v>
       </c>
       <c r="I647" t="n">
-        <v>0.956</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="648">
@@ -29278,7 +29278,7 @@
         <v>0.596</v>
       </c>
       <c r="I648" t="n">
-        <v>0.956</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="649">
@@ -29352,7 +29352,7 @@
         <v>0.0154</v>
       </c>
       <c r="I650" t="n">
-        <v>0.124</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="651">
@@ -29389,7 +29389,7 @@
         <v>0.00491</v>
       </c>
       <c r="I651" t="n">
-        <v>0.0786</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="652">
@@ -29463,7 +29463,7 @@
         <v>0.579</v>
       </c>
       <c r="I653" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="654">
@@ -29537,7 +29537,7 @@
         <v>0.259</v>
       </c>
       <c r="I655" t="n">
-        <v>0.956</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="656">
@@ -29574,7 +29574,7 @@
         <v>0.796</v>
       </c>
       <c r="I656" t="n">
-        <v>1</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="657">
@@ -29611,7 +29611,7 @@
         <v>0.598</v>
       </c>
       <c r="I657" t="n">
-        <v>0.956</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="658">
@@ -29685,7 +29685,7 @@
         <v>0.752</v>
       </c>
       <c r="I659" t="n">
-        <v>1</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="660">
@@ -29722,7 +29722,7 @@
         <v>0.784</v>
       </c>
       <c r="I660" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="661">
@@ -29944,7 +29944,7 @@
         <v>0.364</v>
       </c>
       <c r="I666" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="667">
@@ -29981,7 +29981,7 @@
         <v>0.417</v>
       </c>
       <c r="I667" t="n">
-        <v>1</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="668">
@@ -30129,7 +30129,7 @@
         <v>0.347</v>
       </c>
       <c r="I671" t="n">
-        <v>1</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="672">
@@ -30203,7 +30203,7 @@
         <v>0.867</v>
       </c>
       <c r="I673" t="n">
-        <v>1</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="674">
@@ -30240,7 +30240,7 @@
         <v>0.104</v>
       </c>
       <c r="I674" t="n">
-        <v>0.553</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="675">
@@ -30351,7 +30351,7 @@
         <v>0.483</v>
       </c>
       <c r="I677" t="n">
-        <v>0.91</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="678">
@@ -30388,7 +30388,7 @@
         <v>0.422</v>
       </c>
       <c r="I678" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679">
@@ -30425,7 +30425,7 @@
         <v>0.159</v>
       </c>
       <c r="I679" t="n">
-        <v>0.636</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="680">
@@ -30462,7 +30462,7 @@
         <v>0.512</v>
       </c>
       <c r="I680" t="n">
-        <v>0.91</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="681">
@@ -30536,7 +30536,7 @@
         <v>0.000262</v>
       </c>
       <c r="I682" t="n">
-        <v>0.0042</v>
+        <v>0.00131</v>
       </c>
     </row>
     <row r="683">
@@ -30573,7 +30573,7 @@
         <v>0.00359</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0288</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="684">
@@ -30610,7 +30610,7 @@
         <v>0.836</v>
       </c>
       <c r="I684" t="n">
-        <v>1</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="685">
@@ -30647,7 +30647,7 @@
         <v>0.469</v>
       </c>
       <c r="I685" t="n">
-        <v>0.91</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="686">
@@ -30721,7 +30721,7 @@
         <v>0.648</v>
       </c>
       <c r="I687" t="n">
-        <v>1</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="688">
@@ -30758,7 +30758,7 @@
         <v>0.316</v>
       </c>
       <c r="I688" t="n">
-        <v>0.91</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="689">
@@ -30832,7 +30832,7 @@
         <v>0.0696</v>
       </c>
       <c r="I690" t="n">
-        <v>0.371</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="691">
@@ -30943,7 +30943,7 @@
         <v>0.229</v>
       </c>
       <c r="I693" t="n">
-        <v>0.67</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="694">
@@ -30980,7 +30980,7 @@
         <v>0.465</v>
       </c>
       <c r="I694" t="n">
-        <v>0.858</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="695">
@@ -31017,7 +31017,7 @@
         <v>0.199</v>
       </c>
       <c r="I695" t="n">
-        <v>0.67</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="696">
@@ -31054,7 +31054,7 @@
         <v>0.482</v>
       </c>
       <c r="I696" t="n">
-        <v>0.858</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="697">
@@ -31128,7 +31128,7 @@
         <v>0.00122</v>
       </c>
       <c r="I698" t="n">
-        <v>0.00978</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="699">
@@ -31165,7 +31165,7 @@
         <v>0.000611</v>
       </c>
       <c r="I699" t="n">
-        <v>0.009769999999999999</v>
+        <v>0.00305</v>
       </c>
     </row>
     <row r="700">
@@ -31202,7 +31202,7 @@
         <v>0.872</v>
       </c>
       <c r="I700" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="701">
@@ -31239,7 +31239,7 @@
         <v>0.437</v>
       </c>
       <c r="I701" t="n">
-        <v>0.858</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="702">
@@ -31313,7 +31313,7 @@
         <v>0.251</v>
       </c>
       <c r="I703" t="n">
-        <v>0.67</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="704">
@@ -31424,7 +31424,7 @@
         <v>0.133</v>
       </c>
       <c r="I706" t="n">
-        <v>0.707</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="707">
@@ -31461,7 +31461,7 @@
         <v>0.769</v>
       </c>
       <c r="I707" t="n">
-        <v>1</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="708">
@@ -31609,7 +31609,7 @@
         <v>0.329</v>
       </c>
       <c r="I711" t="n">
-        <v>0.806</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="712">
@@ -31646,7 +31646,7 @@
         <v>0.475</v>
       </c>
       <c r="I712" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="713">
@@ -31720,7 +31720,7 @@
         <v>0.00997</v>
       </c>
       <c r="I714" t="n">
-        <v>0.0798</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="715">
@@ -31757,7 +31757,7 @@
         <v>0.0023</v>
       </c>
       <c r="I715" t="n">
-        <v>0.0368</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="716">
@@ -31794,7 +31794,7 @@
         <v>0.528</v>
       </c>
       <c r="I716" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="717">
@@ -31905,7 +31905,7 @@
         <v>0.259</v>
       </c>
       <c r="I719" t="n">
-        <v>0.806</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="720">
@@ -31942,7 +31942,7 @@
         <v>0.299</v>
       </c>
       <c r="I720" t="n">
-        <v>0.806</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="721">
@@ -31979,7 +31979,7 @@
         <v>0.353</v>
       </c>
       <c r="I721" t="n">
-        <v>0.806</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="722">
@@ -32053,7 +32053,7 @@
         <v>0.518</v>
       </c>
       <c r="I723" t="n">
-        <v>1</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="724">
@@ -32164,7 +32164,7 @@
         <v>0.369</v>
       </c>
       <c r="I726" t="n">
-        <v>1</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="727">
@@ -32201,7 +32201,7 @@
         <v>0.799</v>
       </c>
       <c r="I727" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="728">
@@ -32312,7 +32312,7 @@
         <v>0.526</v>
       </c>
       <c r="I730" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="731">
@@ -32349,7 +32349,7 @@
         <v>0.412</v>
       </c>
       <c r="I731" t="n">
-        <v>1</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="732">
@@ -32497,7 +32497,7 @@
         <v>0.219</v>
       </c>
       <c r="I735" t="n">
-        <v>1</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="736">
@@ -32534,7 +32534,7 @@
         <v>0.669</v>
       </c>
       <c r="I736" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="737">
@@ -32571,7 +32571,7 @@
         <v>0.872</v>
       </c>
       <c r="I737" t="n">
-        <v>1</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="738">
@@ -32608,7 +32608,7 @@
         <v>0.0682</v>
       </c>
       <c r="I738" t="n">
-        <v>0.273</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="739">
@@ -32719,7 +32719,7 @@
         <v>0.483</v>
       </c>
       <c r="I741" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="742">
@@ -32793,7 +32793,7 @@
         <v>0.0362</v>
       </c>
       <c r="I743" t="n">
-        <v>0.193</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="744">
@@ -32830,7 +32830,7 @@
         <v>0.259</v>
       </c>
       <c r="I744" t="n">
-        <v>0.829</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="745">
@@ -32904,7 +32904,7 @@
         <v>0.000262</v>
       </c>
       <c r="I746" t="n">
-        <v>0.0042</v>
+        <v>0.00131</v>
       </c>
     </row>
     <row r="747">
@@ -32941,7 +32941,7 @@
         <v>0.00159</v>
       </c>
       <c r="I747" t="n">
-        <v>0.0127</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="748">
@@ -32978,7 +32978,7 @@
         <v>0.544</v>
       </c>
       <c r="I748" t="n">
-        <v>1</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="749">
@@ -33015,7 +33015,7 @@
         <v>0.634</v>
       </c>
       <c r="I749" t="n">
-        <v>1</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="750">
@@ -33126,7 +33126,7 @@
         <v>0.759</v>
       </c>
       <c r="I752" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="753">
@@ -33200,7 +33200,7 @@
         <v>0.0692</v>
       </c>
       <c r="I754" t="n">
-        <v>0.369</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="755">
@@ -33237,7 +33237,7 @@
         <v>0.763</v>
       </c>
       <c r="I755" t="n">
-        <v>1</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="756">
@@ -33311,7 +33311,7 @@
         <v>0.599</v>
       </c>
       <c r="I757" t="n">
-        <v>0.959</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="758">
@@ -33348,7 +33348,7 @@
         <v>0.86</v>
       </c>
       <c r="I758" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="759">
@@ -33385,7 +33385,7 @@
         <v>0.149</v>
       </c>
       <c r="I759" t="n">
-        <v>0.595</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="760">
@@ -33422,7 +33422,7 @@
         <v>0.293</v>
       </c>
       <c r="I760" t="n">
-        <v>0.863</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="761">
@@ -33459,7 +33459,7 @@
         <v>0.592</v>
       </c>
       <c r="I761" t="n">
-        <v>0.959</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762">
@@ -33496,7 +33496,7 @@
         <v>0.00105</v>
       </c>
       <c r="I762" t="n">
-        <v>0.008410000000000001</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="763">
@@ -33533,7 +33533,7 @@
         <v>0.000234</v>
       </c>
       <c r="I763" t="n">
-        <v>0.00374</v>
+        <v>0.00176</v>
       </c>
     </row>
     <row r="764">
@@ -33570,7 +33570,7 @@
         <v>0.435</v>
       </c>
       <c r="I764" t="n">
-        <v>0.959</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="765">
@@ -33607,7 +33607,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="I765" t="n">
-        <v>0.959</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="766">
@@ -33681,7 +33681,7 @@
         <v>0.324</v>
       </c>
       <c r="I767" t="n">
-        <v>0.863</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="768">
@@ -33792,7 +33792,7 @@
         <v>0.0608</v>
       </c>
       <c r="I770" t="n">
-        <v>0.324</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="771">
@@ -33866,7 +33866,7 @@
         <v>0.673</v>
       </c>
       <c r="I772" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773">
@@ -33903,7 +33903,7 @@
         <v>0.498</v>
       </c>
       <c r="I773" t="n">
-        <v>0.797</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="774">
@@ -33940,7 +33940,7 @@
         <v>0.732</v>
       </c>
       <c r="I774" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775">
@@ -33977,7 +33977,7 @@
         <v>0.133</v>
       </c>
       <c r="I775" t="n">
-        <v>0.531</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="776">
@@ -34014,7 +34014,7 @@
         <v>0.366</v>
       </c>
       <c r="I776" t="n">
-        <v>0.732</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="777">
@@ -34051,7 +34051,7 @@
         <v>0.722</v>
       </c>
       <c r="I777" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
     </row>
     <row r="778">
@@ -34088,7 +34088,7 @@
         <v>0.0154</v>
       </c>
       <c r="I778" t="n">
-        <v>0.143</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="779">
@@ -34125,7 +34125,7 @@
         <v>0.0179</v>
       </c>
       <c r="I779" t="n">
-        <v>0.143</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="780">
@@ -34162,7 +34162,7 @@
         <v>0.872</v>
       </c>
       <c r="I780" t="n">
-        <v>0.997</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="781">
@@ -34199,7 +34199,7 @@
         <v>0.454</v>
       </c>
       <c r="I781" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
     </row>
     <row r="782">
@@ -34273,7 +34273,7 @@
         <v>0.259</v>
       </c>
       <c r="I783" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="784">
@@ -34310,7 +34310,7 @@
         <v>0.364</v>
       </c>
       <c r="I784" t="n">
-        <v>0.732</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="785">
@@ -34347,7 +34347,7 @@
         <v>0.23</v>
       </c>
       <c r="I785" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="786">
@@ -34421,7 +34421,7 @@
         <v>0.752</v>
       </c>
       <c r="I787" t="n">
-        <v>1</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="788">
@@ -34458,7 +34458,7 @@
         <v>0.791</v>
       </c>
       <c r="I788" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="789">
@@ -34532,7 +34532,7 @@
         <v>0.119</v>
       </c>
       <c r="I790" t="n">
-        <v>1</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="791">
@@ -34569,7 +34569,7 @@
         <v>0.783</v>
       </c>
       <c r="I791" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="792">
@@ -34606,7 +34606,7 @@
         <v>0.757</v>
       </c>
       <c r="I792" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="793">
@@ -34680,7 +34680,7 @@
         <v>0.526</v>
       </c>
       <c r="I794" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="795">
@@ -34865,7 +34865,7 @@
         <v>0.487</v>
       </c>
       <c r="I799" t="n">
-        <v>1</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="800">
@@ -34902,7 +34902,7 @@
         <v>0.774</v>
       </c>
       <c r="I800" t="n">
-        <v>1</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="801">
@@ -34939,7 +34939,7 @@
         <v>0.742</v>
       </c>
       <c r="I801" t="n">
-        <v>1</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="802">
@@ -34976,7 +34976,7 @@
         <v>0.0429</v>
       </c>
       <c r="I802" t="n">
-        <v>0.229</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="803">
@@ -35087,7 +35087,7 @@
         <v>0.483</v>
       </c>
       <c r="I805" t="n">
-        <v>0.967</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="806">
@@ -35161,7 +35161,7 @@
         <v>0.0631</v>
       </c>
       <c r="I807" t="n">
-        <v>0.253</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="808">
@@ -35198,7 +35198,7 @@
         <v>0.375</v>
       </c>
       <c r="I808" t="n">
-        <v>0.967</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="809">
@@ -35272,7 +35272,7 @@
         <v>0.00052</v>
       </c>
       <c r="I810" t="n">
-        <v>0.008319999999999999</v>
+        <v>0.00195</v>
       </c>
     </row>
     <row r="811">
@@ -35309,7 +35309,7 @@
         <v>0.0075</v>
       </c>
       <c r="I811" t="n">
-        <v>0.06</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="812">
@@ -35346,7 +35346,7 @@
         <v>0.544</v>
       </c>
       <c r="I812" t="n">
-        <v>0.967</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="813">
@@ -35383,7 +35383,7 @@
         <v>0.328</v>
       </c>
       <c r="I813" t="n">
-        <v>0.967</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="814">
@@ -35457,7 +35457,7 @@
         <v>0.487</v>
       </c>
       <c r="I815" t="n">
-        <v>0.967</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="816">
@@ -35494,7 +35494,7 @@
         <v>0.759</v>
       </c>
       <c r="I816" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="817">
@@ -35568,7 +35568,7 @@
         <v>0.0283</v>
       </c>
       <c r="I818" t="n">
-        <v>0.151</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="819">
@@ -35642,7 +35642,7 @@
         <v>0.647</v>
       </c>
       <c r="I820" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821">
@@ -35679,7 +35679,7 @@
         <v>0.229</v>
       </c>
       <c r="I821" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="822">
@@ -35716,7 +35716,7 @@
         <v>0.866</v>
       </c>
       <c r="I822" t="n">
-        <v>0.99</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="823">
@@ -35753,7 +35753,7 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I823" t="n">
-        <v>0.277</v>
+        <v>0.09420000000000001</v>
       </c>
     </row>
     <row r="824">
@@ -35790,7 +35790,7 @@
         <v>0.281</v>
       </c>
       <c r="I824" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="825">
@@ -35827,7 +35827,7 @@
         <v>0.592</v>
       </c>
       <c r="I825" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="826">
@@ -35864,7 +35864,7 @@
         <v>0.00181</v>
       </c>
       <c r="I826" t="n">
-        <v>0.0236</v>
+        <v>0.00679</v>
       </c>
     </row>
     <row r="827">
@@ -35901,7 +35901,7 @@
         <v>0.00294</v>
       </c>
       <c r="I827" t="n">
-        <v>0.0236</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="828">
@@ -35938,7 +35938,7 @@
         <v>0.634</v>
       </c>
       <c r="I828" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="829">
@@ -35975,7 +35975,7 @@
         <v>0.246</v>
       </c>
       <c r="I829" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="830">
@@ -36049,7 +36049,7 @@
         <v>0.251</v>
       </c>
       <c r="I831" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="832">
@@ -36086,7 +36086,7 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="I832" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="833">
@@ -36123,7 +36123,7 @@
         <v>0.8</v>
       </c>
       <c r="I833" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="834">
@@ -36160,7 +36160,7 @@
         <v>0.133</v>
       </c>
       <c r="I834" t="n">
-        <v>0.424</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="835">
@@ -36345,7 +36345,7 @@
         <v>0.251</v>
       </c>
       <c r="I839" t="n">
-        <v>0.573</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="840">
@@ -36382,7 +36382,7 @@
         <v>0.366</v>
       </c>
       <c r="I840" t="n">
-        <v>0.651</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="841">
@@ -36456,7 +36456,7 @@
         <v>0.00226</v>
       </c>
       <c r="I842" t="n">
-        <v>0.0184</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="843">
@@ -36493,7 +36493,7 @@
         <v>0.0023</v>
       </c>
       <c r="I843" t="n">
-        <v>0.0184</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="844">
@@ -36530,7 +36530,7 @@
         <v>0.434</v>
       </c>
       <c r="I844" t="n">
-        <v>0.694</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="845">
@@ -36567,7 +36567,7 @@
         <v>0.343</v>
       </c>
       <c r="I845" t="n">
-        <v>0.651</v>
+        <v>1</v>
       </c>
     </row>
     <row r="846">
@@ -36641,7 +36641,7 @@
         <v>0.0156</v>
       </c>
       <c r="I847" t="n">
-        <v>0.0833</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="848">
@@ -36678,7 +36678,7 @@
         <v>0.193</v>
       </c>
       <c r="I848" t="n">
-        <v>0.515</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="849">
@@ -36715,7 +36715,7 @@
         <v>0.0296</v>
       </c>
       <c r="I849" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="850">
@@ -36789,7 +36789,7 @@
         <v>0.756</v>
       </c>
       <c r="I851" t="n">
-        <v>1</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="852">
@@ -36900,7 +36900,7 @@
         <v>0.213</v>
       </c>
       <c r="I854" t="n">
-        <v>1</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="855">
@@ -36974,7 +36974,7 @@
         <v>0.757</v>
       </c>
       <c r="I856" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="857">
@@ -37048,7 +37048,7 @@
         <v>0.529</v>
       </c>
       <c r="I858" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="859">
@@ -37233,7 +37233,7 @@
         <v>0.0205</v>
       </c>
       <c r="I863" t="n">
-        <v>0.328</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="864">
@@ -37270,7 +37270,7 @@
         <v>0.67</v>
       </c>
       <c r="I864" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="865">
@@ -37307,7 +37307,7 @@
         <v>0.409</v>
       </c>
       <c r="I865" t="n">
-        <v>1</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="866">
@@ -37344,7 +37344,7 @@
         <v>0.0682</v>
       </c>
       <c r="I866" t="n">
-        <v>0.273</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="867">
@@ -37381,7 +37381,7 @@
         <v>0.489</v>
       </c>
       <c r="I867" t="n">
-        <v>0.736</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="868">
@@ -37455,7 +37455,7 @@
         <v>0.483</v>
       </c>
       <c r="I869" t="n">
-        <v>0.736</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="870">
@@ -37492,7 +37492,7 @@
         <v>0.552</v>
       </c>
       <c r="I870" t="n">
-        <v>0.736</v>
+        <v>1</v>
       </c>
     </row>
     <row r="871">
@@ -37529,7 +37529,7 @@
         <v>0.0631</v>
       </c>
       <c r="I871" t="n">
-        <v>0.273</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="872">
@@ -37566,7 +37566,7 @@
         <v>0.375</v>
       </c>
       <c r="I872" t="n">
-        <v>0.736</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="873">
@@ -37640,7 +37640,7 @@
         <v>2.55e-05</v>
       </c>
       <c r="I874" t="n">
-        <v>0.000408</v>
+        <v>0.000382</v>
       </c>
     </row>
     <row r="875">
@@ -37677,7 +37677,7 @@
         <v>0.000639</v>
       </c>
       <c r="I875" t="n">
-        <v>0.00511</v>
+        <v>0.00958</v>
       </c>
     </row>
     <row r="876">
@@ -37714,7 +37714,7 @@
         <v>0.423</v>
       </c>
       <c r="I876" t="n">
-        <v>0.736</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="877">
@@ -37751,7 +37751,7 @@
         <v>0.214</v>
       </c>
       <c r="I877" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="878">
@@ -37825,7 +37825,7 @@
         <v>0.346</v>
       </c>
       <c r="I879" t="n">
-        <v>0.736</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="880">
@@ -37862,7 +37862,7 @@
         <v>0.523</v>
       </c>
       <c r="I880" t="n">
-        <v>0.736</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="881">
@@ -37936,7 +37936,7 @@
         <v>0.0692</v>
       </c>
       <c r="I882" t="n">
-        <v>0.277</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="883">
@@ -38010,7 +38010,7 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="I884" t="n">
-        <v>0.921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="885">
@@ -38047,7 +38047,7 @@
         <v>0.599</v>
       </c>
       <c r="I885" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="886">
@@ -38084,7 +38084,7 @@
         <v>0.863</v>
       </c>
       <c r="I886" t="n">
-        <v>0.921</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="887">
@@ -38121,7 +38121,7 @@
         <v>0.109</v>
       </c>
       <c r="I887" t="n">
-        <v>0.348</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="888">
@@ -38158,7 +38158,7 @@
         <v>0.281</v>
       </c>
       <c r="I888" t="n">
-        <v>0.642</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="889">
@@ -38195,7 +38195,7 @@
         <v>0.592</v>
       </c>
       <c r="I889" t="n">
-        <v>0.8179999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="890">
@@ -38232,7 +38232,7 @@
         <v>0.000169</v>
       </c>
       <c r="I890" t="n">
-        <v>0.00171</v>
+        <v>0.00253</v>
       </c>
     </row>
     <row r="891">
@@ -38269,7 +38269,7 @@
         <v>0.000213</v>
       </c>
       <c r="I891" t="n">
-        <v>0.00171</v>
+        <v>0.00176</v>
       </c>
     </row>
     <row r="892">
@@ -38306,7 +38306,7 @@
         <v>0.351</v>
       </c>
       <c r="I892" t="n">
-        <v>0.662</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="893">
@@ -38343,7 +38343,7 @@
         <v>0.169</v>
       </c>
       <c r="I893" t="n">
-        <v>0.451</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="894">
@@ -38380,7 +38380,7 @@
         <v>0.613</v>
       </c>
       <c r="I894" t="n">
-        <v>0.8179999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="895">
@@ -38417,7 +38417,7 @@
         <v>0.0154</v>
       </c>
       <c r="I895" t="n">
-        <v>0.082</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="896">
@@ -38454,7 +38454,7 @@
         <v>0.728</v>
       </c>
       <c r="I896" t="n">
-        <v>0.897</v>
+        <v>1</v>
       </c>
     </row>
     <row r="897">
@@ -38491,7 +38491,7 @@
         <v>0.373</v>
       </c>
       <c r="I897" t="n">
-        <v>0.662</v>
+        <v>1</v>
       </c>
     </row>
     <row r="898">
@@ -38528,7 +38528,7 @@
         <v>0.329</v>
       </c>
       <c r="I898" t="n">
-        <v>0.586</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="899">
@@ -38565,7 +38565,7 @@
         <v>0.333</v>
       </c>
       <c r="I899" t="n">
-        <v>0.586</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="900">
@@ -38602,7 +38602,7 @@
         <v>0.0503</v>
       </c>
       <c r="I900" t="n">
-        <v>0.203</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="901">
@@ -38639,7 +38639,7 @@
         <v>0.498</v>
       </c>
       <c r="I901" t="n">
-        <v>0.613</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="902">
@@ -38676,7 +38676,7 @@
         <v>0.611</v>
       </c>
       <c r="I902" t="n">
-        <v>0.698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="903">
@@ -38713,7 +38713,7 @@
         <v>0.133</v>
       </c>
       <c r="I903" t="n">
-        <v>0.303</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="904">
@@ -38750,7 +38750,7 @@
         <v>0.366</v>
       </c>
       <c r="I904" t="n">
-        <v>0.586</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="905">
@@ -38787,7 +38787,7 @@
         <v>0.446</v>
       </c>
       <c r="I905" t="n">
-        <v>0.613</v>
+        <v>1</v>
       </c>
     </row>
     <row r="906">
@@ -38824,7 +38824,7 @@
         <v>0.0944</v>
       </c>
       <c r="I906" t="n">
-        <v>0.252</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="907">
@@ -38861,7 +38861,7 @@
         <v>0.0507</v>
       </c>
       <c r="I907" t="n">
-        <v>0.203</v>
+        <v>0.0951</v>
       </c>
     </row>
     <row r="908">
@@ -38898,7 +38898,7 @@
         <v>0.493</v>
       </c>
       <c r="I908" t="n">
-        <v>0.613</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="909">
@@ -38935,7 +38935,7 @@
         <v>0.715</v>
       </c>
       <c r="I909" t="n">
-        <v>0.763</v>
+        <v>1</v>
       </c>
     </row>
     <row r="910">
@@ -39009,7 +39009,7 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I911" t="n">
-        <v>0.21</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="912">
@@ -39046,7 +39046,7 @@
         <v>3.4e-05</v>
       </c>
       <c r="I912" t="n">
-        <v>0.000272</v>
+        <v>0.00051</v>
       </c>
     </row>
     <row r="913">
@@ -39083,7 +39083,7 @@
         <v>2.21e-06</v>
       </c>
       <c r="I913" t="n">
-        <v>3.53e-05</v>
+        <v>1.66e-05</v>
       </c>
     </row>
     <row r="914">
@@ -39120,7 +39120,7 @@
         <v>0.229</v>
       </c>
       <c r="I914" t="n">
-        <v>0.366</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="915">
@@ -39157,7 +39157,7 @@
         <v>0.167</v>
       </c>
       <c r="I915" t="n">
-        <v>0.297</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="916">
@@ -39194,7 +39194,7 @@
         <v>0.0511</v>
       </c>
       <c r="I916" t="n">
-        <v>0.14</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="917">
@@ -39305,7 +39305,7 @@
         <v>0.0611</v>
       </c>
       <c r="I919" t="n">
-        <v>0.14</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="920">
@@ -39342,7 +39342,7 @@
         <v>0.115</v>
       </c>
       <c r="I920" t="n">
-        <v>0.229</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="921">
@@ -39379,7 +39379,7 @@
         <v>0.486</v>
       </c>
       <c r="I921" t="n">
-        <v>0.648</v>
+        <v>1</v>
       </c>
     </row>
     <row r="922">
@@ -39416,7 +39416,7 @@
         <v>0.336</v>
       </c>
       <c r="I922" t="n">
-        <v>0.489</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="923">
@@ -39490,7 +39490,7 @@
         <v>0.0216</v>
       </c>
       <c r="I924" t="n">
-        <v>0.0866</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="925">
@@ -39527,7 +39527,7 @@
         <v>0.0605</v>
       </c>
       <c r="I925" t="n">
-        <v>0.14</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="926">
@@ -39601,7 +39601,7 @@
         <v>0.000288</v>
       </c>
       <c r="I927" t="n">
-        <v>0.0023</v>
+        <v>0.00106</v>
       </c>
     </row>
     <row r="928">
@@ -39638,7 +39638,7 @@
         <v>0.000225</v>
       </c>
       <c r="I928" t="n">
-        <v>0.0023</v>
+        <v>0.00337</v>
       </c>
     </row>
     <row r="929">
@@ -39675,7 +39675,7 @@
         <v>0.00349</v>
       </c>
       <c r="I929" t="n">
-        <v>0.0186</v>
+        <v>0.0524</v>
       </c>
     </row>
     <row r="930">
@@ -39712,7 +39712,7 @@
         <v>0.0682</v>
       </c>
       <c r="I930" t="n">
-        <v>0.273</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="931">
@@ -39823,7 +39823,7 @@
         <v>0.483</v>
       </c>
       <c r="I933" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="934">
@@ -39897,7 +39897,7 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="I935" t="n">
-        <v>1</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="936">
@@ -40008,7 +40008,7 @@
         <v>0.135</v>
       </c>
       <c r="I938" t="n">
-        <v>0.431</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="939">
@@ -40045,7 +40045,7 @@
         <v>0.0146</v>
       </c>
       <c r="I939" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="940">
@@ -40082,7 +40082,7 @@
         <v>0.6820000000000001</v>
       </c>
       <c r="I940" t="n">
-        <v>1</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="941">
@@ -40119,7 +40119,7 @@
         <v>0.82</v>
       </c>
       <c r="I941" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="942">
@@ -40193,7 +40193,7 @@
         <v>0.83</v>
       </c>
       <c r="I943" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="944">
@@ -40230,7 +40230,7 @@
         <v>7.34e-05</v>
       </c>
       <c r="I944" t="n">
-        <v>0.00117</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="945">
@@ -40267,7 +40267,7 @@
         <v>0.00152</v>
       </c>
       <c r="I945" t="n">
-        <v>0.0122</v>
+        <v>0.0228</v>
       </c>
     </row>
     <row r="946">
@@ -40304,7 +40304,7 @@
         <v>0.15</v>
       </c>
       <c r="I946" t="n">
-        <v>0.457</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="947">
@@ -40341,7 +40341,7 @@
         <v>0.328</v>
       </c>
       <c r="I947" t="n">
-        <v>0.583</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="948">
@@ -40378,7 +40378,7 @@
         <v>0.0788</v>
       </c>
       <c r="I948" t="n">
-        <v>0.42</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="949">
@@ -40415,7 +40415,7 @@
         <v>0.229</v>
       </c>
       <c r="I949" t="n">
-        <v>0.523</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="950">
@@ -40452,7 +40452,7 @@
         <v>0.502</v>
       </c>
       <c r="I950" t="n">
-        <v>0.73</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="951">
@@ -40489,7 +40489,7 @@
         <v>0.136</v>
       </c>
       <c r="I951" t="n">
-        <v>0.457</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="952">
@@ -40526,7 +40526,7 @@
         <v>0.369</v>
       </c>
       <c r="I952" t="n">
-        <v>0.591</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="953">
@@ -40563,7 +40563,7 @@
         <v>0.286</v>
       </c>
       <c r="I953" t="n">
-        <v>0.572</v>
+        <v>1</v>
       </c>
     </row>
     <row r="954">
@@ -40600,7 +40600,7 @@
         <v>0.0484</v>
       </c>
       <c r="I954" t="n">
-        <v>0.387</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="955">
@@ -40637,7 +40637,7 @@
         <v>0.011</v>
       </c>
       <c r="I955" t="n">
-        <v>0.175</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="956">
@@ -40674,7 +40674,7 @@
         <v>0.612</v>
       </c>
       <c r="I956" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="957">
@@ -40711,7 +40711,7 @@
         <v>0.847</v>
       </c>
       <c r="I957" t="n">
-        <v>0.884</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="958">
@@ -40748,7 +40748,7 @@
         <v>0.662</v>
       </c>
       <c r="I958" t="n">
-        <v>0.8139999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="959">
@@ -40785,7 +40785,7 @@
         <v>0.171</v>
       </c>
       <c r="I959" t="n">
-        <v>0.457</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="960">
@@ -40822,7 +40822,7 @@
         <v>0.884</v>
       </c>
       <c r="I960" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="961">
@@ -40859,7 +40859,7 @@
         <v>0.869</v>
       </c>
       <c r="I961" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -518,7 +518,7 @@
         <v>0.0984</v>
       </c>
       <c r="J2" t="n">
-        <v>0.16</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>0.0984</v>
       </c>
       <c r="J3" t="n">
-        <v>0.136</v>
+        <v>0.1475</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.584</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.164</v>
       </c>
       <c r="J5" t="n">
-        <v>0.624</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
         <v>0.0871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.493</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.0871</v>
       </c>
       <c r="J7" t="n">
-        <v>0.31</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.712</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.624</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.186</v>
       </c>
       <c r="J10" t="n">
-        <v>0.641</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.186</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8870000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -958,7 +958,7 @@
         <v>0.147</v>
       </c>
       <c r="J13" t="n">
-        <v>0.824</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.242</v>
+        <v>0.1933333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1038,7 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.234</v>
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -1078,7 +1078,7 @@
         <v>0.165</v>
       </c>
       <c r="J16" t="n">
-        <v>0.712</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="17">
@@ -1118,7 +1118,7 @@
         <v>0.165</v>
       </c>
       <c r="J17" t="n">
-        <v>0.66</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="18">
@@ -1158,7 +1158,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0155</v>
+        <v>0.002575</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0268</v>
+        <v>0.00488</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0649</v>
+        <v>0.08800000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.116</v>
+        <v>0.2225</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.174</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0649</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.174</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0697</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.186</v>
       </c>
       <c r="J24" t="n">
-        <v>0.24</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.186</v>
       </c>
       <c r="J25" t="n">
-        <v>0.188</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.187</v>
       </c>
       <c r="J26" t="n">
-        <v>0.242</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.187</v>
       </c>
       <c r="J27" t="n">
-        <v>0.297</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.203</v>
       </c>
       <c r="J28" t="n">
-        <v>0.355</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.203</v>
       </c>
       <c r="J29" t="n">
-        <v>0.247</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="30">
@@ -1638,7 +1638,7 @@
         <v>0.0897</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0292</v>
+        <v>0.00389</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1678,7 @@
         <v>0.0897</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0268</v>
+        <v>0.00147</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.575</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.174</v>
       </c>
       <c r="J33" t="n">
-        <v>0.232</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.261</v>
       </c>
       <c r="J34" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1415</v>
       </c>
     </row>
     <row r="35">
@@ -1838,7 +1838,7 @@
         <v>0.261</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0279</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="36">
@@ -1878,7 +1878,7 @@
         <v>0.156</v>
       </c>
       <c r="J36" t="n">
-        <v>0.645</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.156</v>
       </c>
       <c r="J37" t="n">
-        <v>0.624</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.222</v>
       </c>
       <c r="J38" t="n">
-        <v>0.373</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.222</v>
       </c>
       <c r="J39" t="n">
-        <v>0.36</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.211</v>
       </c>
       <c r="J40" t="n">
-        <v>0.214</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.211</v>
       </c>
       <c r="J41" t="n">
-        <v>0.131</v>
+        <v>0.2675</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.277</v>
       </c>
       <c r="J42" t="n">
-        <v>0.208</v>
+        <v>0.1445</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.277</v>
       </c>
       <c r="J43" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.05583333333333334</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.16</v>
       </c>
       <c r="J44" t="n">
-        <v>0.627</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.16</v>
       </c>
       <c r="J45" t="n">
-        <v>0.36</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.24</v>
       </c>
       <c r="J46" t="n">
-        <v>0.208</v>
+        <v>0.1445</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.24</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0927</v>
+        <v>0.05583333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.064</v>
       </c>
       <c r="J48" t="n">
-        <v>0.288</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.064</v>
       </c>
       <c r="J49" t="n">
-        <v>0.759</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.174</v>
       </c>
       <c r="J50" t="n">
-        <v>0.513</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.174</v>
       </c>
       <c r="J51" t="n">
-        <v>0.234</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.235</v>
       </c>
       <c r="J52" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.235</v>
       </c>
       <c r="J53" t="n">
-        <v>0.247</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.209</v>
       </c>
       <c r="J54" t="n">
-        <v>0.718</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.209</v>
       </c>
       <c r="J55" t="n">
-        <v>0.757</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.22</v>
       </c>
       <c r="J56" t="n">
-        <v>0.641</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="57">
@@ -2758,7 +2758,7 @@
         <v>0.223</v>
       </c>
       <c r="J58" t="n">
-        <v>0.641</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.223</v>
       </c>
       <c r="J59" t="n">
-        <v>0.757</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.101</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0286</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="61">
@@ -2878,7 +2878,7 @@
         <v>0.101</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0268</v>
+        <v>0.00179</v>
       </c>
     </row>
     <row r="62">
@@ -2918,7 +2918,7 @@
         <v>0.187</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0649</v>
+        <v>0.02783333333333333</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.187</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0697</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="64">
@@ -2998,7 +2998,7 @@
         <v>0.242</v>
       </c>
       <c r="J64" t="n">
-        <v>0.641</v>
+        <v>0.8459999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3038,7 +3038,7 @@
         <v>0.242</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0927</v>
+        <v>0.1365</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.126</v>
       </c>
       <c r="J66" t="n">
-        <v>0.337</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.126</v>
       </c>
       <c r="J67" t="n">
-        <v>0.36</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.198</v>
       </c>
       <c r="J68" t="n">
-        <v>0.86</v>
+        <v>0.8459999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -3198,7 +3198,7 @@
         <v>0.198</v>
       </c>
       <c r="J69" t="n">
-        <v>0.328</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="70">
@@ -3238,7 +3238,7 @@
         <v>0.097</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0578</v>
+        <v>0.024425</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.097</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0413</v>
+        <v>0.024075</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.253</v>
       </c>
       <c r="J72" t="n">
-        <v>0.86</v>
+        <v>0.8459999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.253</v>
       </c>
       <c r="J73" t="n">
-        <v>0.624</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.111</v>
       </c>
       <c r="J74" t="n">
-        <v>0.101</v>
+        <v>0.04225</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.111</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0965</v>
+        <v>0.04425</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.265</v>
       </c>
       <c r="J76" t="n">
-        <v>0.819</v>
+        <v>0.8459999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.265</v>
       </c>
       <c r="J77" t="n">
-        <v>0.328</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.157</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0286</v>
+        <v>0.009849999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.157</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0314</v>
+        <v>0.024075</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.183</v>
       </c>
       <c r="J80" t="n">
-        <v>0.103</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.183</v>
       </c>
       <c r="J81" t="n">
-        <v>0.131</v>
+        <v>0.1365</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.157</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0578</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.157</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0352</v>
+        <v>0.00763</v>
       </c>
     </row>
     <row r="84">
@@ -3798,7 +3798,7 @@
         <v>0.102</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0286</v>
+        <v>0.00742</v>
       </c>
     </row>
     <row r="85">
@@ -3838,7 +3838,7 @@
         <v>0.102</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0279</v>
+        <v>0.00672</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.0997</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0292</v>
+        <v>0.00742</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.0997</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0279</v>
+        <v>0.00672</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.104</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0447</v>
+        <v>0.008946666666666667</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.104</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0314</v>
+        <v>0.00763</v>
       </c>
     </row>
     <row r="90">
@@ -4078,7 +4078,7 @@
         <v>0.184</v>
       </c>
       <c r="J91" t="n">
-        <v>0.988</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.161</v>
       </c>
       <c r="J92" t="n">
-        <v>0.335</v>
+        <v>0.3066666666666666</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.161</v>
       </c>
       <c r="J93" t="n">
-        <v>0.36</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.245</v>
       </c>
       <c r="J94" t="n">
-        <v>0.641</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="95">
@@ -4238,7 +4238,7 @@
         <v>0.245</v>
       </c>
       <c r="J95" t="n">
-        <v>0.831</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="96">
@@ -4278,7 +4278,7 @@
         <v>0.113</v>
       </c>
       <c r="J96" t="n">
-        <v>0.641</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.113</v>
       </c>
       <c r="J97" t="n">
-        <v>0.382</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.206</v>
       </c>
       <c r="J98" t="n">
-        <v>0.783</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.206</v>
       </c>
       <c r="J99" t="n">
-        <v>0.619</v>
+        <v>0.7733333333333334</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.153</v>
       </c>
       <c r="J100" t="n">
-        <v>0.641</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.153</v>
       </c>
       <c r="J101" t="n">
-        <v>0.671</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.258</v>
       </c>
       <c r="J102" t="n">
-        <v>0.627</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.258</v>
       </c>
       <c r="J103" t="n">
-        <v>0.997</v>
+        <v>0.9800000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.118</v>
       </c>
       <c r="J104" t="n">
-        <v>0.319</v>
+        <v>0.3066666666666666</v>
       </c>
     </row>
     <row r="105">
@@ -4638,7 +4638,7 @@
         <v>0.118</v>
       </c>
       <c r="J105" t="n">
-        <v>0.234</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="106">
@@ -4678,7 +4678,7 @@
         <v>0.244</v>
       </c>
       <c r="J106" t="n">
-        <v>0.712</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="107">
@@ -4718,7 +4718,7 @@
         <v>0.244</v>
       </c>
       <c r="J107" t="n">
-        <v>0.495</v>
+        <v>0.7733333333333334</v>
       </c>
     </row>
     <row r="108">
@@ -4758,7 +4758,7 @@
         <v>0.118</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0112</v>
+        <v>0.000935</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.118</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0268</v>
+        <v>0.00491</v>
       </c>
     </row>
     <row r="110">
@@ -4838,7 +4838,7 @@
         <v>0.173</v>
       </c>
       <c r="J110" t="n">
-        <v>0.146</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.173</v>
       </c>
       <c r="J111" t="n">
-        <v>0.154</v>
+        <v>0.3455</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.188</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0286</v>
+        <v>0.01144</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.188</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0279</v>
+        <v>0.01258</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.153</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0649</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.153</v>
       </c>
       <c r="J115" t="n">
-        <v>0.0314</v>
+        <v>0.01258</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.16</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0649</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.16</v>
       </c>
       <c r="J117" t="n">
-        <v>0.0927</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.168</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0677</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.168</v>
       </c>
       <c r="J119" t="n">
-        <v>0.0927</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.149</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0605</v>
+        <v>0.0121</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.149</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0279</v>
+        <v>0.00418</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0612</v>
+        <v>0.0624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.881</v>
+        <v>0.883</v>
       </c>
       <c r="H2" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0984</v>
+        <v>0.0973</v>
       </c>
       <c r="J2" t="n">
-        <v>0.153</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="3">
@@ -546,16 +546,16 @@
         <v>0.059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.881</v>
+        <v>0.883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0984</v>
+        <v>0.0973</v>
       </c>
       <c r="J3" t="n">
         <v>0.1475</v>
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.64</v>
+        <v>0.613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G4" t="n">
-        <v>0.828</v>
+        <v>0.829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I4" t="n">
         <v>0.145</v>
       </c>
       <c r="J4" t="n">
-        <v>0.64</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.485</v>
+        <v>0.501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G5" t="n">
-        <v>0.828</v>
+        <v>0.829</v>
       </c>
       <c r="H5" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I5" t="n">
         <v>0.145</v>
       </c>
       <c r="J5" t="n">
-        <v>0.60625</v>
+        <v>0.62625</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.466</v>
+        <v>0.455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G6" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="H6" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5825</v>
+        <v>0.56875</v>
       </c>
     </row>
     <row r="7">
@@ -706,16 +706,16 @@
         <v>0.887</v>
       </c>
       <c r="F7" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G7" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="H7" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I7" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="J7" t="n">
         <v>0.8870000000000001</v>
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
       <c r="H8" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.2033333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -786,16 +786,16 @@
         <v>0.124</v>
       </c>
       <c r="F9" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
       <c r="H9" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0.2066666666666667</v>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.000515</v>
+        <v>0.000488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G10" t="n">
-        <v>0.922</v>
+        <v>0.925</v>
       </c>
       <c r="H10" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0623</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002575</v>
+        <v>0.00244</v>
       </c>
     </row>
     <row r="11">
@@ -866,16 +866,16 @@
         <v>0.000976</v>
       </c>
       <c r="F11" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G11" t="n">
-        <v>0.922</v>
+        <v>0.925</v>
       </c>
       <c r="H11" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0623</v>
       </c>
       <c r="J11" t="n">
         <v>0.00488</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0176</v>
+        <v>0.0181</v>
       </c>
       <c r="F12" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G12" t="n">
-        <v>0.888</v>
+        <v>0.891</v>
       </c>
       <c r="H12" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0837</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0176</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0445</v>
+        <v>0.0411</v>
       </c>
       <c r="F13" t="n">
-        <v>0.848</v>
+        <v>0.851</v>
       </c>
       <c r="G13" t="n">
-        <v>0.888</v>
+        <v>0.891</v>
       </c>
       <c r="H13" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0837</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0445</v>
+        <v>0.0411</v>
       </c>
     </row>
     <row r="14">
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0184</v>
+        <v>0.0225</v>
       </c>
       <c r="F14" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G14" t="n">
-        <v>0.831</v>
+        <v>0.832</v>
       </c>
       <c r="H14" t="n">
         <v>0.164</v>
@@ -998,7 +998,7 @@
         <v>0.174</v>
       </c>
       <c r="J14" t="n">
-        <v>0.046</v>
+        <v>0.05624999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0181</v>
+        <v>0.0209</v>
       </c>
       <c r="F15" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G15" t="n">
-        <v>0.831</v>
+        <v>0.832</v>
       </c>
       <c r="H15" t="n">
         <v>0.164</v>
@@ -1038,7 +1038,7 @@
         <v>0.174</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04525000000000001</v>
+        <v>0.05225</v>
       </c>
     </row>
     <row r="16">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.108</v>
+        <v>0.135</v>
       </c>
       <c r="F16" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G16" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H16" t="n">
         <v>0.164</v>
@@ -1078,7 +1078,7 @@
         <v>0.186</v>
       </c>
       <c r="J16" t="n">
-        <v>0.14625</v>
+        <v>0.16875</v>
       </c>
     </row>
     <row r="17">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0877</v>
+        <v>0.114</v>
       </c>
       <c r="F17" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G17" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H17" t="n">
         <v>0.164</v>
@@ -1118,7 +1118,7 @@
         <v>0.186</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1461666666666667</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="18">
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="F18" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G18" t="n">
-        <v>0.823</v>
+        <v>0.825</v>
       </c>
       <c r="H18" t="n">
         <v>0.164</v>
@@ -1158,7 +1158,7 @@
         <v>0.187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.14625</v>
+        <v>0.16875</v>
       </c>
     </row>
     <row r="19">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.173</v>
+        <v>0.181</v>
       </c>
       <c r="F19" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G19" t="n">
-        <v>0.823</v>
+        <v>0.825</v>
       </c>
       <c r="H19" t="n">
         <v>0.164</v>
@@ -1198,7 +1198,7 @@
         <v>0.187</v>
       </c>
       <c r="J19" t="n">
-        <v>0.173</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="20">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.207</v>
+        <v>0.218</v>
       </c>
       <c r="F20" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G20" t="n">
-        <v>0.823</v>
+        <v>0.826</v>
       </c>
       <c r="H20" t="n">
         <v>0.164</v>
@@ -1238,7 +1238,7 @@
         <v>0.203</v>
       </c>
       <c r="J20" t="n">
-        <v>0.207</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="21">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.14</v>
+        <v>0.157</v>
       </c>
       <c r="F21" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G21" t="n">
-        <v>0.823</v>
+        <v>0.826</v>
       </c>
       <c r="H21" t="n">
         <v>0.164</v>
@@ -1278,7 +1278,7 @@
         <v>0.203</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.00389</v>
+        <v>0.00383</v>
       </c>
       <c r="F22" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G22" t="n">
-        <v>0.873</v>
+        <v>0.876</v>
       </c>
       <c r="H22" t="n">
         <v>0.164</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0897</v>
+        <v>0.0883</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01945</v>
+        <v>0.01915</v>
       </c>
     </row>
     <row r="23">
@@ -1346,16 +1346,16 @@
         <v>0.00147</v>
       </c>
       <c r="F23" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="G23" t="n">
-        <v>0.873</v>
+        <v>0.876</v>
       </c>
       <c r="H23" t="n">
         <v>0.164</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0897</v>
+        <v>0.0883</v>
       </c>
       <c r="J23" t="n">
         <v>0.00735</v>
@@ -1398,7 +1398,7 @@
         <v>0.174</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4389999999999999</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="25">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.224</v>
+        <v>0.22</v>
       </c>
       <c r="F26" t="n">
         <v>0.87</v>
@@ -1478,7 +1478,7 @@
         <v>0.222</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3733333333333334</v>
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0929</v>
+        <v>0.09</v>
       </c>
       <c r="F28" t="n">
         <v>0.87</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>0.199</v>
@@ -1558,7 +1558,7 @@
         <v>0.211</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3725</v>
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -1589,7 +1589,7 @@
         <v>0.87</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>0.199</v>
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.439</v>
+        <v>0.424</v>
       </c>
       <c r="F30" t="n">
         <v>0.87</v>
       </c>
       <c r="G30" t="n">
-        <v>0.841</v>
+        <v>0.84</v>
       </c>
       <c r="H30" t="n">
         <v>0.199</v>
       </c>
       <c r="I30" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4389999999999999</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="31">
@@ -1669,13 +1669,13 @@
         <v>0.87</v>
       </c>
       <c r="G31" t="n">
-        <v>0.841</v>
+        <v>0.84</v>
       </c>
       <c r="H31" t="n">
         <v>0.199</v>
       </c>
       <c r="I31" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="J31" t="n">
         <v>0.315</v>
@@ -1718,7 +1718,7 @@
         <v>0.064</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3725</v>
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.135</v>
+        <v>0.172</v>
       </c>
       <c r="F36" t="n">
         <v>0.779</v>
       </c>
       <c r="G36" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H36" t="n">
         <v>0.244</v>
@@ -1878,7 +1878,7 @@
         <v>0.235</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3375</v>
+        <v>0.4299999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.14</v>
+        <v>0.221</v>
       </c>
       <c r="F37" t="n">
         <v>0.779</v>
       </c>
       <c r="G37" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H37" t="n">
         <v>0.244</v>
@@ -1918,7 +1918,7 @@
         <v>0.235</v>
       </c>
       <c r="J37" t="n">
-        <v>0.35</v>
+        <v>0.5525</v>
       </c>
     </row>
     <row r="38">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.658</v>
+        <v>0.722</v>
       </c>
       <c r="F38" t="n">
         <v>0.779</v>
       </c>
       <c r="G38" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="H38" t="n">
         <v>0.244</v>
@@ -1958,7 +1958,7 @@
         <v>0.209</v>
       </c>
       <c r="J38" t="n">
-        <v>0.658</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="39">
@@ -1989,7 +1989,7 @@
         <v>0.779</v>
       </c>
       <c r="G39" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="H39" t="n">
         <v>0.244</v>
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.534</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F40" t="n">
         <v>0.779</v>
       </c>
       <c r="G40" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="H40" t="n">
         <v>0.244</v>
       </c>
       <c r="I40" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="J40" t="n">
-        <v>0.658</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="41">
@@ -2069,13 +2069,13 @@
         <v>0.779</v>
       </c>
       <c r="G41" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="H41" t="n">
         <v>0.244</v>
       </c>
       <c r="I41" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.53</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F42" t="n">
         <v>0.779</v>
       </c>
       <c r="G42" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H42" t="n">
         <v>0.244</v>
@@ -2118,7 +2118,7 @@
         <v>0.223</v>
       </c>
       <c r="J42" t="n">
-        <v>0.658</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="43">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.669</v>
+        <v>0.632</v>
       </c>
       <c r="F43" t="n">
         <v>0.779</v>
       </c>
       <c r="G43" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H43" t="n">
         <v>0.244</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0016</v>
+        <v>0.00161</v>
       </c>
       <c r="F44" t="n">
         <v>0.779</v>
@@ -2198,7 +2198,7 @@
         <v>0.101</v>
       </c>
       <c r="J44" t="n">
-        <v>0.008</v>
+        <v>0.00805</v>
       </c>
     </row>
     <row r="45">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0167</v>
+        <v>0.0166</v>
       </c>
       <c r="F46" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G46" t="n">
-        <v>0.821</v>
+        <v>0.824</v>
       </c>
       <c r="H46" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I46" t="n">
         <v>0.187</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02783333333333333</v>
+        <v>0.02766666666666667</v>
       </c>
     </row>
     <row r="47">
@@ -2306,13 +2306,13 @@
         <v>0.0186</v>
       </c>
       <c r="F47" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G47" t="n">
-        <v>0.821</v>
+        <v>0.824</v>
       </c>
       <c r="H47" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I47" t="n">
         <v>0.187</v>
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.835</v>
+        <v>0.848</v>
       </c>
       <c r="F48" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G48" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="H48" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I48" t="n">
         <v>0.198</v>
       </c>
       <c r="J48" t="n">
-        <v>0.835</v>
+        <v>0.8480000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.205</v>
+        <v>0.211</v>
       </c>
       <c r="F49" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G49" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="H49" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I49" t="n">
         <v>0.198</v>
       </c>
       <c r="J49" t="n">
-        <v>0.205</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.009769999999999999</v>
+        <v>0.009730000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G50" t="n">
-        <v>0.833</v>
+        <v>0.837</v>
       </c>
       <c r="H50" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I50" t="n">
         <v>0.097</v>
       </c>
       <c r="J50" t="n">
-        <v>0.024425</v>
+        <v>0.024325</v>
       </c>
     </row>
     <row r="51">
@@ -2466,13 +2466,13 @@
         <v>0.00963</v>
       </c>
       <c r="F51" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G51" t="n">
-        <v>0.833</v>
+        <v>0.837</v>
       </c>
       <c r="H51" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I51" t="n">
         <v>0.097</v>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0338</v>
+        <v>0.0341</v>
       </c>
       <c r="F52" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G52" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="H52" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I52" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="J52" t="n">
-        <v>0.04225</v>
+        <v>0.042625</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0354</v>
+        <v>0.0355</v>
       </c>
       <c r="F53" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G53" t="n">
-        <v>0.824</v>
+        <v>0.825</v>
       </c>
       <c r="H53" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I53" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="J53" t="n">
-        <v>0.04425</v>
+        <v>0.044375</v>
       </c>
     </row>
     <row r="54">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00197</v>
+        <v>0.00189</v>
       </c>
       <c r="F54" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G54" t="n">
-        <v>0.859</v>
+        <v>0.862</v>
       </c>
       <c r="H54" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I54" t="n">
-        <v>0.157</v>
+        <v>0.156</v>
       </c>
       <c r="J54" t="n">
-        <v>0.009849999999999999</v>
+        <v>0.00945</v>
       </c>
     </row>
     <row r="55">
@@ -2626,16 +2626,16 @@
         <v>0.00577</v>
       </c>
       <c r="F55" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G55" t="n">
-        <v>0.859</v>
+        <v>0.862</v>
       </c>
       <c r="H55" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I55" t="n">
-        <v>0.157</v>
+        <v>0.156</v>
       </c>
       <c r="J55" t="n">
         <v>0.024075</v>
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0362</v>
+        <v>0.0355</v>
       </c>
       <c r="F56" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G56" t="n">
-        <v>0.824</v>
+        <v>0.828</v>
       </c>
       <c r="H56" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I56" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0362</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="57">
@@ -2706,16 +2706,16 @@
         <v>0.0546</v>
       </c>
       <c r="F57" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="G57" t="n">
-        <v>0.824</v>
+        <v>0.828</v>
       </c>
       <c r="H57" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I57" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J57" t="n">
         <v>0.0546</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.0106</v>
+        <v>0.0118</v>
       </c>
       <c r="F58" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>0.167</v>
@@ -2758,7 +2758,7 @@
         <v>0.157</v>
       </c>
       <c r="J58" t="n">
-        <v>0.01325</v>
+        <v>0.01475</v>
       </c>
     </row>
     <row r="59">
@@ -2786,10 +2786,10 @@
         <v>0.00763</v>
       </c>
       <c r="F59" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0.167</v>
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00258</v>
+        <v>0.00294</v>
       </c>
       <c r="F60" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G60" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="H60" t="n">
         <v>0.167</v>
       </c>
       <c r="I60" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="J60" t="n">
-        <v>0.009275</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="61">
@@ -2863,19 +2863,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.00261</v>
+        <v>0.00314</v>
       </c>
       <c r="F61" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G61" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="H61" t="n">
         <v>0.167</v>
       </c>
       <c r="I61" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="J61" t="n">
         <v>0.008400000000000001</v>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.00371</v>
+        <v>0.00388</v>
       </c>
       <c r="F62" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G62" t="n">
-        <v>0.837</v>
+        <v>0.84</v>
       </c>
       <c r="H62" t="n">
         <v>0.167</v>
@@ -2918,7 +2918,7 @@
         <v>0.0997</v>
       </c>
       <c r="J62" t="n">
-        <v>0.009275</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="63">
@@ -2946,10 +2946,10 @@
         <v>0.00336</v>
       </c>
       <c r="F63" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G63" t="n">
-        <v>0.837</v>
+        <v>0.84</v>
       </c>
       <c r="H63" t="n">
         <v>0.167</v>
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.00671</v>
+        <v>0.00699</v>
       </c>
       <c r="F64" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G64" t="n">
-        <v>0.841</v>
+        <v>0.844</v>
       </c>
       <c r="H64" t="n">
         <v>0.167</v>
       </c>
       <c r="I64" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="J64" t="n">
-        <v>0.01118333333333333</v>
+        <v>0.01165</v>
       </c>
     </row>
     <row r="65">
@@ -3026,16 +3026,16 @@
         <v>0.00629</v>
       </c>
       <c r="F65" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G65" t="n">
-        <v>0.841</v>
+        <v>0.844</v>
       </c>
       <c r="H65" t="n">
         <v>0.167</v>
       </c>
       <c r="I65" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="J65" t="n">
         <v>0.009537499999999999</v>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.874</v>
+        <v>0.876</v>
       </c>
       <c r="F66" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G66" t="n">
-        <v>0.734</v>
+        <v>0.737</v>
       </c>
       <c r="H66" t="n">
         <v>0.167</v>
@@ -3078,7 +3078,7 @@
         <v>0.184</v>
       </c>
       <c r="J66" t="n">
-        <v>0.874</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="67">
@@ -3103,13 +3103,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="G67" t="n">
-        <v>0.734</v>
+        <v>0.737</v>
       </c>
       <c r="H67" t="n">
         <v>0.167</v>
@@ -3118,7 +3118,7 @@
         <v>0.184</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9549999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.184</v>
+        <v>0.189</v>
       </c>
       <c r="F68" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G68" t="n">
-        <v>0.821</v>
+        <v>0.822</v>
       </c>
       <c r="H68" t="n">
         <v>0.165</v>
       </c>
       <c r="I68" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="69">
@@ -3186,16 +3186,16 @@
         <v>0.252</v>
       </c>
       <c r="F69" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G69" t="n">
-        <v>0.821</v>
+        <v>0.822</v>
       </c>
       <c r="H69" t="n">
         <v>0.165</v>
       </c>
       <c r="I69" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="J69" t="n">
         <v>0.42</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.731</v>
+        <v>0.713</v>
       </c>
       <c r="F70" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G70" t="n">
         <v>0.762</v>
@@ -3238,7 +3238,7 @@
         <v>0.206</v>
       </c>
       <c r="J70" t="n">
-        <v>0.731</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="71">
@@ -3266,7 +3266,7 @@
         <v>0.464</v>
       </c>
       <c r="F71" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G71" t="n">
         <v>0.762</v>
@@ -3278,7 +3278,7 @@
         <v>0.206</v>
       </c>
       <c r="J71" t="n">
-        <v>0.57</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="72">
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.487</v>
+        <v>0.501</v>
       </c>
       <c r="F72" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G72" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H72" t="n">
         <v>0.165</v>
       </c>
       <c r="I72" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="J72" t="n">
-        <v>0.60875</v>
+        <v>0.62625</v>
       </c>
     </row>
     <row r="73">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.57</v>
+        <v>0.532</v>
       </c>
       <c r="F73" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G73" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H73" t="n">
         <v>0.165</v>
       </c>
       <c r="I73" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="J73" t="n">
-        <v>0.57</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="74">
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.17</v>
+        <v>0.179</v>
       </c>
       <c r="F74" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G74" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="H74" t="n">
         <v>0.165</v>
@@ -3398,7 +3398,7 @@
         <v>0.118</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="75">
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
       <c r="F75" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G75" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="H75" t="n">
         <v>0.165</v>
@@ -3438,7 +3438,7 @@
         <v>0.118</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3125</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="76">
@@ -3463,13 +3463,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.000187</v>
+        <v>0.000179</v>
       </c>
       <c r="F76" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G76" t="n">
-        <v>0.886</v>
+        <v>0.888</v>
       </c>
       <c r="H76" t="n">
         <v>0.165</v>
@@ -3478,7 +3478,7 @@
         <v>0.118</v>
       </c>
       <c r="J76" t="n">
-        <v>0.000935</v>
+        <v>0.000895</v>
       </c>
     </row>
     <row r="77">
@@ -3506,10 +3506,10 @@
         <v>0.000982</v>
       </c>
       <c r="F77" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G77" t="n">
-        <v>0.886</v>
+        <v>0.888</v>
       </c>
       <c r="H77" t="n">
         <v>0.165</v>
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.0536</v>
+        <v>0.0543</v>
       </c>
       <c r="F78" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G78" t="n">
-        <v>0.827</v>
+        <v>0.829</v>
       </c>
       <c r="H78" t="n">
         <v>0.165</v>
       </c>
       <c r="I78" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0536</v>
+        <v>0.0543</v>
       </c>
     </row>
     <row r="79">
@@ -3586,16 +3586,16 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="G79" t="n">
-        <v>0.827</v>
+        <v>0.829</v>
       </c>
       <c r="H79" t="n">
         <v>0.165</v>
       </c>
       <c r="I79" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="J79" t="n">
         <v>0.06909999999999999</v>
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.00286</v>
+        <v>0.00352</v>
       </c>
       <c r="F80" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G80" t="n">
         <v>0.789</v>
       </c>
       <c r="H80" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I80" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0143</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="81">
@@ -3666,19 +3666,19 @@
         <v>0.00377</v>
       </c>
       <c r="F81" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G81" t="n">
         <v>0.789</v>
       </c>
       <c r="H81" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I81" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="J81" t="n">
-        <v>0.01045</v>
+        <v>0.009424999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.0142</v>
+        <v>0.0174</v>
       </c>
       <c r="F82" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G82" t="n">
         <v>0.799</v>
       </c>
       <c r="H82" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I82" t="n">
         <v>0.153</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0203</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="83">
@@ -3743,22 +3743,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.00629</v>
+        <v>0.00919</v>
       </c>
       <c r="F83" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G83" t="n">
         <v>0.799</v>
       </c>
       <c r="H83" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I83" t="n">
         <v>0.153</v>
       </c>
       <c r="J83" t="n">
-        <v>0.01048333333333333</v>
+        <v>0.01531666666666667</v>
       </c>
     </row>
     <row r="84">
@@ -3783,22 +3783,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.0173</v>
+        <v>0.0185</v>
       </c>
       <c r="F84" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G84" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="H84" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I84" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0203</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="85">
@@ -3826,19 +3826,19 @@
         <v>0.029</v>
       </c>
       <c r="F85" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G85" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="H85" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I85" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J85" t="n">
-        <v>0.029</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="86">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0203</v>
+        <v>0.0219</v>
       </c>
       <c r="F86" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G86" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="H86" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I86" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0203</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="87">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.029</v>
+        <v>0.0335</v>
       </c>
       <c r="F87" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G87" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="H87" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I87" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="J87" t="n">
-        <v>0.029</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="88">
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0121</v>
+        <v>0.0117</v>
       </c>
       <c r="F88" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I88" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0203</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="89">
@@ -3983,22 +3983,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.00418</v>
+        <v>0.00336</v>
       </c>
       <c r="F89" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="I89" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J89" t="n">
-        <v>0.01045</v>
+        <v>0.009424999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4235,13 +4235,13 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>0.908</v>
       </c>
       <c r="H6" t="n">
-        <v>0.547</v>
+        <v>0.534</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -4272,16 +4272,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G7" t="n">
-        <v>0.883</v>
+        <v>0.9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0264</v>
+        <v>0.0309</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0968</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="8">
@@ -4383,10 +4383,10 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.65</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.642</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -4466,7 +4466,7 @@
         <v>0.451</v>
       </c>
       <c r="I12" t="n">
-        <v>0.645</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="13">
@@ -4870,10 +4870,10 @@
         <v>0.952</v>
       </c>
       <c r="H23" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="I23" t="n">
-        <v>0.594</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="24">
@@ -5419,16 +5419,16 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G38" t="n">
-        <v>0.844</v>
+        <v>0.855</v>
       </c>
       <c r="H38" t="n">
-        <v>0.531</v>
+        <v>0.519</v>
       </c>
       <c r="I38" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="39">
@@ -5456,16 +5456,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G39" t="n">
-        <v>0.845</v>
+        <v>0.87</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00238</v>
+        <v>0.00271</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00436</v>
+        <v>0.00497</v>
       </c>
     </row>
     <row r="40">
@@ -5567,10 +5567,10 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G42" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -6011,16 +6011,16 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G54" t="n">
-        <v>0.915</v>
+        <v>0.922</v>
       </c>
       <c r="H54" t="n">
-        <v>0.429</v>
+        <v>0.414</v>
       </c>
       <c r="I54" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -6048,16 +6048,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G55" t="n">
-        <v>0.896</v>
+        <v>0.909</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00377</v>
+        <v>0.0067</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0124</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="56">
@@ -6159,10 +6159,10 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.724</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.719</v>
       </c>
       <c r="H58" t="n">
         <v>1</v>
@@ -6603,13 +6603,13 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="G70" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="H70" t="n">
         <v>0.85</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.853</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -6640,16 +6640,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G71" t="n">
         <v>0.867</v>
       </c>
       <c r="H71" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0.145</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="72">
@@ -6751,16 +6751,16 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="G74" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.681</v>
+        <v>0.679</v>
       </c>
       <c r="I74" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="75">
@@ -7235,13 +7235,13 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.867</v>
+        <v>0.853</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0131</v>
+        <v>0.0067</v>
       </c>
       <c r="I87" t="n">
-        <v>0.131</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="88">
@@ -7787,16 +7787,16 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G102" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H102" t="n">
-        <v>0.839</v>
+        <v>0.835</v>
       </c>
       <c r="I102" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="103">
@@ -7824,16 +7824,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G103" t="n">
-        <v>0.915</v>
+        <v>0.928</v>
       </c>
       <c r="H103" t="n">
-        <v>2.21e-05</v>
+        <v>5.42e-05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.000243</v>
+        <v>0.000596</v>
       </c>
     </row>
     <row r="104">
@@ -7935,16 +7935,16 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G106" t="n">
-        <v>0.635</v>
+        <v>0.642</v>
       </c>
       <c r="H106" t="n">
-        <v>0.461</v>
+        <v>0.457</v>
       </c>
       <c r="I106" t="n">
-        <v>0.507</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="107">
@@ -8379,16 +8379,16 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G118" t="n">
-        <v>0.875</v>
+        <v>0.881</v>
       </c>
       <c r="H118" t="n">
-        <v>0.856</v>
+        <v>0.853</v>
       </c>
       <c r="I118" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -8416,16 +8416,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G119" t="n">
-        <v>0.89</v>
+        <v>0.889</v>
       </c>
       <c r="H119" t="n">
-        <v>0.00451</v>
+        <v>0.0248</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0124</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="120">
@@ -8527,16 +8527,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="G122" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="H122" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="I122" t="n">
-        <v>0.484</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="123">
@@ -8971,13 +8971,13 @@
         <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="H134" t="n">
-        <v>0.377</v>
+        <v>0.366</v>
       </c>
       <c r="I134" t="n">
         <v>1</v>
@@ -9008,16 +9008,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G135" t="n">
-        <v>0.858</v>
+        <v>0.867</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0975</v>
+        <v>0.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.179</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="136">
@@ -9119,16 +9119,16 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="G138" t="n">
-        <v>0.775</v>
+        <v>0.792</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0454</v>
+        <v>0.0297</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0713</v>
+        <v>0.0544</v>
       </c>
     </row>
     <row r="139">
@@ -9202,7 +9202,7 @@
         <v>0.363</v>
       </c>
       <c r="I140" t="n">
-        <v>0.645</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="141">
@@ -9603,13 +9603,13 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.897</v>
+        <v>0.884</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0417</v>
+        <v>0.0219</v>
       </c>
       <c r="I151" t="n">
-        <v>0.153</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9714,13 +9714,13 @@
         <v>0.982</v>
       </c>
       <c r="G154" t="n">
-        <v>0.906</v>
+        <v>0.907</v>
       </c>
       <c r="H154" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0883</v>
       </c>
       <c r="I154" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="155">
@@ -10155,10 +10155,10 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G166" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="H166" t="n">
         <v>1</v>
@@ -10192,16 +10192,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G167" t="n">
-        <v>0.859</v>
+        <v>0.884</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0011</v>
+        <v>0.00119</v>
       </c>
       <c r="I167" t="n">
-        <v>0.00242</v>
+        <v>0.00262</v>
       </c>
     </row>
     <row r="168">
@@ -10303,16 +10303,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G170" t="n">
-        <v>0.802</v>
+        <v>0.821</v>
       </c>
       <c r="H170" t="n">
-        <v>0.00099</v>
+        <v>0.000441</v>
       </c>
       <c r="I170" t="n">
-        <v>0.00218</v>
+        <v>0.0009700000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -10747,16 +10747,16 @@
         <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G182" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H182" t="n">
-        <v>0.388</v>
+        <v>0.377</v>
       </c>
       <c r="I182" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -10784,16 +10784,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G183" t="n">
-        <v>0.878</v>
+        <v>0.884</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0131</v>
+        <v>0.0269</v>
       </c>
       <c r="I183" t="n">
-        <v>0.024</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="184">
@@ -10895,16 +10895,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="G186" t="n">
-        <v>0.851</v>
+        <v>0.862</v>
       </c>
       <c r="H186" t="n">
-        <v>0.00637</v>
+        <v>0.00352</v>
       </c>
       <c r="I186" t="n">
-        <v>0.014</v>
+        <v>0.00774</v>
       </c>
     </row>
     <row r="187">
@@ -11339,13 +11339,13 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="G198" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="H198" t="n">
         <v>0.85</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0.853</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -11376,16 +11376,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G199" t="n">
         <v>0.917</v>
       </c>
       <c r="H199" t="n">
-        <v>0.00231</v>
+        <v>0.009690000000000001</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0127</v>
+        <v>0.0533</v>
       </c>
     </row>
     <row r="200">
@@ -11487,16 +11487,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="G202" t="n">
-        <v>0.775</v>
+        <v>0.783</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0454</v>
+        <v>0.0435</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0713</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="203">
@@ -11971,13 +11971,13 @@
         <v>1</v>
       </c>
       <c r="G215" t="n">
-        <v>0.969</v>
+        <v>0.954</v>
       </c>
       <c r="H215" t="n">
-        <v>0.516</v>
+        <v>0.271</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="216">
@@ -12523,16 +12523,16 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G230" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="H230" t="n">
-        <v>0.846</v>
+        <v>0.843</v>
       </c>
       <c r="I230" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="231">
@@ -12560,16 +12560,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G231" t="n">
-        <v>0.887</v>
+        <v>0.899</v>
       </c>
       <c r="H231" t="n">
-        <v>0.000189</v>
+        <v>0.000476</v>
       </c>
       <c r="I231" t="n">
-        <v>0.00052</v>
+        <v>0.00131</v>
       </c>
     </row>
     <row r="232">
@@ -12671,16 +12671,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G234" t="n">
-        <v>0.74</v>
+        <v>0.747</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0223</v>
+        <v>0.0209</v>
       </c>
       <c r="I234" t="n">
-        <v>0.035</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="235">
@@ -13115,16 +13115,16 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G246" t="n">
-        <v>0.868</v>
+        <v>0.874</v>
       </c>
       <c r="H246" t="n">
-        <v>0.717</v>
+        <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -13152,16 +13152,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G247" t="n">
-        <v>0.926</v>
+        <v>0.925</v>
       </c>
       <c r="H247" t="n">
-        <v>0.000178</v>
+        <v>0.00156</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.008580000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -13263,16 +13263,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="G250" t="n">
-        <v>0.84</v>
+        <v>0.845</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0141</v>
+        <v>0.013</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0222</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="251">
@@ -13707,13 +13707,13 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="G262" t="n">
-        <v>0.883</v>
+        <v>0.892</v>
       </c>
       <c r="H262" t="n">
-        <v>0.846</v>
+        <v>0.841</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -13744,16 +13744,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G263" t="n">
-        <v>0.917</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H263" t="n">
-        <v>0.00231</v>
+        <v>0.0023</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0127</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="264">
@@ -13855,16 +13855,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="G266" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
       <c r="H266" t="n">
-        <v>0.16</v>
+        <v>0.118</v>
       </c>
       <c r="I266" t="n">
-        <v>0.196</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="267">
@@ -14342,10 +14342,10 @@
         <v>0.969</v>
       </c>
       <c r="H279" t="n">
-        <v>0.516</v>
+        <v>0.514</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -14450,13 +14450,13 @@
         <v>0.982</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>0.238</v>
+        <v>0.241</v>
       </c>
       <c r="I282" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="283">
@@ -14891,16 +14891,16 @@
         <v>5</v>
       </c>
       <c r="F294" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G294" t="n">
-        <v>0.831</v>
+        <v>0.842</v>
       </c>
       <c r="H294" t="n">
-        <v>0.681</v>
+        <v>0.672</v>
       </c>
       <c r="I294" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="295">
@@ -14928,16 +14928,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G295" t="n">
-        <v>0.887</v>
+        <v>0.913</v>
       </c>
       <c r="H295" t="n">
-        <v>0.000189</v>
+        <v>0.000171</v>
       </c>
       <c r="I295" t="n">
-        <v>0.00052</v>
+        <v>0.000627</v>
       </c>
     </row>
     <row r="296">
@@ -15039,16 +15039,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G298" t="n">
-        <v>0.729</v>
+        <v>0.747</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0336</v>
+        <v>0.0209</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0462</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="299">
@@ -15483,16 +15483,16 @@
         <v>5</v>
       </c>
       <c r="F310" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G310" t="n">
-        <v>0.901</v>
+        <v>0.908</v>
       </c>
       <c r="H310" t="n">
-        <v>0.701</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I310" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -15520,16 +15520,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G311" t="n">
-        <v>0.926</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H311" t="n">
-        <v>0.000178</v>
+        <v>0.000267</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.00294</v>
       </c>
     </row>
     <row r="312">
@@ -15631,16 +15631,16 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="G314" t="n">
-        <v>0.819</v>
+        <v>0.83</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0461</v>
+        <v>0.0305</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0592</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="315">
@@ -16075,10 +16075,10 @@
         <v>5</v>
       </c>
       <c r="F326" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G326" t="n">
         <v>0.867</v>
-      </c>
-      <c r="G326" t="n">
-        <v>0.858</v>
       </c>
       <c r="H326" t="n">
         <v>1</v>
@@ -16112,16 +16112,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.767</v>
+        <v>0.792</v>
       </c>
       <c r="G327" t="n">
-        <v>0.867</v>
+        <v>0.883</v>
       </c>
       <c r="H327" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I327" t="n">
-        <v>0.145</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="328">
@@ -16223,16 +16223,16 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="G330" t="n">
-        <v>0.775</v>
+        <v>0.792</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0454</v>
+        <v>0.0297</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0713</v>
+        <v>0.0544</v>
       </c>
     </row>
     <row r="331">
@@ -16676,7 +16676,7 @@
         <v>0.245</v>
       </c>
       <c r="I342" t="n">
-        <v>0.539</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="343">
@@ -16710,10 +16710,10 @@
         <v>0.887</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0238</v>
+        <v>0.0229</v>
       </c>
       <c r="I343" t="n">
-        <v>0.131</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="344">
@@ -16818,13 +16818,13 @@
         <v>0.982</v>
       </c>
       <c r="G346" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="H346" t="n">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="I346" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="347">
@@ -17259,16 +17259,16 @@
         <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="G358" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H358" t="n">
-        <v>0.839</v>
+        <v>0.835</v>
       </c>
       <c r="I358" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="359">
@@ -17296,16 +17296,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.606</v>
+        <v>0.638</v>
       </c>
       <c r="G359" t="n">
-        <v>0.887</v>
+        <v>0.913</v>
       </c>
       <c r="H359" t="n">
-        <v>0.000189</v>
+        <v>0.000171</v>
       </c>
       <c r="I359" t="n">
-        <v>0.00052</v>
+        <v>0.000627</v>
       </c>
     </row>
     <row r="360">
@@ -17407,16 +17407,16 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G362" t="n">
-        <v>0.76</v>
+        <v>0.779</v>
       </c>
       <c r="H362" t="n">
-        <v>0.00899</v>
+        <v>0.00494</v>
       </c>
       <c r="I362" t="n">
-        <v>0.0165</v>
+        <v>0.00906</v>
       </c>
     </row>
     <row r="363">
@@ -17851,10 +17851,10 @@
         <v>5</v>
       </c>
       <c r="F374" t="n">
-        <v>0.884</v>
+        <v>0.891</v>
       </c>
       <c r="G374" t="n">
-        <v>0.881</v>
+        <v>0.887</v>
       </c>
       <c r="H374" t="n">
         <v>1</v>
@@ -17888,16 +17888,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.754</v>
+        <v>0.779</v>
       </c>
       <c r="G375" t="n">
-        <v>0.887</v>
+        <v>0.9</v>
       </c>
       <c r="H375" t="n">
-        <v>0.00723</v>
+        <v>0.00889</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0159</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="376">
@@ -17999,16 +17999,16 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.724</v>
+        <v>0.728</v>
       </c>
       <c r="G378" t="n">
-        <v>0.844</v>
+        <v>0.855</v>
       </c>
       <c r="H378" t="n">
-        <v>0.009719999999999999</v>
+        <v>0.00558</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0178</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="379">
@@ -18443,13 +18443,13 @@
         <v>5</v>
       </c>
       <c r="F390" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="G390" t="n">
-        <v>0.875</v>
+        <v>0.883</v>
       </c>
       <c r="H390" t="n">
-        <v>0.579</v>
+        <v>0.569</v>
       </c>
       <c r="I390" t="n">
         <v>1</v>
@@ -18480,16 +18480,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="G391" t="n">
         <v>0.833</v>
       </c>
       <c r="H391" t="n">
-        <v>0.329</v>
+        <v>0.617</v>
       </c>
       <c r="I391" t="n">
-        <v>0.329</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="392">
@@ -18591,16 +18591,16 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G394" t="n">
-        <v>0.783</v>
+        <v>0.792</v>
       </c>
       <c r="H394" t="n">
-        <v>0.0154</v>
+        <v>0.0146</v>
       </c>
       <c r="I394" t="n">
-        <v>0.0423</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="395">
@@ -19072,10 +19072,10 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G407" t="n">
-        <v>0.881</v>
+        <v>0.866</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -19192,7 +19192,7 @@
         <v>0.364</v>
       </c>
       <c r="I410" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="411">
@@ -19627,16 +19627,16 @@
         <v>5</v>
       </c>
       <c r="F422" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="G422" t="n">
-        <v>0.831</v>
+        <v>0.842</v>
       </c>
       <c r="H422" t="n">
-        <v>0.422</v>
+        <v>0.409</v>
       </c>
       <c r="I422" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="423">
@@ -19664,16 +19664,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="G423" t="n">
-        <v>0.831</v>
+        <v>0.841</v>
       </c>
       <c r="H423" t="n">
-        <v>0.159</v>
+        <v>0.29</v>
       </c>
       <c r="I423" t="n">
-        <v>0.175</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="424">
@@ -19775,16 +19775,16 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G426" t="n">
-        <v>0.823</v>
+        <v>0.832</v>
       </c>
       <c r="H426" t="n">
-        <v>0.000262</v>
+        <v>0.000217</v>
       </c>
       <c r="I426" t="n">
-        <v>0.000961</v>
+        <v>0.000597</v>
       </c>
     </row>
     <row r="427">
@@ -20219,16 +20219,16 @@
         <v>5</v>
       </c>
       <c r="F438" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="G438" t="n">
-        <v>0.895</v>
+        <v>0.901</v>
       </c>
       <c r="H438" t="n">
-        <v>0.465</v>
+        <v>0.453</v>
       </c>
       <c r="I438" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -20256,16 +20256,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G439" t="n">
-        <v>0.855</v>
+        <v>0.853</v>
       </c>
       <c r="H439" t="n">
-        <v>0.199</v>
+        <v>0.412</v>
       </c>
       <c r="I439" t="n">
-        <v>0.199</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="440">
@@ -20367,16 +20367,16 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="G442" t="n">
-        <v>0.859</v>
+        <v>0.863</v>
       </c>
       <c r="H442" t="n">
-        <v>0.00122</v>
+        <v>0.00158</v>
       </c>
       <c r="I442" t="n">
-        <v>0.00447</v>
+        <v>0.00434</v>
       </c>
     </row>
     <row r="443">
@@ -20811,10 +20811,10 @@
         <v>5</v>
       </c>
       <c r="F454" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G454" t="n">
         <v>0.842</v>
-      </c>
-      <c r="G454" t="n">
-        <v>0.85</v>
       </c>
       <c r="H454" t="n">
         <v>1</v>
@@ -20848,16 +20848,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="G455" t="n">
-        <v>0.833</v>
+        <v>0.842</v>
       </c>
       <c r="H455" t="n">
-        <v>0.329</v>
+        <v>0.501</v>
       </c>
       <c r="I455" t="n">
-        <v>0.329</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="456">
@@ -20959,16 +20959,16 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G458" t="n">
-        <v>0.792</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H458" t="n">
-        <v>0.00997</v>
+        <v>0.00579</v>
       </c>
       <c r="I458" t="n">
-        <v>0.0423</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="459">
@@ -21406,13 +21406,13 @@
         <v>0.983</v>
       </c>
       <c r="G470" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="H470" t="n">
-        <v>0.369</v>
+        <v>0.212</v>
       </c>
       <c r="I470" t="n">
-        <v>0.676</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="471">
@@ -21440,16 +21440,16 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G471" t="n">
-        <v>0.849</v>
+        <v>0.838</v>
       </c>
       <c r="H471" t="n">
-        <v>0.799</v>
+        <v>0.619</v>
       </c>
       <c r="I471" t="n">
-        <v>0.977</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="472">
@@ -21554,13 +21554,13 @@
         <v>0.948</v>
       </c>
       <c r="G474" t="n">
-        <v>0.908</v>
+        <v>0.909</v>
       </c>
       <c r="H474" t="n">
-        <v>0.526</v>
+        <v>0.527</v>
       </c>
       <c r="I474" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="475">
@@ -21995,16 +21995,16 @@
         <v>5</v>
       </c>
       <c r="F486" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="G486" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H486" t="n">
-        <v>0.552</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I486" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="487">
@@ -22032,16 +22032,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="G487" t="n">
-        <v>0.873</v>
+        <v>0.899</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0362</v>
+        <v>0.0417</v>
       </c>
       <c r="I487" t="n">
-        <v>0.0569</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="488">
@@ -22143,16 +22143,16 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G490" t="n">
-        <v>0.823</v>
+        <v>0.842</v>
       </c>
       <c r="H490" t="n">
-        <v>0.000262</v>
+        <v>0.000102</v>
       </c>
       <c r="I490" t="n">
-        <v>0.000961</v>
+        <v>0.000561</v>
       </c>
     </row>
     <row r="491">
@@ -22587,16 +22587,16 @@
         <v>5</v>
       </c>
       <c r="F502" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="G502" t="n">
-        <v>0.875</v>
+        <v>0.867</v>
       </c>
       <c r="H502" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="I502" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -22624,16 +22624,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G503" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="H503" t="n">
-        <v>0.149</v>
+        <v>0.246</v>
       </c>
       <c r="I503" t="n">
-        <v>0.164</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="504">
@@ -22735,16 +22735,16 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="G506" t="n">
-        <v>0.863</v>
+        <v>0.874</v>
       </c>
       <c r="H506" t="n">
-        <v>0.00105</v>
+        <v>0.000507</v>
       </c>
       <c r="I506" t="n">
-        <v>0.00447</v>
+        <v>0.00279</v>
       </c>
     </row>
     <row r="507">
@@ -23179,13 +23179,13 @@
         <v>5</v>
       </c>
       <c r="F518" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="G518" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="H518" t="n">
-        <v>0.732</v>
+        <v>0.727</v>
       </c>
       <c r="I518" t="n">
         <v>1</v>
@@ -23216,16 +23216,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="G519" t="n">
-        <v>0.858</v>
+        <v>0.867</v>
       </c>
       <c r="H519" t="n">
-        <v>0.133</v>
+        <v>0.225</v>
       </c>
       <c r="I519" t="n">
-        <v>0.183</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="520">
@@ -23327,16 +23327,16 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G522" t="n">
-        <v>0.783</v>
+        <v>0.8</v>
       </c>
       <c r="H522" t="n">
-        <v>0.0154</v>
+        <v>0.009310000000000001</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0423</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="523">
@@ -23808,16 +23808,16 @@
         <v>6</v>
       </c>
       <c r="F535" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G535" t="n">
-        <v>0.897</v>
+        <v>0.884</v>
       </c>
       <c r="H535" t="n">
-        <v>0.783</v>
+        <v>1</v>
       </c>
       <c r="I535" t="n">
-        <v>0.977</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -23922,13 +23922,13 @@
         <v>0.948</v>
       </c>
       <c r="G538" t="n">
-        <v>0.907</v>
+        <v>0.908</v>
       </c>
       <c r="H538" t="n">
         <v>0.526</v>
       </c>
       <c r="I538" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="539">
@@ -24363,16 +24363,16 @@
         <v>5</v>
       </c>
       <c r="F550" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="G550" t="n">
-        <v>0.792</v>
+        <v>0.803</v>
       </c>
       <c r="H550" t="n">
-        <v>0.846</v>
+        <v>0.843</v>
       </c>
       <c r="I550" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="551">
@@ -24400,16 +24400,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="G551" t="n">
-        <v>0.859</v>
+        <v>0.884</v>
       </c>
       <c r="H551" t="n">
-        <v>0.0631</v>
+        <v>0.0756</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0771</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="552">
@@ -24511,16 +24511,16 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G554" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="H554" t="n">
-        <v>0.00052</v>
+        <v>0.000217</v>
       </c>
       <c r="I554" t="n">
-        <v>0.00143</v>
+        <v>0.000597</v>
       </c>
     </row>
     <row r="555">
@@ -24955,16 +24955,16 @@
         <v>5</v>
       </c>
       <c r="F566" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="G566" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H566" t="n">
-        <v>0.866</v>
+        <v>0.734</v>
       </c>
       <c r="I566" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -24992,16 +24992,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G567" t="n">
-        <v>0.878</v>
+        <v>0.884</v>
       </c>
       <c r="H567" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="I567" t="n">
-        <v>0.109</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="568">
@@ -25103,16 +25103,16 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="G570" t="n">
-        <v>0.857</v>
+        <v>0.868</v>
       </c>
       <c r="H570" t="n">
-        <v>0.00181</v>
+        <v>0.000918</v>
       </c>
       <c r="I570" t="n">
-        <v>0.00498</v>
+        <v>0.00337</v>
       </c>
     </row>
     <row r="571">
@@ -25547,10 +25547,10 @@
         <v>5</v>
       </c>
       <c r="F582" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="G582" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H582" t="n">
         <v>1</v>
@@ -25584,16 +25584,16 @@
         <v>6</v>
       </c>
       <c r="F583" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="G583" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H583" t="n">
-        <v>0.251</v>
+        <v>0.396</v>
       </c>
       <c r="I583" t="n">
-        <v>0.307</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="584">
@@ -25695,16 +25695,16 @@
         <v>9</v>
       </c>
       <c r="F586" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G586" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="H586" t="n">
-        <v>0.00226</v>
+        <v>0.00115</v>
       </c>
       <c r="I586" t="n">
-        <v>0.0249</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="587">
@@ -25778,7 +25778,7 @@
         <v>0.434</v>
       </c>
       <c r="I588" t="n">
-        <v>0.645</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="589">
@@ -26148,7 +26148,7 @@
         <v>0.213</v>
       </c>
       <c r="I598" t="n">
-        <v>0.539</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="599">
@@ -26176,16 +26176,16 @@
         <v>6</v>
       </c>
       <c r="F599" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G599" t="n">
-        <v>0.871</v>
+        <v>0.859</v>
       </c>
       <c r="H599" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
       <c r="I599" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="600">
@@ -26290,13 +26290,13 @@
         <v>0.948</v>
       </c>
       <c r="G602" t="n">
-        <v>0.911</v>
+        <v>0.912</v>
       </c>
       <c r="H602" t="n">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="I602" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="603">
@@ -26731,16 +26731,16 @@
         <v>5</v>
       </c>
       <c r="F614" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="G614" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="H614" t="n">
-        <v>0.552</v>
+        <v>0.541</v>
       </c>
       <c r="I614" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="615">
@@ -26768,16 +26768,16 @@
         <v>6</v>
       </c>
       <c r="F615" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="G615" t="n">
-        <v>0.859</v>
+        <v>0.884</v>
       </c>
       <c r="H615" t="n">
-        <v>0.0631</v>
+        <v>0.0756</v>
       </c>
       <c r="I615" t="n">
-        <v>0.0771</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="616">
@@ -26879,16 +26879,16 @@
         <v>9</v>
       </c>
       <c r="F618" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G618" t="n">
-        <v>0.854</v>
+        <v>0.874</v>
       </c>
       <c r="H618" t="n">
-        <v>2.55e-05</v>
+        <v>7.720000000000001e-06</v>
       </c>
       <c r="I618" t="n">
-        <v>0.00028</v>
+        <v>8.49e-05</v>
       </c>
     </row>
     <row r="619">
@@ -27323,16 +27323,16 @@
         <v>5</v>
       </c>
       <c r="F630" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="G630" t="n">
-        <v>0.869</v>
+        <v>0.875</v>
       </c>
       <c r="H630" t="n">
-        <v>0.863</v>
+        <v>0.86</v>
       </c>
       <c r="I630" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631">
@@ -27360,16 +27360,16 @@
         <v>6</v>
       </c>
       <c r="F631" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G631" t="n">
-        <v>0.865</v>
+        <v>0.871</v>
       </c>
       <c r="H631" t="n">
-        <v>0.109</v>
+        <v>0.239</v>
       </c>
       <c r="I631" t="n">
-        <v>0.15</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="632">
@@ -27471,16 +27471,16 @@
         <v>9</v>
       </c>
       <c r="F634" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="G634" t="n">
-        <v>0.882</v>
+        <v>0.892</v>
       </c>
       <c r="H634" t="n">
-        <v>0.000169</v>
+        <v>6.81e-05</v>
       </c>
       <c r="I634" t="n">
-        <v>0.00186</v>
+        <v>0.000749</v>
       </c>
     </row>
     <row r="635">
@@ -27915,13 +27915,13 @@
         <v>5</v>
       </c>
       <c r="F646" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="G646" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H646" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="I646" t="n">
         <v>1</v>
@@ -27952,16 +27952,16 @@
         <v>6</v>
       </c>
       <c r="F647" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="G647" t="n">
-        <v>0.858</v>
+        <v>0.875</v>
       </c>
       <c r="H647" t="n">
-        <v>0.133</v>
+        <v>0.161</v>
       </c>
       <c r="I647" t="n">
-        <v>0.183</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="648">
@@ -28063,16 +28063,16 @@
         <v>9</v>
       </c>
       <c r="F650" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G650" t="n">
-        <v>0.742</v>
+        <v>0.75</v>
       </c>
       <c r="H650" t="n">
-        <v>0.0944</v>
+        <v>0.0919</v>
       </c>
       <c r="I650" t="n">
-        <v>0.13</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="651">
@@ -28140,13 +28140,13 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="G652" t="n">
-        <v>0.85</v>
+        <v>0.858</v>
       </c>
       <c r="H652" t="n">
-        <v>0.493</v>
+        <v>0.387</v>
       </c>
       <c r="I652" t="n">
-        <v>0.645</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="653">
@@ -28544,16 +28544,16 @@
         <v>6</v>
       </c>
       <c r="F663" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G663" t="n">
         <v>0.982</v>
       </c>
       <c r="H663" t="n">
-        <v>0.0611</v>
+        <v>0.0616</v>
       </c>
       <c r="I663" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="664">
@@ -28664,7 +28664,7 @@
         <v>0.336</v>
       </c>
       <c r="I666" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="667">
@@ -28732,13 +28732,13 @@
         <v>0.855</v>
       </c>
       <c r="G668" t="n">
-        <v>0.98</v>
+        <v>0.981</v>
       </c>
       <c r="H668" t="n">
-        <v>0.0216</v>
+        <v>0.0207</v>
       </c>
       <c r="I668" t="n">
-        <v>0.238</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="669">
@@ -29099,16 +29099,16 @@
         <v>5</v>
       </c>
       <c r="F678" t="n">
-        <v>0.766</v>
+        <v>0.776</v>
       </c>
       <c r="G678" t="n">
-        <v>0.701</v>
+        <v>0.711</v>
       </c>
       <c r="H678" t="n">
-        <v>0.466</v>
+        <v>0.458</v>
       </c>
       <c r="I678" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="679">
@@ -29136,16 +29136,16 @@
         <v>6</v>
       </c>
       <c r="F679" t="n">
-        <v>0.718</v>
+        <v>0.754</v>
       </c>
       <c r="G679" t="n">
-        <v>0.775</v>
+        <v>0.797</v>
       </c>
       <c r="H679" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I679" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="680">
@@ -29247,16 +29247,16 @@
         <v>9</v>
       </c>
       <c r="F682" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="G682" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="H682" t="n">
-        <v>0.135</v>
+        <v>0.131</v>
       </c>
       <c r="I682" t="n">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="683">
@@ -29324,13 +29324,13 @@
         <v>0.791</v>
       </c>
       <c r="G684" t="n">
-        <v>0.746</v>
+        <v>0.761</v>
       </c>
       <c r="H684" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="I684" t="n">
-        <v>0.75</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="685">
@@ -29691,16 +29691,16 @@
         <v>5</v>
       </c>
       <c r="F694" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="G694" t="n">
-        <v>0.824</v>
+        <v>0.831</v>
       </c>
       <c r="H694" t="n">
-        <v>0.502</v>
+        <v>0.493</v>
       </c>
       <c r="I694" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
@@ -29728,16 +29728,16 @@
         <v>6</v>
       </c>
       <c r="F695" t="n">
-        <v>0.791</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G695" t="n">
-        <v>0.866</v>
+        <v>0.88</v>
       </c>
       <c r="H695" t="n">
-        <v>0.136</v>
+        <v>0.164</v>
       </c>
       <c r="I695" t="n">
-        <v>0.164</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="696">
@@ -29839,16 +29839,16 @@
         <v>9</v>
       </c>
       <c r="F698" t="n">
-        <v>0.714</v>
+        <v>0.719</v>
       </c>
       <c r="G698" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H698" t="n">
-        <v>0.0484</v>
+        <v>0.0463</v>
       </c>
       <c r="I698" t="n">
-        <v>0.0592</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="699">
@@ -29916,13 +29916,13 @@
         <v>0.822</v>
       </c>
       <c r="G700" t="n">
-        <v>0.847</v>
+        <v>0.857</v>
       </c>
       <c r="H700" t="n">
-        <v>0.612</v>
+        <v>0.492</v>
       </c>
       <c r="I700" t="n">
-        <v>0.697</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="701">

--- a/eval/learning-curve/results/statistical_tests_original120.xlsx
+++ b/eval/learning-curve/results/statistical_tests_original120.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0624</v>
+        <v>0.0612</v>
       </c>
       <c r="F2" t="n">
         <v>0.851</v>
@@ -518,7 +518,7 @@
         <v>0.0973</v>
       </c>
       <c r="J2" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.613</v>
+        <v>0.622</v>
       </c>
       <c r="F4" t="n">
         <v>0.851</v>
@@ -598,7 +598,7 @@
         <v>0.145</v>
       </c>
       <c r="J4" t="n">
-        <v>0.613</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.501</v>
+        <v>0.485</v>
       </c>
       <c r="F5" t="n">
         <v>0.851</v>
@@ -638,7 +638,7 @@
         <v>0.145</v>
       </c>
       <c r="J5" t="n">
-        <v>0.62625</v>
+        <v>0.60625</v>
       </c>
     </row>
     <row r="6">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.455</v>
+        <v>0.443</v>
       </c>
       <c r="F6" t="n">
         <v>0.851</v>
       </c>
       <c r="G6" t="n">
-        <v>0.828</v>
+        <v>0.827</v>
       </c>
       <c r="H6" t="n">
         <v>0.114</v>
@@ -678,7 +678,7 @@
         <v>0.185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.56875</v>
+        <v>0.55375</v>
       </c>
     </row>
     <row r="7">
@@ -709,7 +709,7 @@
         <v>0.851</v>
       </c>
       <c r="G7" t="n">
-        <v>0.828</v>
+        <v>0.827</v>
       </c>
       <c r="H7" t="n">
         <v>0.114</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
         <v>0.851</v>
@@ -758,7 +758,7 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2033333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.000488</v>
+        <v>0.000515</v>
       </c>
       <c r="F10" t="n">
         <v>0.851</v>
       </c>
       <c r="G10" t="n">
-        <v>0.925</v>
+        <v>0.924</v>
       </c>
       <c r="H10" t="n">
         <v>0.114</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0623</v>
+        <v>0.0638</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00244</v>
+        <v>0.002575</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.000976</v>
+        <v>0.000973</v>
       </c>
       <c r="F11" t="n">
         <v>0.851</v>
       </c>
       <c r="G11" t="n">
-        <v>0.925</v>
+        <v>0.924</v>
       </c>
       <c r="H11" t="n">
         <v>0.114</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0623</v>
+        <v>0.0638</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00488</v>
+        <v>0.004865</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0181</v>
+        <v>0.0176</v>
       </c>
       <c r="F12" t="n">
         <v>0.851</v>
       </c>
       <c r="G12" t="n">
-        <v>0.891</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="n">
         <v>0.114</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0837</v>
+        <v>0.0844</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0181</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +949,13 @@
         <v>0.851</v>
       </c>
       <c r="G13" t="n">
-        <v>0.891</v>
+        <v>0.89</v>
       </c>
       <c r="H13" t="n">
         <v>0.114</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0837</v>
+        <v>0.0844</v>
       </c>
       <c r="J13" t="n">
         <v>0.0411</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0225</v>
+        <v>0.0209</v>
       </c>
       <c r="F14" t="n">
         <v>0.798</v>
@@ -998,7 +998,7 @@
         <v>0.174</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05624999999999999</v>
+        <v>0.05225</v>
       </c>
     </row>
     <row r="15">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0209</v>
+        <v>0.0181</v>
       </c>
       <c r="F15" t="n">
         <v>0.798</v>
@@ -1038,7 +1038,7 @@
         <v>0.174</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05225</v>
+        <v>0.04525000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="F16" t="n">
         <v>0.798</v>
       </c>
       <c r="G16" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="H16" t="n">
         <v>0.164</v>
@@ -1078,7 +1078,7 @@
         <v>0.186</v>
       </c>
       <c r="J16" t="n">
-        <v>0.16875</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="17">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="F17" t="n">
         <v>0.798</v>
       </c>
       <c r="G17" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="H17" t="n">
         <v>0.164</v>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="F18" t="n">
         <v>0.798</v>
       </c>
       <c r="G18" t="n">
-        <v>0.825</v>
+        <v>0.824</v>
       </c>
       <c r="H18" t="n">
         <v>0.164</v>
@@ -1158,7 +1158,7 @@
         <v>0.187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.16875</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="19">
@@ -1189,7 +1189,7 @@
         <v>0.798</v>
       </c>
       <c r="G19" t="n">
-        <v>0.825</v>
+        <v>0.824</v>
       </c>
       <c r="H19" t="n">
         <v>0.164</v>
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="F20" t="n">
         <v>0.798</v>
       </c>
       <c r="G20" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="H20" t="n">
         <v>0.164</v>
@@ -1238,7 +1238,7 @@
         <v>0.203</v>
       </c>
       <c r="J20" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="21">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.157</v>
+        <v>0.148</v>
       </c>
       <c r="F21" t="n">
         <v>0.798</v>
       </c>
       <c r="G21" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="H21" t="n">
         <v>0.164</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.00383</v>
+        <v>0.00365</v>
       </c>
       <c r="F22" t="n">
         <v>0.798</v>
@@ -1318,7 +1318,7 @@
         <v>0.0883</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01915</v>
+        <v>0.01825</v>
       </c>
     </row>
     <row r="23">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.09</v>
+        <v>0.0893</v>
       </c>
       <c r="F28" t="n">
         <v>0.87</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="F36" t="n">
         <v>0.779</v>
@@ -1878,7 +1878,7 @@
         <v>0.235</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4299999999999999</v>
+        <v>0.4175</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="F38" t="n">
         <v>0.779</v>
       </c>
       <c r="G38" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="H38" t="n">
         <v>0.244</v>
@@ -1958,7 +1958,7 @@
         <v>0.209</v>
       </c>
       <c r="J38" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="39">
@@ -1989,7 +1989,7 @@
         <v>0.779</v>
       </c>
       <c r="G39" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="H39" t="n">
         <v>0.244</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F40" t="n">
         <v>0.779</v>
@@ -2038,7 +2038,7 @@
         <v>0.219</v>
       </c>
       <c r="J40" t="n">
-        <v>0.705</v>
+        <v>0.7062499999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F42" t="n">
         <v>0.779</v>
@@ -2115,10 +2115,10 @@
         <v>0.244</v>
       </c>
       <c r="I42" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J42" t="n">
-        <v>0.705</v>
+        <v>0.7062499999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2155,7 +2155,7 @@
         <v>0.244</v>
       </c>
       <c r="I43" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J43" t="n">
         <v>0.83625</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.00161</v>
+        <v>0.0016</v>
       </c>
       <c r="F44" t="n">
         <v>0.779</v>
@@ -2198,7 +2198,7 @@
         <v>0.101</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00805</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="45">
@@ -2266,7 +2266,7 @@
         <v>0.0166</v>
       </c>
       <c r="F46" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G46" t="n">
         <v>0.824</v>
@@ -2306,7 +2306,7 @@
         <v>0.0186</v>
       </c>
       <c r="F47" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G47" t="n">
         <v>0.824</v>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.848</v>
+        <v>0.838</v>
       </c>
       <c r="F48" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G48" t="n">
         <v>0.759</v>
@@ -2358,7 +2358,7 @@
         <v>0.198</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8480000000000001</v>
+        <v>0.8379999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2386,7 +2386,7 @@
         <v>0.211</v>
       </c>
       <c r="F49" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G49" t="n">
         <v>0.759</v>
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.009730000000000001</v>
+        <v>0.00975</v>
       </c>
       <c r="F50" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G50" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="H50" t="n">
         <v>0.193</v>
       </c>
       <c r="I50" t="n">
-        <v>0.097</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>0.024325</v>
+        <v>0.024375</v>
       </c>
     </row>
     <row r="51">
@@ -2466,16 +2466,16 @@
         <v>0.00963</v>
       </c>
       <c r="F51" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G51" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="H51" t="n">
         <v>0.193</v>
       </c>
       <c r="I51" t="n">
-        <v>0.097</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0.024075</v>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0341</v>
+        <v>0.0338</v>
       </c>
       <c r="F52" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G52" t="n">
         <v>0.825</v>
@@ -2518,7 +2518,7 @@
         <v>0.11</v>
       </c>
       <c r="J52" t="n">
-        <v>0.042625</v>
+        <v>0.04225</v>
       </c>
     </row>
     <row r="53">
@@ -2546,7 +2546,7 @@
         <v>0.0355</v>
       </c>
       <c r="F53" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G53" t="n">
         <v>0.825</v>
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00189</v>
+        <v>0.00198</v>
       </c>
       <c r="F54" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G54" t="n">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="H54" t="n">
         <v>0.193</v>
@@ -2598,7 +2598,7 @@
         <v>0.156</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00945</v>
+        <v>0.009899999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2626,10 +2626,10 @@
         <v>0.00577</v>
       </c>
       <c r="F55" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G55" t="n">
-        <v>0.862</v>
+        <v>0.861</v>
       </c>
       <c r="H55" t="n">
         <v>0.193</v>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0355</v>
+        <v>0.0359</v>
       </c>
       <c r="F56" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G56" t="n">
-        <v>0.828</v>
+        <v>0.827</v>
       </c>
       <c r="H56" t="n">
         <v>0.193</v>
@@ -2678,7 +2678,7 @@
         <v>0.184</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0355</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="57">
@@ -2706,10 +2706,10 @@
         <v>0.0546</v>
       </c>
       <c r="F57" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="G57" t="n">
-        <v>0.828</v>
+        <v>0.827</v>
       </c>
       <c r="H57" t="n">
         <v>0.193</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.0118</v>
+        <v>0.0111</v>
       </c>
       <c r="F58" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G58" t="n">
         <v>0.8120000000000001</v>
@@ -2758,7 +2758,7 @@
         <v>0.157</v>
       </c>
       <c r="J58" t="n">
-        <v>0.01475</v>
+        <v>0.013875</v>
       </c>
     </row>
     <row r="59">
@@ -2786,7 +2786,7 @@
         <v>0.00763</v>
       </c>
       <c r="F59" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G59" t="n">
         <v>0.8120000000000001</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00294</v>
+        <v>0.00289</v>
       </c>
       <c r="F60" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G60" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="H60" t="n">
         <v>0.167</v>
@@ -2838,7 +2838,7 @@
         <v>0.103</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0097</v>
+        <v>0.009575</v>
       </c>
     </row>
     <row r="61">
@@ -2866,10 +2866,10 @@
         <v>0.00314</v>
       </c>
       <c r="F61" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G61" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="H61" t="n">
         <v>0.167</v>
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.00388</v>
+        <v>0.00383</v>
       </c>
       <c r="F62" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G62" t="n">
-        <v>0.84</v>
+        <v>0.839</v>
       </c>
       <c r="H62" t="n">
         <v>0.167</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0997</v>
+        <v>0.0994</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0097</v>
+        <v>0.009575</v>
       </c>
     </row>
     <row r="63">
@@ -2946,16 +2946,16 @@
         <v>0.00336</v>
       </c>
       <c r="F63" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G63" t="n">
-        <v>0.84</v>
+        <v>0.839</v>
       </c>
       <c r="H63" t="n">
         <v>0.167</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0997</v>
+        <v>0.0994</v>
       </c>
       <c r="J63" t="n">
         <v>0.008400000000000001</v>
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.00699</v>
+        <v>0.00692</v>
       </c>
       <c r="F64" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G64" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="H64" t="n">
         <v>0.167</v>
       </c>
       <c r="I64" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="J64" t="n">
-        <v>0.01165</v>
+        <v>0.01153333333333333</v>
       </c>
     </row>
     <row r="65">
@@ -3026,16 +3026,16 @@
         <v>0.00629</v>
       </c>
       <c r="F65" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G65" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="H65" t="n">
         <v>0.167</v>
       </c>
       <c r="I65" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="J65" t="n">
         <v>0.009537499999999999</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.876</v>
+        <v>0.891</v>
       </c>
       <c r="F66" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G66" t="n">
         <v>0.737</v>
@@ -3078,7 +3078,7 @@
         <v>0.184</v>
       </c>
       <c r="J66" t="n">
-        <v>0.876</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="67">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="F67" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="G67" t="n">
         <v>0.737</v>
@@ -3118,7 +3118,7 @@
         <v>0.184</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0.9549999999999998</v>
       </c>
     </row>
     <row r="68">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.189</v>
+        <v>0.184</v>
       </c>
       <c r="F68" t="n">
         <v>0.787</v>
@@ -3158,7 +3158,7 @@
         <v>0.162</v>
       </c>
       <c r="J68" t="n">
-        <v>0.315</v>
+        <v>0.3066666666666666</v>
       </c>
     </row>
     <row r="69">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
       <c r="F70" t="n">
         <v>0.787</v>
@@ -3238,7 +3238,7 @@
         <v>0.206</v>
       </c>
       <c r="J70" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.206</v>
       </c>
       <c r="J71" t="n">
-        <v>0.532</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="72">
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.501</v>
+        <v>0.505</v>
       </c>
       <c r="F72" t="n">
         <v>0.787</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H72" t="n">
         <v>0.165</v>
       </c>
       <c r="I72" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="J72" t="n">
-        <v>0.62625</v>
+        <v>0.63125</v>
       </c>
     </row>
     <row r="73">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.532</v>
+        <v>0.57</v>
       </c>
       <c r="F73" t="n">
         <v>0.787</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H73" t="n">
         <v>0.165</v>
       </c>
       <c r="I73" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="J73" t="n">
-        <v>0.532</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="74">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.179</v>
+        <v>0.175</v>
       </c>
       <c r="F74" t="n">
         <v>0.787</v>
@@ -3398,7 +3398,7 @@
         <v>0.118</v>
       </c>
       <c r="J74" t="n">
-        <v>0.315</v>
+        <v>0.3066666666666666</v>
       </c>
     </row>
     <row r="75">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F75" t="n">
         <v>0.787</v>
@@ -3438,7 +3438,7 @@
         <v>0.118</v>
       </c>
       <c r="J75" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="76">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.000179</v>
+        <v>0.000187</v>
       </c>
       <c r="F76" t="n">
         <v>0.787</v>
@@ -3478,7 +3478,7 @@
         <v>0.118</v>
       </c>
       <c r="J76" t="n">
-        <v>0.000895</v>
+        <v>0.000935</v>
       </c>
     </row>
     <row r="77">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.0543</v>
+        <v>0.0538</v>
       </c>
       <c r="F78" t="n">
         <v>0.787</v>
@@ -3555,10 +3555,10 @@
         <v>0.165</v>
       </c>
       <c r="I78" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0543</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="79">
@@ -3595,7 +3595,7 @@
         <v>0.165</v>
       </c>
       <c r="I79" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J79" t="n">
         <v>0.06909999999999999</v>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.00352</v>
+        <v>0.00322</v>
       </c>
       <c r="F80" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G80" t="n">
         <v>0.789</v>
@@ -3638,7 +3638,7 @@
         <v>0.189</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0176</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="81">
@@ -3666,7 +3666,7 @@
         <v>0.00377</v>
       </c>
       <c r="F81" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G81" t="n">
         <v>0.789</v>
@@ -3706,10 +3706,10 @@
         <v>0.0174</v>
       </c>
       <c r="F82" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G82" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H82" t="n">
         <v>0.177</v>
@@ -3746,10 +3746,10 @@
         <v>0.00919</v>
       </c>
       <c r="F83" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G83" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H83" t="n">
         <v>0.177</v>
@@ -3786,16 +3786,16 @@
         <v>0.0185</v>
       </c>
       <c r="F84" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G84" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H84" t="n">
         <v>0.177</v>
       </c>
       <c r="I84" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="J84" t="n">
         <v>0.0219</v>
@@ -3826,16 +3826,16 @@
         <v>0.029</v>
       </c>
       <c r="F85" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G85" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H85" t="n">
         <v>0.177</v>
       </c>
       <c r="I85" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="J85" t="n">
         <v>0.0335</v>
@@ -3866,16 +3866,16 @@
         <v>0.0219</v>
       </c>
       <c r="F86" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G86" t="n">
-        <v>0.803</v>
+        <v>0.802</v>
       </c>
       <c r="H86" t="n">
         <v>0.177</v>
       </c>
       <c r="I86" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="J86" t="n">
         <v>0.0219</v>
@@ -3906,16 +3906,16 @@
         <v>0.0335</v>
       </c>
       <c r="F87" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G87" t="n">
-        <v>0.803</v>
+        <v>0.802</v>
       </c>
       <c r="H87" t="n">
         <v>0.177</v>
       </c>
       <c r="I87" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="J87" t="n">
         <v>0.0335</v>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0117</v>
+        <v>0.0112</v>
       </c>
       <c r="F88" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G88" t="n">
         <v>0.8129999999999999</v>
@@ -3986,7 +3986,7 @@
         <v>0.00336</v>
       </c>
       <c r="F89" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="G89" t="n">
         <v>0.8129999999999999</v>
@@ -4272,16 +4272,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G7" t="n">
         <v>0.9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0309</v>
+        <v>0.0206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.113</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="8">
@@ -4870,10 +4870,10 @@
         <v>0.952</v>
       </c>
       <c r="H23" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.497</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="24">
@@ -5456,16 +5456,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G39" t="n">
         <v>0.87</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00271</v>
+        <v>0.00152</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00497</v>
+        <v>0.00279</v>
       </c>
     </row>
     <row r="40">
@@ -6048,16 +6048,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G55" t="n">
         <v>0.909</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0067</v>
+        <v>0.00413</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0244</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="56">
@@ -6640,16 +6640,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G71" t="n">
         <v>0.867</v>
       </c>
       <c r="H71" t="n">
-        <v>0.17</v>
+        <v>0.126</v>
       </c>
       <c r="I71" t="n">
-        <v>0.267</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="72">
@@ -7238,10 +7238,10 @@
         <v>0.853</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0067</v>
+        <v>0.00691</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0737</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="88">
@@ -7824,16 +7824,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G103" t="n">
         <v>0.928</v>
       </c>
       <c r="H103" t="n">
-        <v>5.42e-05</v>
+        <v>2.61e-05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.000596</v>
+        <v>0.000287</v>
       </c>
     </row>
     <row r="104">
@@ -8416,16 +8416,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G119" t="n">
         <v>0.889</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0248</v>
+        <v>0.0109</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0493</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="120">
@@ -9008,16 +9008,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G135" t="n">
-        <v>0.867</v>
+        <v>0.858</v>
       </c>
       <c r="H135" t="n">
-        <v>0.17</v>
+        <v>0.178</v>
       </c>
       <c r="I135" t="n">
-        <v>0.267</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="136">
@@ -9122,13 +9122,13 @@
         <v>0.658</v>
       </c>
       <c r="G138" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0297</v>
+        <v>0.0435</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0544</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="139">
@@ -9603,13 +9603,13 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.884</v>
+        <v>0.882</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0219</v>
+        <v>0.022</v>
       </c>
       <c r="I151" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="152">
@@ -9714,13 +9714,13 @@
         <v>0.982</v>
       </c>
       <c r="G154" t="n">
-        <v>0.907</v>
+        <v>0.906</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0883</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="155">
@@ -10192,16 +10192,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G167" t="n">
-        <v>0.884</v>
+        <v>0.87</v>
       </c>
       <c r="H167" t="n">
-        <v>0.00119</v>
+        <v>0.00152</v>
       </c>
       <c r="I167" t="n">
-        <v>0.00262</v>
+        <v>0.00279</v>
       </c>
     </row>
     <row r="168">
@@ -10306,13 +10306,13 @@
         <v>0.579</v>
       </c>
       <c r="G170" t="n">
-        <v>0.821</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H170" t="n">
-        <v>0.000441</v>
+        <v>0.000856</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0009700000000000001</v>
+        <v>0.00188</v>
       </c>
     </row>
     <row r="171">
@@ -10784,16 +10784,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G183" t="n">
-        <v>0.884</v>
+        <v>0.876</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0269</v>
+        <v>0.0288</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0493</v>
+        <v>0.0528</v>
       </c>
     </row>
     <row r="184">
@@ -10898,13 +10898,13 @@
         <v>0.728</v>
       </c>
       <c r="G186" t="n">
-        <v>0.862</v>
+        <v>0.856</v>
       </c>
       <c r="H186" t="n">
-        <v>0.00352</v>
+        <v>0.00577</v>
       </c>
       <c r="I186" t="n">
-        <v>0.00774</v>
+        <v>0.0127</v>
       </c>
     </row>
     <row r="187">
@@ -11376,16 +11376,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G199" t="n">
         <v>0.917</v>
       </c>
       <c r="H199" t="n">
-        <v>0.009690000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0533</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="200">
@@ -11974,10 +11974,10 @@
         <v>0.954</v>
       </c>
       <c r="H215" t="n">
-        <v>0.271</v>
+        <v>0.274</v>
       </c>
       <c r="I215" t="n">
-        <v>0.497</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="216">
@@ -12560,16 +12560,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G231" t="n">
         <v>0.899</v>
       </c>
       <c r="H231" t="n">
-        <v>0.000476</v>
+        <v>0.000248</v>
       </c>
       <c r="I231" t="n">
-        <v>0.00131</v>
+        <v>0.000682</v>
       </c>
     </row>
     <row r="232">
@@ -12680,7 +12680,7 @@
         <v>0.0209</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0287</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="235">
@@ -13152,16 +13152,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G247" t="n">
         <v>0.925</v>
       </c>
       <c r="H247" t="n">
-        <v>0.00156</v>
+        <v>0.0005509999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>0.008580000000000001</v>
+        <v>0.00303</v>
       </c>
     </row>
     <row r="248">
@@ -13744,16 +13744,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G263" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0023</v>
+        <v>0.00136</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0253</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="264">
@@ -13858,13 +13858,13 @@
         <v>0.658</v>
       </c>
       <c r="G266" t="n">
-        <v>0.758</v>
+        <v>0.75</v>
       </c>
       <c r="H266" t="n">
-        <v>0.118</v>
+        <v>0.157</v>
       </c>
       <c r="I266" t="n">
-        <v>0.144</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="267">
@@ -14342,10 +14342,10 @@
         <v>0.969</v>
       </c>
       <c r="H279" t="n">
-        <v>0.514</v>
+        <v>0.516</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -14450,13 +14450,13 @@
         <v>0.982</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="I282" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="283">
@@ -14928,16 +14928,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G295" t="n">
         <v>0.913</v>
       </c>
       <c r="H295" t="n">
-        <v>0.000171</v>
+        <v>8.58e-05</v>
       </c>
       <c r="I295" t="n">
-        <v>0.000627</v>
+        <v>0.000315</v>
       </c>
     </row>
     <row r="296">
@@ -15042,13 +15042,13 @@
         <v>0.579</v>
       </c>
       <c r="G298" t="n">
-        <v>0.747</v>
+        <v>0.737</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0209</v>
+        <v>0.0319</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0287</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="299">
@@ -15520,16 +15520,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G311" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="H311" t="n">
-        <v>0.000267</v>
+        <v>0.000141</v>
       </c>
       <c r="I311" t="n">
-        <v>0.00294</v>
+        <v>0.00155</v>
       </c>
     </row>
     <row r="312">
@@ -15634,13 +15634,13 @@
         <v>0.728</v>
       </c>
       <c r="G314" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0305</v>
+        <v>0.0441</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0419</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="315">
@@ -16112,16 +16112,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G327" t="n">
         <v>0.883</v>
       </c>
       <c r="H327" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0558</v>
       </c>
       <c r="I327" t="n">
-        <v>0.218</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="328">
@@ -16226,13 +16226,13 @@
         <v>0.658</v>
       </c>
       <c r="G330" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0297</v>
+        <v>0.0435</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0544</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="331">
@@ -16710,10 +16710,10 @@
         <v>0.887</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0229</v>
+        <v>0.0238</v>
       </c>
       <c r="I343" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="344">
@@ -16818,13 +16818,13 @@
         <v>0.982</v>
       </c>
       <c r="G346" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="H346" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="I346" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="347">
@@ -17296,16 +17296,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="G359" t="n">
         <v>0.913</v>
       </c>
       <c r="H359" t="n">
-        <v>0.000171</v>
+        <v>8.58e-05</v>
       </c>
       <c r="I359" t="n">
-        <v>0.000627</v>
+        <v>0.000315</v>
       </c>
     </row>
     <row r="360">
@@ -17410,13 +17410,13 @@
         <v>0.579</v>
       </c>
       <c r="G362" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="H362" t="n">
-        <v>0.00494</v>
+        <v>0.00826</v>
       </c>
       <c r="I362" t="n">
-        <v>0.00906</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="363">
@@ -17888,16 +17888,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="G375" t="n">
         <v>0.9</v>
       </c>
       <c r="H375" t="n">
-        <v>0.00889</v>
+        <v>0.00535</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0244</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="376">
@@ -18002,13 +18002,13 @@
         <v>0.728</v>
       </c>
       <c r="G378" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
       <c r="H378" t="n">
-        <v>0.00558</v>
+        <v>0.008970000000000001</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0102</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="379">
@@ -18480,16 +18480,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G391" t="n">
         <v>0.833</v>
       </c>
       <c r="H391" t="n">
-        <v>0.617</v>
+        <v>0.509</v>
       </c>
       <c r="I391" t="n">
-        <v>0.617</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="392">
@@ -19072,7 +19072,7 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="G407" t="n">
         <v>0.866</v>
@@ -19192,7 +19192,7 @@
         <v>0.364</v>
       </c>
       <c r="I410" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="411">
@@ -19664,16 +19664,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.754</v>
+        <v>0.739</v>
       </c>
       <c r="G423" t="n">
         <v>0.841</v>
       </c>
       <c r="H423" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="I423" t="n">
-        <v>0.319</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="424">
@@ -19784,7 +19784,7 @@
         <v>0.000217</v>
       </c>
       <c r="I426" t="n">
-        <v>0.000597</v>
+        <v>0.000796</v>
       </c>
     </row>
     <row r="427">
@@ -20256,16 +20256,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G439" t="n">
         <v>0.853</v>
       </c>
       <c r="H439" t="n">
-        <v>0.412</v>
+        <v>0.327</v>
       </c>
       <c r="I439" t="n">
-        <v>0.412</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="440">
@@ -20376,7 +20376,7 @@
         <v>0.00158</v>
       </c>
       <c r="I442" t="n">
-        <v>0.00434</v>
+        <v>0.00443</v>
       </c>
     </row>
     <row r="443">
@@ -20848,16 +20848,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G455" t="n">
-        <v>0.842</v>
+        <v>0.833</v>
       </c>
       <c r="H455" t="n">
-        <v>0.501</v>
+        <v>0.509</v>
       </c>
       <c r="I455" t="n">
-        <v>0.551</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="456">
@@ -20962,13 +20962,13 @@
         <v>0.642</v>
       </c>
       <c r="G458" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H458" t="n">
-        <v>0.00579</v>
+        <v>0.009310000000000001</v>
       </c>
       <c r="I458" t="n">
-        <v>0.0318</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="459">
@@ -21440,10 +21440,10 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="G471" t="n">
-        <v>0.838</v>
+        <v>0.836</v>
       </c>
       <c r="H471" t="n">
         <v>0.619</v>
@@ -21554,13 +21554,13 @@
         <v>0.948</v>
       </c>
       <c r="G474" t="n">
-        <v>0.909</v>
+        <v>0.908</v>
       </c>
       <c r="H474" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="I474" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="475">
@@ -22032,16 +22032,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.754</v>
+        <v>0.739</v>
       </c>
       <c r="G487" t="n">
-        <v>0.899</v>
+        <v>0.884</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0417</v>
+        <v>0.0487</v>
       </c>
       <c r="I487" t="n">
-        <v>0.0655</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="488">
@@ -22146,13 +22146,13 @@
         <v>0.579</v>
       </c>
       <c r="G490" t="n">
-        <v>0.842</v>
+        <v>0.832</v>
       </c>
       <c r="H490" t="n">
-        <v>0.000102</v>
+        <v>0.000217</v>
       </c>
       <c r="I490" t="n">
-        <v>0.000561</v>
+        <v>0.000796</v>
       </c>
     </row>
     <row r="491">
@@ -22624,16 +22624,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G503" t="n">
-        <v>0.867</v>
+        <v>0.859</v>
       </c>
       <c r="H503" t="n">
-        <v>0.246</v>
+        <v>0.253</v>
       </c>
       <c r="I503" t="n">
-        <v>0.271</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="504">
@@ -22738,13 +22738,13 @@
         <v>0.719</v>
       </c>
       <c r="G506" t="n">
-        <v>0.874</v>
+        <v>0.868</v>
       </c>
       <c r="H506" t="n">
-        <v>0.000507</v>
+        <v>0.000918</v>
       </c>
       <c r="I506" t="n">
-        <v>0.00279</v>
+        <v>0.00443</v>
       </c>
     </row>
     <row r="507">
@@ -23216,16 +23216,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G519" t="n">
-        <v>0.867</v>
+        <v>0.858</v>
       </c>
       <c r="H519" t="n">
-        <v>0.225</v>
+        <v>0.234</v>
       </c>
       <c r="I519" t="n">
-        <v>0.309</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="520">
@@ -23330,13 +23330,13 @@
         <v>0.642</v>
       </c>
       <c r="G522" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="H522" t="n">
-        <v>0.009310000000000001</v>
+        <v>0.0146</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0341</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="523">
@@ -23808,10 +23808,10 @@
         <v>6</v>
       </c>
       <c r="F535" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="G535" t="n">
-        <v>0.884</v>
+        <v>0.882</v>
       </c>
       <c r="H535" t="n">
         <v>1</v>
@@ -23922,13 +23922,13 @@
         <v>0.948</v>
       </c>
       <c r="G538" t="n">
-        <v>0.908</v>
+        <v>0.907</v>
       </c>
       <c r="H538" t="n">
         <v>0.526</v>
       </c>
       <c r="I538" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="539">
@@ -24400,16 +24400,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.754</v>
+        <v>0.739</v>
       </c>
       <c r="G551" t="n">
-        <v>0.884</v>
+        <v>0.87</v>
       </c>
       <c r="H551" t="n">
-        <v>0.0756</v>
+        <v>0.0848</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0924</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="552">
@@ -24514,13 +24514,13 @@
         <v>0.579</v>
       </c>
       <c r="G554" t="n">
-        <v>0.832</v>
+        <v>0.821</v>
       </c>
       <c r="H554" t="n">
-        <v>0.000217</v>
+        <v>0.000441</v>
       </c>
       <c r="I554" t="n">
-        <v>0.000597</v>
+        <v>0.00121</v>
       </c>
     </row>
     <row r="555">
@@ -24992,16 +24992,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G567" t="n">
-        <v>0.884</v>
+        <v>0.876</v>
       </c>
       <c r="H567" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="I567" t="n">
-        <v>0.193</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="568">
@@ -25106,13 +25106,13 @@
         <v>0.719</v>
       </c>
       <c r="G570" t="n">
-        <v>0.868</v>
+        <v>0.862</v>
       </c>
       <c r="H570" t="n">
-        <v>0.000918</v>
+        <v>0.00161</v>
       </c>
       <c r="I570" t="n">
-        <v>0.00337</v>
+        <v>0.00443</v>
       </c>
     </row>
     <row r="571">
@@ -25584,16 +25584,16 @@
         <v>6</v>
       </c>
       <c r="F583" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G583" t="n">
-        <v>0.85</v>
+        <v>0.842</v>
       </c>
       <c r="H583" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="I583" t="n">
-        <v>0.484</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="584">
@@ -25698,13 +25698,13 @@
         <v>0.642</v>
       </c>
       <c r="G586" t="n">
-        <v>0.833</v>
+        <v>0.825</v>
       </c>
       <c r="H586" t="n">
-        <v>0.00115</v>
+        <v>0.00204</v>
       </c>
       <c r="I586" t="n">
-        <v>0.0126</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="587">
@@ -26176,10 +26176,10 @@
         <v>6</v>
       </c>
       <c r="F599" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="G599" t="n">
-        <v>0.859</v>
+        <v>0.857</v>
       </c>
       <c r="H599" t="n">
         <v>0.797</v>
@@ -26290,13 +26290,13 @@
         <v>0.948</v>
       </c>
       <c r="G602" t="n">
-        <v>0.912</v>
+        <v>0.911</v>
       </c>
       <c r="H602" t="n">
-        <v>0.53</v>
+        <v>0.529</v>
       </c>
       <c r="I602" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="603">
@@ -26768,16 +26768,16 @@
         <v>6</v>
       </c>
       <c r="F615" t="n">
-        <v>0.754</v>
+        <v>0.739</v>
       </c>
       <c r="G615" t="n">
-        <v>0.884</v>
+        <v>0.87</v>
       </c>
       <c r="H615" t="n">
-        <v>0.0756</v>
+        <v>0.0848</v>
       </c>
       <c r="I615" t="n">
-        <v>0.0924</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="616">
@@ -26882,13 +26882,13 @@
         <v>0.579</v>
       </c>
       <c r="G618" t="n">
-        <v>0.874</v>
+        <v>0.863</v>
       </c>
       <c r="H618" t="n">
-        <v>7.720000000000001e-06</v>
+        <v>1.93e-05</v>
       </c>
       <c r="I618" t="n">
-        <v>8.49e-05</v>
+        <v>0.000212</v>
       </c>
     </row>
     <row r="619">
@@ -27360,16 +27360,16 @@
         <v>6</v>
       </c>
       <c r="F631" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G631" t="n">
-        <v>0.871</v>
+        <v>0.863</v>
       </c>
       <c r="H631" t="n">
-        <v>0.239</v>
+        <v>0.247</v>
       </c>
       <c r="I631" t="n">
-        <v>0.271</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="632">
@@ -27474,13 +27474,13 @@
         <v>0.719</v>
       </c>
       <c r="G634" t="n">
-        <v>0.892</v>
+        <v>0.886</v>
       </c>
       <c r="H634" t="n">
-        <v>6.81e-05</v>
+        <v>0.000138</v>
       </c>
       <c r="I634" t="n">
-        <v>0.000749</v>
+        <v>0.00152</v>
       </c>
     </row>
     <row r="635">
@@ -27952,16 +27952,16 @@
         <v>6</v>
       </c>
       <c r="F647" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G647" t="n">
         <v>0.875</v>
       </c>
       <c r="H647" t="n">
-        <v>0.161</v>
+        <v>0.118</v>
       </c>
       <c r="I647" t="n">
-        <v>0.267</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="648">
@@ -28544,16 +28544,16 @@
         <v>6</v>
       </c>
       <c r="F663" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="G663" t="n">
         <v>0.982</v>
       </c>
       <c r="H663" t="n">
-        <v>0.0616</v>
+        <v>0.0611</v>
       </c>
       <c r="I663" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="664">
@@ -28664,7 +28664,7 @@
         <v>0.336</v>
       </c>
       <c r="I666" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="667">
@@ -29136,16 +29136,16 @@
         <v>6</v>
       </c>
       <c r="F679" t="n">
-        <v>0.754</v>
+        <v>0.739</v>
       </c>
       <c r="G679" t="n">
         <v>0.797</v>
       </c>
       <c r="H679" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="I679" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="680">
@@ -29728,16 +29728,16 @@
         <v>6</v>
       </c>
       <c r="F695" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G695" t="n">
         <v>0.88</v>
       </c>
       <c r="H695" t="n">
-        <v>0.164</v>
+        <v>0.121</v>
       </c>
       <c r="I695" t="n">
-        <v>0.226</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="696">
